--- a/Deliverables/BOM/eSpark-BOM-v2.1_Wo_Battery Boards.xlsx
+++ b/Deliverables/BOM/eSpark-BOM-v2.1_Wo_Battery Boards.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\Melih-SoundSensor\Deliverables\BOM\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5FEA017A-14A7-4810-A29C-A67AEE81FCC3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{686FFF28-20FD-4C10-BD42-91F322F9BCBD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-5730" yWindow="3105" windowWidth="11790" windowHeight="15360" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="20 Boards" sheetId="1" r:id="rId1"/>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="968" uniqueCount="211">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1016" uniqueCount="219">
   <si>
     <t>Component list</t>
   </si>
@@ -656,6 +656,30 @@
   </si>
   <si>
     <t>Single Board Cost</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Custom Supplier </t>
+  </si>
+  <si>
+    <t>Custom Supplier</t>
+  </si>
+  <si>
+    <t>LULU Quote</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LULU Qoute </t>
+  </si>
+  <si>
+    <t xml:space="preserve">2250 Pieces Stock in LCSC </t>
+  </si>
+  <si>
+    <t xml:space="preserve">1780 Pieces Stock in LCSC </t>
+  </si>
+  <si>
+    <t xml:space="preserve">2910 Pieces Stock in LCSC </t>
+  </si>
+  <si>
+    <t>Less Stock On LCSC ETA request sended</t>
   </si>
 </sst>
 </file>
@@ -667,7 +691,7 @@
     <numFmt numFmtId="165" formatCode="&quot;$&quot;#,##0.0000"/>
     <numFmt numFmtId="166" formatCode="&quot;$&quot;#,##0.00"/>
   </numFmts>
-  <fonts count="27" x14ac:knownFonts="1">
+  <fonts count="29" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -853,6 +877,22 @@
     <font>
       <b/>
       <sz val="14"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color rgb="FFFF0000"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -1153,7 +1193,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="138">
+  <cellXfs count="151">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -1279,24 +1319,6 @@
     <xf numFmtId="0" fontId="11" fillId="3" borderId="5" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="17" fillId="5" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1318,28 +1340,22 @@
     <xf numFmtId="0" fontId="11" fillId="5" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="17" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="11" fillId="5" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1485,7 +1501,6 @@
     <xf numFmtId="0" fontId="19" fillId="4" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="11" fillId="5" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1504,7 +1519,6 @@
     <xf numFmtId="165" fontId="18" fillId="2" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
     <xf numFmtId="0" fontId="11" fillId="5" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1531,6 +1545,36 @@
     </xf>
     <xf numFmtId="165" fontId="18" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="15" fillId="3" borderId="15" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="15" fillId="3" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="26" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="top"/>
@@ -1540,11 +1584,48 @@
       <alignment horizontal="center" vertical="top"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="166" fontId="15" fillId="3" borderId="15" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="28" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="166" fontId="15" fillId="3" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="28" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="27" fillId="4" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="19" fillId="4" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="23" fillId="4" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="2" borderId="17" xfId="1" quotePrefix="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="20" fillId="2" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="20" fillId="2" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="17" xfId="1" quotePrefix="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="21" fillId="4" borderId="17" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="4" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="4" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -2011,8 +2092,7 @@
     <col min="11" max="11" width="9" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="8.7109375" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="19.28515625" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="16.140625" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="13.42578125" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="16.140625" bestFit="1" customWidth="1"/>
     <col min="16" max="16" width="19.7109375" bestFit="1" customWidth="1"/>
     <col min="17" max="17" width="20.28515625" bestFit="1" customWidth="1"/>
     <col min="18" max="18" width="16.5703125" bestFit="1" customWidth="1"/>
@@ -2030,15 +2110,15 @@
       <c r="H1" s="2"/>
       <c r="I1" s="2"/>
       <c r="J1" s="2"/>
-      <c r="K1" s="49"/>
-      <c r="L1" s="49"/>
-      <c r="M1" s="49"/>
-      <c r="N1" s="49"/>
-      <c r="O1" s="49"/>
-      <c r="P1" s="49"/>
-      <c r="Q1" s="49"/>
-      <c r="R1" s="49"/>
-      <c r="S1" s="50"/>
+      <c r="K1" s="126"/>
+      <c r="L1" s="126"/>
+      <c r="M1" s="126"/>
+      <c r="N1" s="126"/>
+      <c r="O1" s="126"/>
+      <c r="P1" s="126"/>
+      <c r="Q1" s="126"/>
+      <c r="R1" s="126"/>
+      <c r="S1" s="127"/>
     </row>
     <row r="2" spans="1:19" ht="32.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1"/>
@@ -2088,7 +2168,7 @@
       <c r="P3" s="5"/>
       <c r="Q3" s="5"/>
       <c r="R3" s="5"/>
-      <c r="S3" s="51"/>
+      <c r="S3" s="128"/>
     </row>
     <row r="4" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A4" s="1"/>
@@ -2113,7 +2193,7 @@
       <c r="P4" s="6"/>
       <c r="Q4" s="6"/>
       <c r="R4" s="6"/>
-      <c r="S4" s="52"/>
+      <c r="S4" s="129"/>
     </row>
     <row r="5" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A5" s="1"/>
@@ -2138,7 +2218,7 @@
       <c r="P5" s="6"/>
       <c r="Q5" s="6"/>
       <c r="R5" s="6"/>
-      <c r="S5" s="52"/>
+      <c r="S5" s="129"/>
     </row>
     <row r="6" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A6" s="1"/>
@@ -2159,7 +2239,7 @@
       <c r="P6" s="6"/>
       <c r="Q6" s="6"/>
       <c r="R6" s="6"/>
-      <c r="S6" s="52"/>
+      <c r="S6" s="129"/>
     </row>
     <row r="7" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A7" s="1"/>
@@ -2180,7 +2260,7 @@
       <c r="P7" s="8"/>
       <c r="Q7" s="8"/>
       <c r="R7" s="8"/>
-      <c r="S7" s="52"/>
+      <c r="S7" s="129"/>
     </row>
     <row r="8" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" s="1"/>
@@ -2201,11 +2281,11 @@
       <c r="P8" s="8"/>
       <c r="Q8" s="8"/>
       <c r="R8" s="8"/>
-      <c r="S8" s="52"/>
+      <c r="S8" s="129"/>
     </row>
     <row r="9" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A9" s="1"/>
-      <c r="B9" s="55" t="s">
+      <c r="B9" s="49" t="s">
         <v>4</v>
       </c>
       <c r="C9" s="30" t="s">
@@ -2262,11 +2342,11 @@
     </row>
     <row r="10" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A10" s="1"/>
-      <c r="B10" s="69">
+      <c r="B10" s="61">
         <f>ROW(B10) - ROW($B$9)</f>
         <v>1</v>
       </c>
-      <c r="C10" s="58" t="s">
+      <c r="C10" s="52" t="s">
         <v>7</v>
       </c>
       <c r="D10" s="39" t="s">
@@ -2287,7 +2367,7 @@
       <c r="I10" s="38" t="s">
         <v>176</v>
       </c>
-      <c r="J10" s="79" t="s">
+      <c r="J10" s="71" t="s">
         <v>146</v>
       </c>
       <c r="K10" s="38" t="s">
@@ -2303,14 +2383,14 @@
       <c r="N10" s="39">
         <v>40</v>
       </c>
-      <c r="O10" s="102" t="s">
+      <c r="O10" s="94" t="s">
         <v>152</v>
       </c>
-      <c r="P10" s="96">
+      <c r="P10" s="88">
         <v>1.7100000000000001E-2</v>
       </c>
       <c r="Q10" s="42">
-        <f>P10*N10</f>
+        <f t="shared" ref="Q10:Q30" si="0">P10*N10</f>
         <v>0.68400000000000005</v>
       </c>
       <c r="R10" s="39"/>
@@ -2318,11 +2398,11 @@
     </row>
     <row r="11" spans="1:19" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A11" s="1"/>
-      <c r="B11" s="61">
-        <f t="shared" ref="B11:B38" si="0">ROW(B11) - ROW($B$9)</f>
+      <c r="B11" s="55">
+        <f t="shared" ref="B11:B38" si="1">ROW(B11) - ROW($B$9)</f>
         <v>2</v>
       </c>
-      <c r="C11" s="59" t="s">
+      <c r="C11" s="53" t="s">
         <v>7</v>
       </c>
       <c r="D11" s="41" t="s">
@@ -2353,20 +2433,20 @@
         <v>17</v>
       </c>
       <c r="M11" s="40">
-        <f t="shared" ref="M11:M39" si="1">L11*20</f>
+        <f t="shared" ref="M11:M39" si="2">L11*20</f>
         <v>340</v>
       </c>
       <c r="N11" s="41">
         <v>400</v>
       </c>
-      <c r="O11" s="88" t="s">
+      <c r="O11" s="80" t="s">
         <v>152</v>
       </c>
-      <c r="P11" s="97">
+      <c r="P11" s="89">
         <v>4.4999999999999997E-3</v>
       </c>
-      <c r="Q11" s="93">
-        <f>P11*N11</f>
+      <c r="Q11" s="85">
+        <f t="shared" si="0"/>
         <v>1.7999999999999998</v>
       </c>
       <c r="R11" s="41"/>
@@ -2374,67 +2454,67 @@
     </row>
     <row r="12" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A12" s="1"/>
-      <c r="B12" s="61">
+      <c r="B12" s="55">
         <f>ROW(B12) - ROW($B$9)</f>
         <v>3</v>
       </c>
-      <c r="C12" s="70" t="s">
+      <c r="C12" s="62" t="s">
         <v>7</v>
       </c>
-      <c r="D12" s="72" t="s">
+      <c r="D12" s="64" t="s">
         <v>13</v>
       </c>
-      <c r="E12" s="56" t="s">
+      <c r="E12" s="50" t="s">
         <v>43</v>
       </c>
-      <c r="F12" s="72" t="s">
+      <c r="F12" s="64" t="s">
         <v>73</v>
       </c>
-      <c r="G12" s="56" t="s">
+      <c r="G12" s="50" t="s">
         <v>95</v>
       </c>
-      <c r="H12" s="72" t="s">
+      <c r="H12" s="64" t="s">
         <v>114</v>
       </c>
-      <c r="I12" s="56" t="s">
-        <v>176</v>
-      </c>
-      <c r="J12" s="80" t="s">
+      <c r="I12" s="50" t="s">
+        <v>176</v>
+      </c>
+      <c r="J12" s="72" t="s">
         <v>154</v>
       </c>
-      <c r="K12" s="56" t="s">
+      <c r="K12" s="50" t="s">
         <v>133</v>
       </c>
-      <c r="L12" s="72">
+      <c r="L12" s="64">
         <v>8</v>
       </c>
-      <c r="M12" s="56">
-        <f t="shared" si="1"/>
+      <c r="M12" s="50">
+        <f t="shared" si="2"/>
         <v>160</v>
       </c>
-      <c r="N12" s="72">
+      <c r="N12" s="64">
         <v>200</v>
       </c>
-      <c r="O12" s="102" t="s">
+      <c r="O12" s="94" t="s">
         <v>152</v>
       </c>
-      <c r="P12" s="98">
+      <c r="P12" s="90">
         <v>2.5000000000000001E-3</v>
       </c>
-      <c r="Q12" s="94">
-        <f>P12*N12</f>
+      <c r="Q12" s="86">
+        <f t="shared" si="0"/>
         <v>0.5</v>
       </c>
-      <c r="R12" s="72"/>
-      <c r="S12" s="100"/>
+      <c r="R12" s="64"/>
+      <c r="S12" s="92"/>
     </row>
     <row r="13" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A13" s="1"/>
-      <c r="B13" s="61">
-        <f t="shared" si="0"/>
+      <c r="B13" s="55">
+        <f t="shared" si="1"/>
         <v>4</v>
       </c>
-      <c r="C13" s="59" t="s">
+      <c r="C13" s="53" t="s">
         <v>7</v>
       </c>
       <c r="D13" s="41" t="s">
@@ -2465,20 +2545,20 @@
         <v>2</v>
       </c>
       <c r="M13" s="40">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>40</v>
       </c>
       <c r="N13" s="41">
         <v>45</v>
       </c>
-      <c r="O13" s="88" t="s">
+      <c r="O13" s="80" t="s">
         <v>152</v>
       </c>
-      <c r="P13" s="97">
+      <c r="P13" s="89">
         <v>1.5225</v>
       </c>
-      <c r="Q13" s="93">
-        <f>P13*N13</f>
+      <c r="Q13" s="85">
+        <f t="shared" si="0"/>
         <v>68.512500000000003</v>
       </c>
       <c r="R13" s="41"/>
@@ -2486,67 +2566,67 @@
     </row>
     <row r="14" spans="1:19" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A14" s="1"/>
-      <c r="B14" s="61">
+      <c r="B14" s="55">
         <f>ROW(B14) - ROW($B$9)</f>
         <v>5</v>
       </c>
-      <c r="C14" s="70" t="s">
+      <c r="C14" s="62" t="s">
         <v>7</v>
       </c>
-      <c r="D14" s="72" t="s">
+      <c r="D14" s="64" t="s">
         <v>15</v>
       </c>
-      <c r="E14" s="56" t="s">
+      <c r="E14" s="50" t="s">
         <v>45</v>
       </c>
-      <c r="F14" s="72" t="s">
+      <c r="F14" s="64" t="s">
         <v>72</v>
       </c>
-      <c r="G14" s="56" t="s">
+      <c r="G14" s="50" t="s">
         <v>97</v>
       </c>
-      <c r="H14" s="72" t="s">
+      <c r="H14" s="64" t="s">
         <v>114</v>
       </c>
-      <c r="I14" s="56" t="s">
-        <v>176</v>
-      </c>
-      <c r="J14" s="80" t="s">
+      <c r="I14" s="50" t="s">
+        <v>176</v>
+      </c>
+      <c r="J14" s="72" t="s">
         <v>155</v>
       </c>
-      <c r="K14" s="56" t="s">
+      <c r="K14" s="50" t="s">
         <v>135</v>
       </c>
-      <c r="L14" s="72">
+      <c r="L14" s="64">
         <v>12</v>
       </c>
-      <c r="M14" s="56">
-        <f t="shared" si="1"/>
+      <c r="M14" s="50">
+        <f t="shared" si="2"/>
         <v>240</v>
       </c>
-      <c r="N14" s="72">
+      <c r="N14" s="64">
         <v>300</v>
       </c>
-      <c r="O14" s="102" t="s">
+      <c r="O14" s="94" t="s">
         <v>152</v>
       </c>
-      <c r="P14" s="98">
+      <c r="P14" s="90">
         <v>5.3E-3</v>
       </c>
-      <c r="Q14" s="94">
-        <f>P14*N14</f>
+      <c r="Q14" s="86">
+        <f t="shared" si="0"/>
         <v>1.59</v>
       </c>
-      <c r="R14" s="72"/>
-      <c r="S14" s="100"/>
+      <c r="R14" s="64"/>
+      <c r="S14" s="92"/>
     </row>
     <row r="15" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A15" s="1"/>
-      <c r="B15" s="61">
-        <f t="shared" si="0"/>
+      <c r="B15" s="55">
+        <f t="shared" si="1"/>
         <v>6</v>
       </c>
-      <c r="C15" s="59" t="s">
+      <c r="C15" s="53" t="s">
         <v>7</v>
       </c>
       <c r="D15" s="41" t="s">
@@ -2577,20 +2657,20 @@
         <v>1</v>
       </c>
       <c r="M15" s="40">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>20</v>
       </c>
       <c r="N15" s="41">
         <v>30</v>
       </c>
-      <c r="O15" s="88" t="s">
+      <c r="O15" s="80" t="s">
         <v>152</v>
       </c>
-      <c r="P15" s="97">
+      <c r="P15" s="89">
         <v>3.3500000000000002E-2</v>
       </c>
-      <c r="Q15" s="93">
-        <f>P15*N15</f>
+      <c r="Q15" s="85">
+        <f t="shared" si="0"/>
         <v>1.0050000000000001</v>
       </c>
       <c r="R15" s="41"/>
@@ -2598,67 +2678,67 @@
     </row>
     <row r="16" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A16" s="1"/>
-      <c r="B16" s="61">
+      <c r="B16" s="55">
         <f>ROW(B16) - ROW($B$9)</f>
         <v>7</v>
       </c>
-      <c r="C16" s="70" t="s">
+      <c r="C16" s="62" t="s">
         <v>7</v>
       </c>
-      <c r="D16" s="72" t="s">
+      <c r="D16" s="64" t="s">
         <v>17</v>
       </c>
-      <c r="E16" s="56" t="s">
+      <c r="E16" s="50" t="s">
         <v>47</v>
       </c>
-      <c r="F16" s="72" t="s">
+      <c r="F16" s="64" t="s">
         <v>72</v>
       </c>
-      <c r="G16" s="56" t="s">
+      <c r="G16" s="50" t="s">
         <v>99</v>
       </c>
-      <c r="H16" s="72" t="s">
+      <c r="H16" s="64" t="s">
         <v>114</v>
       </c>
-      <c r="I16" s="56" t="s">
-        <v>176</v>
-      </c>
-      <c r="J16" s="80" t="s">
+      <c r="I16" s="50" t="s">
+        <v>176</v>
+      </c>
+      <c r="J16" s="72" t="s">
         <v>157</v>
       </c>
-      <c r="K16" s="56" t="s">
+      <c r="K16" s="50" t="s">
         <v>137</v>
       </c>
-      <c r="L16" s="72">
+      <c r="L16" s="64">
         <v>6</v>
       </c>
-      <c r="M16" s="56">
-        <f t="shared" si="1"/>
+      <c r="M16" s="50">
+        <f t="shared" si="2"/>
         <v>120</v>
       </c>
-      <c r="N16" s="72">
+      <c r="N16" s="64">
         <v>200</v>
       </c>
-      <c r="O16" s="102" t="s">
+      <c r="O16" s="94" t="s">
         <v>152</v>
       </c>
-      <c r="P16" s="98">
+      <c r="P16" s="90">
         <v>2.7000000000000001E-3</v>
       </c>
-      <c r="Q16" s="94">
-        <f>P16*N16</f>
+      <c r="Q16" s="86">
+        <f t="shared" si="0"/>
         <v>0.54</v>
       </c>
-      <c r="R16" s="72"/>
-      <c r="S16" s="100"/>
+      <c r="R16" s="64"/>
+      <c r="S16" s="92"/>
     </row>
     <row r="17" spans="1:19" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A17" s="1"/>
-      <c r="B17" s="61">
-        <f t="shared" si="0"/>
+      <c r="B17" s="55">
+        <f t="shared" si="1"/>
         <v>8</v>
       </c>
-      <c r="C17" s="59" t="s">
+      <c r="C17" s="53" t="s">
         <v>7</v>
       </c>
       <c r="D17" s="41" t="s">
@@ -2689,20 +2769,20 @@
         <v>16</v>
       </c>
       <c r="M17" s="40">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>320</v>
       </c>
       <c r="N17" s="41">
         <v>350</v>
       </c>
-      <c r="O17" s="88" t="s">
+      <c r="O17" s="80" t="s">
         <v>152</v>
       </c>
-      <c r="P17" s="97">
+      <c r="P17" s="89">
         <v>9.2999999999999992E-3</v>
       </c>
-      <c r="Q17" s="93">
-        <f>P17*N17</f>
+      <c r="Q17" s="85">
+        <f t="shared" si="0"/>
         <v>3.2549999999999999</v>
       </c>
       <c r="R17" s="41"/>
@@ -2710,67 +2790,67 @@
     </row>
     <row r="18" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A18" s="1"/>
-      <c r="B18" s="61">
+      <c r="B18" s="55">
         <f>ROW(B18) - ROW($B$9)</f>
         <v>9</v>
       </c>
-      <c r="C18" s="70" t="s">
+      <c r="C18" s="62" t="s">
         <v>7</v>
       </c>
-      <c r="D18" s="72" t="s">
+      <c r="D18" s="64" t="s">
         <v>159</v>
       </c>
-      <c r="E18" s="56" t="s">
+      <c r="E18" s="50" t="s">
         <v>49</v>
       </c>
-      <c r="F18" s="72" t="s">
+      <c r="F18" s="64" t="s">
         <v>72</v>
       </c>
-      <c r="G18" s="56" t="s">
+      <c r="G18" s="50" t="s">
         <v>101</v>
       </c>
-      <c r="H18" s="72" t="s">
+      <c r="H18" s="64" t="s">
         <v>113</v>
       </c>
-      <c r="I18" s="56" t="s">
-        <v>176</v>
-      </c>
-      <c r="J18" s="80" t="s">
+      <c r="I18" s="50" t="s">
+        <v>176</v>
+      </c>
+      <c r="J18" s="72" t="s">
         <v>193</v>
       </c>
-      <c r="K18" s="56" t="s">
+      <c r="K18" s="50" t="s">
         <v>139</v>
       </c>
-      <c r="L18" s="72">
+      <c r="L18" s="64">
         <v>3</v>
       </c>
-      <c r="M18" s="56">
-        <f t="shared" si="1"/>
+      <c r="M18" s="50">
+        <f t="shared" si="2"/>
         <v>60</v>
       </c>
-      <c r="N18" s="72">
+      <c r="N18" s="64">
         <v>80</v>
       </c>
-      <c r="O18" s="102" t="s">
+      <c r="O18" s="94" t="s">
         <v>152</v>
       </c>
-      <c r="P18" s="98">
+      <c r="P18" s="90">
         <v>2.3E-2</v>
       </c>
-      <c r="Q18" s="94">
-        <f>P18*N18</f>
+      <c r="Q18" s="86">
+        <f t="shared" si="0"/>
         <v>1.8399999999999999</v>
       </c>
-      <c r="R18" s="72"/>
-      <c r="S18" s="100"/>
+      <c r="R18" s="64"/>
+      <c r="S18" s="92"/>
     </row>
     <row r="19" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A19" s="1"/>
-      <c r="B19" s="61">
+      <c r="B19" s="55">
         <f>ROW(B19) - ROW($B$9)</f>
         <v>10</v>
       </c>
-      <c r="C19" s="59" t="s">
+      <c r="C19" s="53" t="s">
         <v>7</v>
       </c>
       <c r="D19" s="41" t="s">
@@ -2801,20 +2881,20 @@
         <v>1</v>
       </c>
       <c r="M19" s="40">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>20</v>
       </c>
       <c r="N19" s="41">
         <v>100</v>
       </c>
-      <c r="O19" s="88" t="s">
+      <c r="O19" s="80" t="s">
         <v>152</v>
       </c>
-      <c r="P19" s="97">
+      <c r="P19" s="89">
         <v>3.0999999999999999E-3</v>
       </c>
-      <c r="Q19" s="93">
-        <f>P19*N19</f>
+      <c r="Q19" s="85">
+        <f t="shared" si="0"/>
         <v>0.31</v>
       </c>
       <c r="R19" s="41"/>
@@ -2822,67 +2902,67 @@
     </row>
     <row r="20" spans="1:19" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A20" s="1"/>
-      <c r="B20" s="61">
+      <c r="B20" s="55">
+        <f t="shared" si="1"/>
+        <v>11</v>
+      </c>
+      <c r="C20" s="62" t="s">
+        <v>7</v>
+      </c>
+      <c r="D20" s="64" t="s">
+        <v>20</v>
+      </c>
+      <c r="E20" s="50" t="s">
+        <v>51</v>
+      </c>
+      <c r="F20" s="64" t="s">
+        <v>75</v>
+      </c>
+      <c r="G20" s="50" t="s">
+        <v>103</v>
+      </c>
+      <c r="H20" s="64" t="s">
+        <v>116</v>
+      </c>
+      <c r="I20" s="50" t="s">
+        <v>176</v>
+      </c>
+      <c r="J20" s="72" t="s">
+        <v>194</v>
+      </c>
+      <c r="K20" s="50" t="s">
+        <v>139</v>
+      </c>
+      <c r="L20" s="64">
+        <v>16</v>
+      </c>
+      <c r="M20" s="50">
+        <f t="shared" si="2"/>
+        <v>320</v>
+      </c>
+      <c r="N20" s="64">
+        <v>350</v>
+      </c>
+      <c r="O20" s="94" t="s">
+        <v>152</v>
+      </c>
+      <c r="P20" s="90">
+        <v>6.7199999999999996E-2</v>
+      </c>
+      <c r="Q20" s="86">
         <f t="shared" si="0"/>
-        <v>11</v>
-      </c>
-      <c r="C20" s="70" t="s">
-        <v>7</v>
-      </c>
-      <c r="D20" s="72" t="s">
-        <v>20</v>
-      </c>
-      <c r="E20" s="56" t="s">
-        <v>51</v>
-      </c>
-      <c r="F20" s="72" t="s">
-        <v>75</v>
-      </c>
-      <c r="G20" s="56" t="s">
-        <v>103</v>
-      </c>
-      <c r="H20" s="72" t="s">
-        <v>116</v>
-      </c>
-      <c r="I20" s="56" t="s">
-        <v>176</v>
-      </c>
-      <c r="J20" s="80" t="s">
-        <v>194</v>
-      </c>
-      <c r="K20" s="56" t="s">
-        <v>139</v>
-      </c>
-      <c r="L20" s="72">
-        <v>16</v>
-      </c>
-      <c r="M20" s="56">
-        <f t="shared" si="1"/>
-        <v>320</v>
-      </c>
-      <c r="N20" s="72">
-        <v>350</v>
-      </c>
-      <c r="O20" s="102" t="s">
-        <v>152</v>
-      </c>
-      <c r="P20" s="98">
-        <v>6.7199999999999996E-2</v>
-      </c>
-      <c r="Q20" s="94">
-        <f>P20*N20</f>
         <v>23.52</v>
       </c>
-      <c r="R20" s="72"/>
-      <c r="S20" s="100"/>
+      <c r="R20" s="64"/>
+      <c r="S20" s="92"/>
     </row>
     <row r="21" spans="1:19" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A21" s="1"/>
-      <c r="B21" s="61">
+      <c r="B21" s="55">
         <f>ROW(B21) - ROW($B$9)</f>
         <v>12</v>
       </c>
-      <c r="C21" s="59" t="s">
+      <c r="C21" s="53" t="s">
         <v>163</v>
       </c>
       <c r="D21" s="41" t="s">
@@ -2891,7 +2971,7 @@
       <c r="E21" s="40" t="s">
         <v>52</v>
       </c>
-      <c r="F21" s="76" t="s">
+      <c r="F21" s="68" t="s">
         <v>171</v>
       </c>
       <c r="G21" s="40" t="s">
@@ -2913,20 +2993,20 @@
         <v>1</v>
       </c>
       <c r="M21" s="40">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>20</v>
       </c>
       <c r="N21" s="41">
         <v>30</v>
       </c>
-      <c r="O21" s="88" t="s">
+      <c r="O21" s="80" t="s">
         <v>152</v>
       </c>
-      <c r="P21" s="97">
+      <c r="P21" s="89">
         <v>3.9800000000000002E-2</v>
       </c>
-      <c r="Q21" s="93">
-        <f>P21*N21</f>
+      <c r="Q21" s="85">
+        <f t="shared" si="0"/>
         <v>1.194</v>
       </c>
       <c r="R21" s="41"/>
@@ -2934,67 +3014,67 @@
     </row>
     <row r="22" spans="1:19" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A22" s="1"/>
-      <c r="B22" s="61">
+      <c r="B22" s="55">
+        <f t="shared" si="1"/>
+        <v>13</v>
+      </c>
+      <c r="C22" s="62" t="s">
+        <v>163</v>
+      </c>
+      <c r="D22" s="64" t="s">
+        <v>22</v>
+      </c>
+      <c r="E22" s="50" t="s">
+        <v>53</v>
+      </c>
+      <c r="F22" s="64" t="s">
+        <v>77</v>
+      </c>
+      <c r="G22" s="50" t="s">
+        <v>104</v>
+      </c>
+      <c r="H22" s="64" t="s">
+        <v>118</v>
+      </c>
+      <c r="I22" s="50" t="s">
+        <v>176</v>
+      </c>
+      <c r="J22" s="72" t="s">
+        <v>173</v>
+      </c>
+      <c r="K22" s="50" t="s">
+        <v>176</v>
+      </c>
+      <c r="L22" s="64">
+        <v>1</v>
+      </c>
+      <c r="M22" s="50">
+        <f t="shared" si="2"/>
+        <v>20</v>
+      </c>
+      <c r="N22" s="64">
+        <v>30</v>
+      </c>
+      <c r="O22" s="81" t="s">
+        <v>152</v>
+      </c>
+      <c r="P22" s="90">
+        <v>3.1800000000000002E-2</v>
+      </c>
+      <c r="Q22" s="86">
         <f t="shared" si="0"/>
-        <v>13</v>
-      </c>
-      <c r="C22" s="70" t="s">
-        <v>163</v>
-      </c>
-      <c r="D22" s="72" t="s">
-        <v>22</v>
-      </c>
-      <c r="E22" s="56" t="s">
-        <v>53</v>
-      </c>
-      <c r="F22" s="72" t="s">
-        <v>77</v>
-      </c>
-      <c r="G22" s="56" t="s">
-        <v>104</v>
-      </c>
-      <c r="H22" s="72" t="s">
-        <v>118</v>
-      </c>
-      <c r="I22" s="56" t="s">
-        <v>176</v>
-      </c>
-      <c r="J22" s="80" t="s">
-        <v>173</v>
-      </c>
-      <c r="K22" s="56" t="s">
-        <v>176</v>
-      </c>
-      <c r="L22" s="72">
-        <v>1</v>
-      </c>
-      <c r="M22" s="56">
-        <f t="shared" si="1"/>
-        <v>20</v>
-      </c>
-      <c r="N22" s="72">
-        <v>30</v>
-      </c>
-      <c r="O22" s="89" t="s">
-        <v>152</v>
-      </c>
-      <c r="P22" s="98">
-        <v>3.1800000000000002E-2</v>
-      </c>
-      <c r="Q22" s="94">
-        <f>P22*N22</f>
         <v>0.95400000000000007</v>
       </c>
-      <c r="R22" s="72"/>
-      <c r="S22" s="100"/>
+      <c r="R22" s="64"/>
+      <c r="S22" s="92"/>
     </row>
     <row r="23" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A23" s="1"/>
-      <c r="B23" s="61">
+      <c r="B23" s="55">
         <f>ROW(B23) - ROW($B$9)</f>
         <v>14</v>
       </c>
-      <c r="C23" s="59" t="s">
+      <c r="C23" s="53" t="s">
         <v>164</v>
       </c>
       <c r="D23" s="41" t="s">
@@ -3006,7 +3086,7 @@
       <c r="F23" s="41" t="s">
         <v>78</v>
       </c>
-      <c r="G23" s="103" t="s">
+      <c r="G23" s="95" t="s">
         <v>105</v>
       </c>
       <c r="H23" s="41" t="s">
@@ -3015,7 +3095,7 @@
       <c r="I23" s="40" t="s">
         <v>196</v>
       </c>
-      <c r="J23" s="81" t="s">
+      <c r="J23" s="73" t="s">
         <v>195</v>
       </c>
       <c r="K23" s="40" t="s">
@@ -3025,20 +3105,20 @@
         <v>1</v>
       </c>
       <c r="M23" s="40">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>20</v>
       </c>
       <c r="N23" s="41">
         <v>40</v>
       </c>
-      <c r="O23" s="104" t="s">
+      <c r="O23" s="96" t="s">
         <v>152</v>
       </c>
-      <c r="P23" s="97">
+      <c r="P23" s="89">
         <v>2.5899999999999999E-2</v>
       </c>
-      <c r="Q23" s="93">
-        <f>P23*N23</f>
+      <c r="Q23" s="85">
+        <f t="shared" si="0"/>
         <v>1.036</v>
       </c>
       <c r="R23" s="41"/>
@@ -3046,169 +3126,181 @@
     </row>
     <row r="24" spans="1:19" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A24" s="1"/>
-      <c r="B24" s="61">
+      <c r="B24" s="55">
+        <f t="shared" si="1"/>
+        <v>15</v>
+      </c>
+      <c r="C24" s="62" t="s">
+        <v>165</v>
+      </c>
+      <c r="D24" s="64" t="s">
+        <v>24</v>
+      </c>
+      <c r="E24" s="50" t="s">
+        <v>55</v>
+      </c>
+      <c r="F24" s="64" t="s">
+        <v>175</v>
+      </c>
+      <c r="G24" s="50" t="s">
+        <v>79</v>
+      </c>
+      <c r="H24" s="64" t="s">
+        <v>120</v>
+      </c>
+      <c r="I24" s="50" t="s">
+        <v>176</v>
+      </c>
+      <c r="J24" s="74" t="s">
+        <v>185</v>
+      </c>
+      <c r="K24" s="50" t="s">
+        <v>176</v>
+      </c>
+      <c r="L24" s="64">
+        <v>1</v>
+      </c>
+      <c r="M24" s="50">
+        <f t="shared" si="2"/>
+        <v>20</v>
+      </c>
+      <c r="N24" s="64">
+        <v>30</v>
+      </c>
+      <c r="O24" s="82" t="s">
+        <v>152</v>
+      </c>
+      <c r="P24" s="90">
+        <v>5.5599999999999997E-2</v>
+      </c>
+      <c r="Q24" s="86">
         <f t="shared" si="0"/>
-        <v>15</v>
-      </c>
-      <c r="C24" s="70" t="s">
-        <v>165</v>
-      </c>
-      <c r="D24" s="72" t="s">
-        <v>24</v>
-      </c>
-      <c r="E24" s="56" t="s">
-        <v>55</v>
-      </c>
-      <c r="F24" s="72" t="s">
-        <v>175</v>
-      </c>
-      <c r="G24" s="56" t="s">
-        <v>79</v>
-      </c>
-      <c r="H24" s="72" t="s">
-        <v>120</v>
-      </c>
-      <c r="I24" s="56" t="s">
-        <v>176</v>
-      </c>
-      <c r="J24" s="82" t="s">
-        <v>185</v>
-      </c>
-      <c r="K24" s="56" t="s">
-        <v>176</v>
-      </c>
-      <c r="L24" s="72">
-        <v>1</v>
-      </c>
-      <c r="M24" s="56">
-        <f t="shared" si="1"/>
-        <v>20</v>
-      </c>
-      <c r="N24" s="72">
-        <v>30</v>
-      </c>
-      <c r="O24" s="90" t="s">
-        <v>152</v>
-      </c>
-      <c r="P24" s="98">
-        <v>5.5599999999999997E-2</v>
-      </c>
-      <c r="Q24" s="94">
-        <f>P24*N24</f>
         <v>1.6679999999999999</v>
       </c>
-      <c r="R24" s="72"/>
-      <c r="S24" s="100"/>
+      <c r="R24" s="64"/>
+      <c r="S24" s="92"/>
     </row>
     <row r="25" spans="1:19" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A25" s="1"/>
-      <c r="B25" s="61">
+      <c r="B25" s="55">
         <f>ROW(B25) - ROW($B$9)</f>
         <v>16</v>
       </c>
-      <c r="C25" s="59" t="s">
+      <c r="C25" s="139" t="s">
         <v>8</v>
       </c>
-      <c r="D25" s="41" t="s">
+      <c r="D25" s="140" t="s">
         <v>25</v>
       </c>
-      <c r="E25" s="40" t="s">
+      <c r="E25" s="108" t="s">
         <v>56</v>
       </c>
-      <c r="F25" s="41" t="s">
+      <c r="F25" s="140" t="s">
         <v>175</v>
       </c>
-      <c r="G25" s="40" t="s">
+      <c r="G25" s="108" t="s">
         <v>80</v>
       </c>
-      <c r="H25" s="41" t="s">
+      <c r="H25" s="140" t="s">
         <v>121</v>
       </c>
-      <c r="I25" s="40" t="s">
-        <v>176</v>
-      </c>
-      <c r="J25" s="41"/>
-      <c r="K25" s="40"/>
-      <c r="L25" s="41">
+      <c r="I25" s="108" t="s">
+        <v>176</v>
+      </c>
+      <c r="J25" s="140" t="s">
+        <v>176</v>
+      </c>
+      <c r="K25" s="108" t="s">
+        <v>176</v>
+      </c>
+      <c r="L25" s="140">
         <v>8</v>
       </c>
-      <c r="M25" s="40">
-        <f t="shared" si="1"/>
+      <c r="M25" s="108">
+        <f t="shared" si="2"/>
         <v>160</v>
       </c>
-      <c r="N25" s="41"/>
-      <c r="O25" s="57"/>
-      <c r="P25" s="97"/>
-      <c r="Q25" s="93">
-        <f>P25*N25</f>
-        <v>0</v>
-      </c>
-      <c r="R25" s="41"/>
+      <c r="N25" s="140">
+        <v>200</v>
+      </c>
+      <c r="O25" s="96" t="s">
+        <v>211</v>
+      </c>
+      <c r="P25" s="141">
+        <v>2</v>
+      </c>
+      <c r="Q25" s="142">
+        <f t="shared" si="0"/>
+        <v>400</v>
+      </c>
+      <c r="R25" s="136" t="s">
+        <v>214</v>
+      </c>
       <c r="S25" s="44"/>
     </row>
     <row r="26" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A26" s="1"/>
-      <c r="B26" s="61">
+      <c r="B26" s="55">
+        <f t="shared" si="1"/>
+        <v>17</v>
+      </c>
+      <c r="C26" s="62" t="s">
+        <v>164</v>
+      </c>
+      <c r="D26" s="64" t="s">
+        <v>26</v>
+      </c>
+      <c r="E26" s="50" t="s">
+        <v>57</v>
+      </c>
+      <c r="F26" s="64" t="s">
+        <v>81</v>
+      </c>
+      <c r="G26" s="97">
+        <v>61300611121</v>
+      </c>
+      <c r="H26" s="64" t="s">
+        <v>122</v>
+      </c>
+      <c r="I26" s="50" t="s">
+        <v>197</v>
+      </c>
+      <c r="J26" s="72" t="s">
+        <v>197</v>
+      </c>
+      <c r="K26" s="50" t="s">
+        <v>176</v>
+      </c>
+      <c r="L26" s="64">
+        <v>1</v>
+      </c>
+      <c r="M26" s="50">
+        <f t="shared" si="2"/>
+        <v>20</v>
+      </c>
+      <c r="N26" s="64">
+        <v>40</v>
+      </c>
+      <c r="O26" s="94" t="s">
+        <v>152</v>
+      </c>
+      <c r="P26" s="90">
+        <v>2.7900000000000001E-2</v>
+      </c>
+      <c r="Q26" s="86">
         <f t="shared" si="0"/>
-        <v>17</v>
-      </c>
-      <c r="C26" s="70" t="s">
-        <v>164</v>
-      </c>
-      <c r="D26" s="72" t="s">
-        <v>26</v>
-      </c>
-      <c r="E26" s="56" t="s">
-        <v>57</v>
-      </c>
-      <c r="F26" s="72" t="s">
-        <v>81</v>
-      </c>
-      <c r="G26" s="105">
-        <v>61300611121</v>
-      </c>
-      <c r="H26" s="72" t="s">
-        <v>122</v>
-      </c>
-      <c r="I26" s="56" t="s">
-        <v>197</v>
-      </c>
-      <c r="J26" s="80" t="s">
-        <v>197</v>
-      </c>
-      <c r="K26" s="56" t="s">
-        <v>176</v>
-      </c>
-      <c r="L26" s="72">
-        <v>1</v>
-      </c>
-      <c r="M26" s="56">
-        <f t="shared" si="1"/>
-        <v>20</v>
-      </c>
-      <c r="N26" s="72">
-        <v>40</v>
-      </c>
-      <c r="O26" s="102" t="s">
-        <v>152</v>
-      </c>
-      <c r="P26" s="98">
-        <v>2.7900000000000001E-2</v>
-      </c>
-      <c r="Q26" s="94">
-        <f>P26*N26</f>
         <v>1.1160000000000001</v>
       </c>
-      <c r="R26" s="72"/>
-      <c r="S26" s="100"/>
+      <c r="R26" s="64"/>
+      <c r="S26" s="92"/>
     </row>
     <row r="27" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A27" s="1"/>
-      <c r="B27" s="61">
+      <c r="B27" s="55">
         <f>ROW(B27) - ROW($B$9)</f>
         <v>18</v>
       </c>
-      <c r="C27" s="59" t="s">
+      <c r="C27" s="53" t="s">
         <v>166</v>
       </c>
       <c r="D27" s="41" t="s">
@@ -3220,16 +3312,16 @@
       <c r="F27" s="41" t="s">
         <v>82</v>
       </c>
-      <c r="G27" s="103" t="s">
+      <c r="G27" s="95" t="s">
         <v>106</v>
       </c>
       <c r="H27" s="41" t="s">
         <v>119</v>
       </c>
-      <c r="I27" s="78" t="s">
+      <c r="I27" s="70" t="s">
         <v>182</v>
       </c>
-      <c r="J27" s="83" t="s">
+      <c r="J27" s="75" t="s">
         <v>181</v>
       </c>
       <c r="K27" s="40" t="s">
@@ -3239,20 +3331,20 @@
         <v>3</v>
       </c>
       <c r="M27" s="40">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>60</v>
       </c>
       <c r="N27" s="41">
         <v>100</v>
       </c>
-      <c r="O27" s="104" t="s">
+      <c r="O27" s="96" t="s">
         <v>152</v>
       </c>
-      <c r="P27" s="97">
+      <c r="P27" s="89">
         <v>6.9999999999999999E-4</v>
       </c>
-      <c r="Q27" s="93">
-        <f>P27*N27</f>
+      <c r="Q27" s="85">
+        <f t="shared" si="0"/>
         <v>6.9999999999999993E-2</v>
       </c>
       <c r="R27" s="41"/>
@@ -3260,67 +3352,67 @@
     </row>
     <row r="28" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A28" s="1"/>
-      <c r="B28" s="61">
+      <c r="B28" s="55">
+        <f t="shared" si="1"/>
+        <v>19</v>
+      </c>
+      <c r="C28" s="62" t="s">
+        <v>166</v>
+      </c>
+      <c r="D28" s="64" t="s">
+        <v>28</v>
+      </c>
+      <c r="E28" s="50" t="s">
+        <v>59</v>
+      </c>
+      <c r="F28" s="64" t="s">
+        <v>82</v>
+      </c>
+      <c r="G28" s="50" t="s">
+        <v>107</v>
+      </c>
+      <c r="H28" s="64" t="s">
+        <v>114</v>
+      </c>
+      <c r="I28" s="50" t="s">
+        <v>176</v>
+      </c>
+      <c r="J28" s="72" t="s">
+        <v>183</v>
+      </c>
+      <c r="K28" s="50" t="s">
+        <v>142</v>
+      </c>
+      <c r="L28" s="64">
+        <v>3</v>
+      </c>
+      <c r="M28" s="50">
+        <f t="shared" si="2"/>
+        <v>60</v>
+      </c>
+      <c r="N28" s="64">
+        <v>100</v>
+      </c>
+      <c r="O28" s="83" t="s">
+        <v>152</v>
+      </c>
+      <c r="P28" s="90">
+        <v>1E-3</v>
+      </c>
+      <c r="Q28" s="86">
         <f t="shared" si="0"/>
-        <v>19</v>
-      </c>
-      <c r="C28" s="70" t="s">
-        <v>166</v>
-      </c>
-      <c r="D28" s="72" t="s">
-        <v>28</v>
-      </c>
-      <c r="E28" s="56" t="s">
-        <v>59</v>
-      </c>
-      <c r="F28" s="72" t="s">
-        <v>82</v>
-      </c>
-      <c r="G28" s="56" t="s">
-        <v>107</v>
-      </c>
-      <c r="H28" s="72" t="s">
-        <v>114</v>
-      </c>
-      <c r="I28" s="56" t="s">
-        <v>176</v>
-      </c>
-      <c r="J28" s="80" t="s">
-        <v>183</v>
-      </c>
-      <c r="K28" s="56" t="s">
-        <v>142</v>
-      </c>
-      <c r="L28" s="72">
-        <v>3</v>
-      </c>
-      <c r="M28" s="56">
-        <f t="shared" si="1"/>
-        <v>60</v>
-      </c>
-      <c r="N28" s="72">
-        <v>100</v>
-      </c>
-      <c r="O28" s="91" t="s">
-        <v>152</v>
-      </c>
-      <c r="P28" s="98">
-        <v>1E-3</v>
-      </c>
-      <c r="Q28" s="94">
-        <f>P28*N28</f>
         <v>0.1</v>
       </c>
-      <c r="R28" s="72"/>
-      <c r="S28" s="100"/>
+      <c r="R28" s="64"/>
+      <c r="S28" s="92"/>
     </row>
     <row r="29" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A29" s="1"/>
-      <c r="B29" s="61">
+      <c r="B29" s="55">
         <f>ROW(B29) - ROW($B$9)</f>
         <v>20</v>
       </c>
-      <c r="C29" s="59" t="s">
+      <c r="C29" s="53" t="s">
         <v>166</v>
       </c>
       <c r="D29" s="41" t="s">
@@ -3341,7 +3433,7 @@
       <c r="I29" s="40" t="s">
         <v>176</v>
       </c>
-      <c r="J29" s="83" t="s">
+      <c r="J29" s="75" t="s">
         <v>184</v>
       </c>
       <c r="K29" s="40" t="s">
@@ -3351,20 +3443,20 @@
         <v>2</v>
       </c>
       <c r="M29" s="40">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>40</v>
       </c>
       <c r="N29" s="41">
         <v>100</v>
       </c>
-      <c r="O29" s="92" t="s">
+      <c r="O29" s="84" t="s">
         <v>152</v>
       </c>
-      <c r="P29" s="97">
+      <c r="P29" s="89">
         <v>1E-3</v>
       </c>
-      <c r="Q29" s="93">
-        <f>P29*N29</f>
+      <c r="Q29" s="85">
+        <f t="shared" si="0"/>
         <v>0.1</v>
       </c>
       <c r="R29" s="41"/>
@@ -3372,67 +3464,67 @@
     </row>
     <row r="30" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A30" s="1"/>
-      <c r="B30" s="61">
+      <c r="B30" s="55">
+        <f t="shared" si="1"/>
+        <v>21</v>
+      </c>
+      <c r="C30" s="62" t="s">
+        <v>166</v>
+      </c>
+      <c r="D30" s="64" t="s">
+        <v>30</v>
+      </c>
+      <c r="E30" s="50" t="s">
+        <v>61</v>
+      </c>
+      <c r="F30" s="64" t="s">
+        <v>82</v>
+      </c>
+      <c r="G30" s="50" t="s">
+        <v>109</v>
+      </c>
+      <c r="H30" s="64" t="s">
+        <v>114</v>
+      </c>
+      <c r="I30" s="50" t="s">
+        <v>176</v>
+      </c>
+      <c r="J30" s="72" t="s">
+        <v>198</v>
+      </c>
+      <c r="K30" s="50" t="s">
+        <v>144</v>
+      </c>
+      <c r="L30" s="64">
+        <v>1</v>
+      </c>
+      <c r="M30" s="50">
+        <f t="shared" si="2"/>
+        <v>20</v>
+      </c>
+      <c r="N30" s="64">
+        <v>100</v>
+      </c>
+      <c r="O30" s="94" t="s">
+        <v>152</v>
+      </c>
+      <c r="P30" s="90">
+        <v>1E-3</v>
+      </c>
+      <c r="Q30" s="86">
         <f t="shared" si="0"/>
-        <v>21</v>
-      </c>
-      <c r="C30" s="70" t="s">
-        <v>166</v>
-      </c>
-      <c r="D30" s="72" t="s">
-        <v>30</v>
-      </c>
-      <c r="E30" s="56" t="s">
-        <v>61</v>
-      </c>
-      <c r="F30" s="72" t="s">
-        <v>82</v>
-      </c>
-      <c r="G30" s="56" t="s">
-        <v>109</v>
-      </c>
-      <c r="H30" s="72" t="s">
-        <v>114</v>
-      </c>
-      <c r="I30" s="56" t="s">
-        <v>176</v>
-      </c>
-      <c r="J30" s="80" t="s">
-        <v>198</v>
-      </c>
-      <c r="K30" s="56" t="s">
-        <v>144</v>
-      </c>
-      <c r="L30" s="72">
-        <v>1</v>
-      </c>
-      <c r="M30" s="56">
-        <f t="shared" si="1"/>
-        <v>20</v>
-      </c>
-      <c r="N30" s="72">
-        <v>100</v>
-      </c>
-      <c r="O30" s="102" t="s">
-        <v>152</v>
-      </c>
-      <c r="P30" s="98">
-        <v>1E-3</v>
-      </c>
-      <c r="Q30" s="94">
-        <f>P30*N30</f>
         <v>0.1</v>
       </c>
-      <c r="R30" s="72"/>
-      <c r="S30" s="100"/>
+      <c r="R30" s="64"/>
+      <c r="S30" s="92"/>
     </row>
     <row r="31" spans="1:19" ht="108.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A31" s="1"/>
-      <c r="B31" s="61">
+      <c r="B31" s="55">
         <f>ROW(B31) - ROW($B$9)</f>
         <v>22</v>
       </c>
-      <c r="C31" s="59" t="s">
+      <c r="C31" s="53" t="s">
         <v>167</v>
       </c>
       <c r="D31" s="41" t="s">
@@ -3463,91 +3555,91 @@
         <v>48</v>
       </c>
       <c r="M31" s="40">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>960</v>
       </c>
       <c r="N31" s="41" t="s">
         <v>176</v>
       </c>
-      <c r="O31" s="57" t="s">
-        <v>176</v>
-      </c>
-      <c r="P31" s="97" t="s">
-        <v>176</v>
-      </c>
-      <c r="Q31" s="93" t="s">
+      <c r="O31" s="51" t="s">
+        <v>176</v>
+      </c>
+      <c r="P31" s="89" t="s">
+        <v>176</v>
+      </c>
+      <c r="Q31" s="85" t="s">
         <v>176</v>
       </c>
       <c r="R31" s="41" t="s">
         <v>176</v>
       </c>
-      <c r="S31" s="60" t="s">
+      <c r="S31" s="54" t="s">
         <v>176</v>
       </c>
     </row>
     <row r="32" spans="1:19" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A32" s="1"/>
-      <c r="B32" s="61">
-        <f t="shared" si="0"/>
+      <c r="B32" s="55">
+        <f t="shared" si="1"/>
         <v>23</v>
       </c>
-      <c r="C32" s="70" t="s">
+      <c r="C32" s="62" t="s">
         <v>168</v>
       </c>
-      <c r="D32" s="72" t="s">
+      <c r="D32" s="64" t="s">
         <v>32</v>
       </c>
-      <c r="E32" s="56" t="s">
+      <c r="E32" s="50" t="s">
         <v>63</v>
       </c>
-      <c r="F32" s="72" t="s">
+      <c r="F32" s="64" t="s">
         <v>175</v>
       </c>
-      <c r="G32" s="77" t="s">
+      <c r="G32" s="69" t="s">
         <v>84</v>
       </c>
-      <c r="H32" s="72" t="s">
+      <c r="H32" s="64" t="s">
         <v>120</v>
       </c>
-      <c r="I32" s="56" t="s">
-        <v>176</v>
-      </c>
-      <c r="J32" s="80" t="s">
+      <c r="I32" s="50" t="s">
+        <v>176</v>
+      </c>
+      <c r="J32" s="72" t="s">
         <v>174</v>
       </c>
-      <c r="K32" s="56" t="s">
-        <v>176</v>
-      </c>
-      <c r="L32" s="72">
+      <c r="K32" s="50" t="s">
+        <v>176</v>
+      </c>
+      <c r="L32" s="64">
         <v>1</v>
       </c>
-      <c r="M32" s="56">
-        <f t="shared" si="1"/>
+      <c r="M32" s="50">
+        <f t="shared" si="2"/>
         <v>20</v>
       </c>
-      <c r="N32" s="72">
+      <c r="N32" s="64">
         <v>30</v>
       </c>
-      <c r="O32" s="102" t="s">
+      <c r="O32" s="94" t="s">
         <v>152</v>
       </c>
-      <c r="P32" s="98">
+      <c r="P32" s="90">
         <v>5.8200000000000002E-2</v>
       </c>
-      <c r="Q32" s="94">
-        <f>P32*N32</f>
+      <c r="Q32" s="86">
+        <f t="shared" ref="Q32:Q39" si="3">P32*N32</f>
         <v>1.746</v>
       </c>
-      <c r="R32" s="72"/>
-      <c r="S32" s="100"/>
+      <c r="R32" s="64"/>
+      <c r="S32" s="92"/>
     </row>
     <row r="33" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A33" s="1"/>
-      <c r="B33" s="61">
+      <c r="B33" s="55">
         <f>ROW(B33) - ROW($B$9)</f>
         <v>24</v>
       </c>
-      <c r="C33" s="59" t="s">
+      <c r="C33" s="53" t="s">
         <v>9</v>
       </c>
       <c r="D33" s="41" t="s">
@@ -3578,20 +3670,20 @@
         <v>1</v>
       </c>
       <c r="M33" s="40">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>20</v>
       </c>
       <c r="N33" s="41">
         <v>22</v>
       </c>
-      <c r="O33" s="88" t="s">
+      <c r="O33" s="80" t="s">
         <v>152</v>
       </c>
-      <c r="P33" s="97">
+      <c r="P33" s="89">
         <v>3.99</v>
       </c>
-      <c r="Q33" s="93">
-        <f>P33*N33</f>
+      <c r="Q33" s="85">
+        <f t="shared" si="3"/>
         <v>87.78</v>
       </c>
       <c r="R33" s="41"/>
@@ -3599,167 +3691,181 @@
     </row>
     <row r="34" spans="1:19" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A34" s="1"/>
-      <c r="B34" s="61">
-        <f t="shared" si="0"/>
+      <c r="B34" s="55">
+        <f t="shared" si="1"/>
         <v>25</v>
       </c>
-      <c r="C34" s="70" t="s">
+      <c r="C34" s="62" t="s">
         <v>169</v>
       </c>
-      <c r="D34" s="72" t="s">
+      <c r="D34" s="64" t="s">
         <v>34</v>
       </c>
-      <c r="E34" s="56" t="s">
+      <c r="E34" s="50" t="s">
         <v>65</v>
       </c>
-      <c r="F34" s="72" t="s">
+      <c r="F34" s="64" t="s">
         <v>86</v>
       </c>
-      <c r="G34" s="56" t="s">
+      <c r="G34" s="50" t="s">
         <v>110</v>
       </c>
-      <c r="H34" s="72" t="s">
+      <c r="H34" s="64" t="s">
         <v>124</v>
       </c>
-      <c r="I34" s="56" t="s">
-        <v>176</v>
-      </c>
-      <c r="J34" s="84" t="s">
+      <c r="I34" s="50" t="s">
+        <v>176</v>
+      </c>
+      <c r="J34" s="76" t="s">
         <v>179</v>
       </c>
-      <c r="K34" s="56" t="s">
-        <v>176</v>
-      </c>
-      <c r="L34" s="72">
+      <c r="K34" s="50" t="s">
+        <v>176</v>
+      </c>
+      <c r="L34" s="64">
         <v>1</v>
       </c>
-      <c r="M34" s="56">
-        <f t="shared" si="1"/>
+      <c r="M34" s="50">
+        <f t="shared" si="2"/>
         <v>20</v>
       </c>
-      <c r="N34" s="72">
+      <c r="N34" s="64">
         <v>22</v>
       </c>
-      <c r="O34" s="102" t="s">
+      <c r="O34" s="94" t="s">
         <v>152</v>
       </c>
-      <c r="P34" s="98">
+      <c r="P34" s="90">
         <v>0.42</v>
       </c>
-      <c r="Q34" s="94">
-        <f>P34*N34</f>
+      <c r="Q34" s="86">
+        <f t="shared" si="3"/>
         <v>9.24</v>
       </c>
-      <c r="R34" s="72"/>
-      <c r="S34" s="100"/>
+      <c r="R34" s="64"/>
+      <c r="S34" s="92"/>
     </row>
     <row r="35" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A35" s="1"/>
-      <c r="B35" s="61">
+      <c r="B35" s="55">
         <f>ROW(B35) - ROW($B$9)</f>
         <v>26</v>
       </c>
-      <c r="C35" s="59" t="s">
+      <c r="C35" s="139" t="s">
         <v>169</v>
       </c>
-      <c r="D35" s="41" t="s">
+      <c r="D35" s="140" t="s">
         <v>35</v>
       </c>
-      <c r="E35" s="40" t="s">
+      <c r="E35" s="108" t="s">
         <v>66</v>
       </c>
-      <c r="F35" s="41" t="s">
+      <c r="F35" s="140" t="s">
         <v>87</v>
       </c>
-      <c r="G35" s="40" t="s">
+      <c r="G35" s="108" t="s">
         <v>111</v>
       </c>
-      <c r="H35" s="41" t="s">
+      <c r="H35" s="140" t="s">
         <v>118</v>
       </c>
-      <c r="I35" s="40"/>
-      <c r="J35" s="41"/>
-      <c r="K35" s="40"/>
-      <c r="L35" s="41">
+      <c r="I35" s="108" t="s">
+        <v>176</v>
+      </c>
+      <c r="J35" s="140" t="s">
+        <v>176</v>
+      </c>
+      <c r="K35" s="108" t="s">
+        <v>176</v>
+      </c>
+      <c r="L35" s="140">
         <v>1</v>
       </c>
-      <c r="M35" s="40">
-        <f t="shared" si="1"/>
+      <c r="M35" s="108">
+        <f t="shared" si="2"/>
         <v>20</v>
       </c>
-      <c r="N35" s="41"/>
-      <c r="O35" s="57"/>
-      <c r="P35" s="97"/>
-      <c r="Q35" s="93">
-        <f>P35*N35</f>
-        <v>0</v>
-      </c>
-      <c r="R35" s="41"/>
+      <c r="N35" s="140">
+        <v>22</v>
+      </c>
+      <c r="O35" s="80" t="s">
+        <v>211</v>
+      </c>
+      <c r="P35" s="141">
+        <v>18.649999999999999</v>
+      </c>
+      <c r="Q35" s="142">
+        <f t="shared" si="3"/>
+        <v>410.29999999999995</v>
+      </c>
+      <c r="R35" s="136" t="s">
+        <v>214</v>
+      </c>
       <c r="S35" s="44"/>
     </row>
     <row r="36" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A36" s="1"/>
-      <c r="B36" s="61">
-        <f t="shared" si="0"/>
+      <c r="B36" s="55">
+        <f t="shared" si="1"/>
         <v>27</v>
       </c>
-      <c r="C36" s="70" t="s">
+      <c r="C36" s="62" t="s">
         <v>169</v>
       </c>
-      <c r="D36" s="72" t="s">
+      <c r="D36" s="64" t="s">
         <v>36</v>
       </c>
-      <c r="E36" s="56" t="s">
+      <c r="E36" s="50" t="s">
         <v>67</v>
       </c>
-      <c r="F36" s="72" t="s">
+      <c r="F36" s="64" t="s">
         <v>186</v>
       </c>
-      <c r="G36" s="56" t="s">
+      <c r="G36" s="50" t="s">
         <v>88</v>
       </c>
-      <c r="H36" s="72" t="s">
+      <c r="H36" s="64" t="s">
         <v>118</v>
       </c>
-      <c r="I36" s="56" t="s">
-        <v>176</v>
-      </c>
-      <c r="J36" s="80" t="s">
+      <c r="I36" s="50" t="s">
+        <v>176</v>
+      </c>
+      <c r="J36" s="72" t="s">
         <v>199</v>
       </c>
-      <c r="K36" s="56" t="s">
-        <v>176</v>
-      </c>
-      <c r="L36" s="72">
+      <c r="K36" s="50" t="s">
+        <v>176</v>
+      </c>
+      <c r="L36" s="64">
         <v>2</v>
       </c>
-      <c r="M36" s="56">
-        <f t="shared" si="1"/>
+      <c r="M36" s="50">
+        <f t="shared" si="2"/>
         <v>40</v>
       </c>
-      <c r="N36" s="72">
-        <v>45</v>
-      </c>
-      <c r="O36" s="102" t="s">
+      <c r="N36" s="64">
+        <v>44</v>
+      </c>
+      <c r="O36" s="143" t="s">
         <v>152</v>
       </c>
-      <c r="P36" s="98">
+      <c r="P36" s="90">
         <v>3.2374999999999998</v>
       </c>
-      <c r="Q36" s="94">
-        <f>P36*N36</f>
-        <v>145.6875</v>
-      </c>
-      <c r="R36" s="72"/>
-      <c r="S36" s="100"/>
+      <c r="Q36" s="144">
+        <f t="shared" si="3"/>
+        <v>142.44999999999999</v>
+      </c>
+      <c r="R36" s="64"/>
+      <c r="S36" s="92"/>
     </row>
     <row r="37" spans="1:19" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A37" s="1"/>
-      <c r="B37" s="61">
+      <c r="B37" s="55">
         <f>ROW(B37) - ROW($B$9)</f>
         <v>28</v>
       </c>
-      <c r="C37" s="59" t="s">
+      <c r="C37" s="53" t="s">
         <v>169</v>
       </c>
       <c r="D37" s="41" t="s">
@@ -3780,7 +3886,7 @@
       <c r="I37" s="40" t="s">
         <v>176</v>
       </c>
-      <c r="J37" s="85" t="s">
+      <c r="J37" s="77" t="s">
         <v>180</v>
       </c>
       <c r="K37" s="40" t="s">
@@ -3790,20 +3896,20 @@
         <v>1</v>
       </c>
       <c r="M37" s="40">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>20</v>
       </c>
       <c r="N37" s="41">
         <v>30</v>
       </c>
-      <c r="O37" s="88" t="s">
+      <c r="O37" s="80" t="s">
         <v>152</v>
       </c>
-      <c r="P37" s="97">
+      <c r="P37" s="89">
         <v>5.67E-2</v>
       </c>
-      <c r="Q37" s="93">
-        <f>P37*N37</f>
+      <c r="Q37" s="85">
+        <f t="shared" si="3"/>
         <v>1.7010000000000001</v>
       </c>
       <c r="R37" s="41"/>
@@ -3811,137 +3917,141 @@
     </row>
     <row r="38" spans="1:19" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A38" s="1"/>
-      <c r="B38" s="61">
-        <f t="shared" si="0"/>
+      <c r="B38" s="55">
+        <f t="shared" si="1"/>
         <v>29</v>
       </c>
-      <c r="C38" s="70" t="s">
+      <c r="C38" s="62" t="s">
         <v>170</v>
       </c>
-      <c r="D38" s="72" t="s">
+      <c r="D38" s="64" t="s">
         <v>38</v>
       </c>
-      <c r="E38" s="56" t="s">
+      <c r="E38" s="50" t="s">
         <v>69</v>
       </c>
-      <c r="F38" s="72" t="s">
+      <c r="F38" s="64" t="s">
         <v>175</v>
       </c>
-      <c r="G38" s="56" t="s">
+      <c r="G38" s="50" t="s">
         <v>90</v>
       </c>
-      <c r="H38" s="72" t="s">
+      <c r="H38" s="64" t="s">
         <v>126</v>
       </c>
-      <c r="I38" s="56"/>
-      <c r="J38" s="86" t="s">
+      <c r="I38" s="50" t="s">
+        <v>176</v>
+      </c>
+      <c r="J38" s="78" t="s">
         <v>177</v>
       </c>
-      <c r="K38" s="56" t="s">
+      <c r="K38" s="50" t="s">
         <v>187</v>
       </c>
-      <c r="L38" s="72">
+      <c r="L38" s="64">
         <v>1</v>
       </c>
-      <c r="M38" s="56">
-        <f t="shared" si="1"/>
+      <c r="M38" s="50">
+        <f t="shared" si="2"/>
         <v>20</v>
       </c>
-      <c r="N38" s="72">
+      <c r="N38" s="64">
         <v>22</v>
       </c>
-      <c r="O38" s="102" t="s">
+      <c r="O38" s="94" t="s">
         <v>152</v>
       </c>
-      <c r="P38" s="98">
+      <c r="P38" s="90">
         <v>0.15179999999999999</v>
       </c>
-      <c r="Q38" s="94">
-        <f>P38*N38</f>
+      <c r="Q38" s="86">
+        <f t="shared" si="3"/>
         <v>3.3395999999999999</v>
       </c>
-      <c r="R38" s="72"/>
-      <c r="S38" s="100"/>
+      <c r="R38" s="64"/>
+      <c r="S38" s="92"/>
     </row>
     <row r="39" spans="1:19" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A39" s="1"/>
-      <c r="B39" s="61">
+      <c r="B39" s="55">
         <f>ROW(B39) - ROW($B$9)</f>
         <v>30</v>
       </c>
-      <c r="C39" s="71" t="s">
+      <c r="C39" s="63" t="s">
         <v>170</v>
       </c>
-      <c r="D39" s="75" t="s">
+      <c r="D39" s="67" t="s">
         <v>39</v>
       </c>
-      <c r="E39" s="73" t="s">
+      <c r="E39" s="65" t="s">
         <v>70</v>
       </c>
-      <c r="F39" s="75" t="s">
+      <c r="F39" s="67" t="s">
         <v>175</v>
       </c>
-      <c r="G39" s="73" t="s">
+      <c r="G39" s="65" t="s">
         <v>91</v>
       </c>
-      <c r="H39" s="75" t="s">
+      <c r="H39" s="67" t="s">
         <v>127</v>
       </c>
-      <c r="I39" s="73"/>
-      <c r="J39" s="87" t="s">
+      <c r="I39" s="65" t="s">
+        <v>176</v>
+      </c>
+      <c r="J39" s="79" t="s">
         <v>178</v>
       </c>
-      <c r="K39" s="73" t="s">
+      <c r="K39" s="65" t="s">
         <v>188</v>
       </c>
-      <c r="L39" s="75">
+      <c r="L39" s="67">
         <v>2</v>
       </c>
-      <c r="M39" s="73">
-        <f t="shared" si="1"/>
+      <c r="M39" s="65">
+        <f t="shared" si="2"/>
         <v>40</v>
       </c>
-      <c r="N39" s="75">
+      <c r="N39" s="67">
         <v>45</v>
       </c>
-      <c r="O39" s="115" t="s">
+      <c r="O39" s="107" t="s">
         <v>152</v>
       </c>
-      <c r="P39" s="99">
+      <c r="P39" s="91">
         <v>7.4099999999999999E-2</v>
       </c>
-      <c r="Q39" s="95">
-        <f>P39*N39</f>
+      <c r="Q39" s="87">
+        <f t="shared" si="3"/>
         <v>3.3344999999999998</v>
       </c>
-      <c r="R39" s="75"/>
-      <c r="S39" s="101"/>
+      <c r="R39" s="67"/>
+      <c r="S39" s="93"/>
     </row>
     <row r="40" spans="1:19" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A40" s="1"/>
-      <c r="B40" s="74"/>
-      <c r="C40" s="62"/>
-      <c r="D40" s="63"/>
-      <c r="E40" s="64"/>
-      <c r="F40" s="65"/>
-      <c r="G40" s="66"/>
-      <c r="H40" s="65"/>
-      <c r="I40" s="66"/>
-      <c r="J40" s="65"/>
-      <c r="K40" s="66"/>
-      <c r="L40" s="66"/>
-      <c r="M40" s="66"/>
+      <c r="B40" s="66"/>
+      <c r="C40" s="56"/>
+      <c r="D40" s="57"/>
+      <c r="E40" s="58"/>
+      <c r="F40" s="59"/>
+      <c r="G40" s="60"/>
+      <c r="H40" s="59"/>
+      <c r="I40" s="60"/>
+      <c r="J40" s="59"/>
+      <c r="K40" s="60"/>
+      <c r="L40" s="60"/>
+      <c r="M40" s="60"/>
       <c r="N40" s="134" t="s">
         <v>209</v>
       </c>
       <c r="O40" s="135"/>
       <c r="P40" s="135"/>
-      <c r="Q40" s="136" t="e">
-        <f>SUM(#REF!)</f>
-        <v>#REF!</v>
-      </c>
-      <c r="R40" s="67"/>
-      <c r="S40" s="68"/>
+      <c r="Q40" s="124">
+        <f>SUM(Q10:Q39)</f>
+        <v>1169.7855999999999</v>
+      </c>
+      <c r="R40" s="130"/>
+      <c r="S40" s="131"/>
     </row>
     <row r="41" spans="1:19" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A41" s="1"/>
@@ -3962,12 +4072,12 @@
       </c>
       <c r="O41" s="135"/>
       <c r="P41" s="135"/>
-      <c r="Q41" s="137" t="e">
-        <f>Q40/5</f>
-        <v>#REF!</v>
-      </c>
-      <c r="R41" s="53"/>
-      <c r="S41" s="54"/>
+      <c r="Q41" s="125">
+        <f>Q40/20</f>
+        <v>58.489279999999994</v>
+      </c>
+      <c r="R41" s="132"/>
+      <c r="S41" s="133"/>
     </row>
   </sheetData>
   <mergeCells count="5">
@@ -3977,7 +4087,7 @@
     <mergeCell ref="N40:P40"/>
     <mergeCell ref="N41:P41"/>
   </mergeCells>
-  <conditionalFormatting sqref="O13 O25 O31 O33 O35 O15 O17 O19">
+  <conditionalFormatting sqref="O13 O31 O33 O15 O17 O19 O35">
     <cfRule type="dataBar" priority="5">
       <dataBar>
         <cfvo type="min"/>
@@ -4093,7 +4203,7 @@
               <x14:axisColor rgb="FF000000"/>
             </x14:dataBar>
           </x14:cfRule>
-          <xm:sqref>O13 O25 O31 O33 O35 O15 O17 O19</xm:sqref>
+          <xm:sqref>O13 O31 O33 O15 O17 O19 O35</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
           <x14:cfRule type="dataBar" id="{5E155581-B981-4F73-BB54-C6503AC77979}">
@@ -4155,7 +4265,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0C782E35-1BDF-4DFF-9BFC-645AE3AAA1FF}">
-  <dimension ref="A1:S41"/>
+  <dimension ref="A1:S43"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="3" bestFit="1" customWidth="1"/>
@@ -4171,8 +4281,10 @@
     <col min="12" max="12" width="8.7109375" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="21.42578125" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="18.28515625" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="15.7109375" bestFit="1" customWidth="1"/>
     <col min="16" max="16" width="21.85546875" bestFit="1" customWidth="1"/>
     <col min="17" max="17" width="22.42578125" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="11.42578125" customWidth="1"/>
     <col min="19" max="19" width="26.85546875" customWidth="1"/>
   </cols>
   <sheetData>
@@ -4187,15 +4299,15 @@
       <c r="H1" s="2"/>
       <c r="I1" s="2"/>
       <c r="J1" s="2"/>
-      <c r="K1" s="49"/>
-      <c r="L1" s="49"/>
-      <c r="M1" s="49"/>
-      <c r="N1" s="49"/>
-      <c r="O1" s="49"/>
-      <c r="P1" s="49"/>
-      <c r="Q1" s="49"/>
-      <c r="R1" s="49"/>
-      <c r="S1" s="50"/>
+      <c r="K1" s="126"/>
+      <c r="L1" s="126"/>
+      <c r="M1" s="126"/>
+      <c r="N1" s="126"/>
+      <c r="O1" s="126"/>
+      <c r="P1" s="126"/>
+      <c r="Q1" s="126"/>
+      <c r="R1" s="126"/>
+      <c r="S1" s="127"/>
     </row>
     <row r="2" spans="1:19" ht="32.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1"/>
@@ -4245,7 +4357,7 @@
       <c r="P3" s="5"/>
       <c r="Q3" s="5"/>
       <c r="R3" s="5"/>
-      <c r="S3" s="51"/>
+      <c r="S3" s="128"/>
     </row>
     <row r="4" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A4" s="1"/>
@@ -4270,7 +4382,7 @@
       <c r="P4" s="6"/>
       <c r="Q4" s="6"/>
       <c r="R4" s="6"/>
-      <c r="S4" s="52"/>
+      <c r="S4" s="129"/>
     </row>
     <row r="5" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A5" s="1"/>
@@ -4295,7 +4407,7 @@
       <c r="P5" s="6"/>
       <c r="Q5" s="6"/>
       <c r="R5" s="6"/>
-      <c r="S5" s="52"/>
+      <c r="S5" s="129"/>
     </row>
     <row r="6" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A6" s="1"/>
@@ -4316,7 +4428,7 @@
       <c r="P6" s="6"/>
       <c r="Q6" s="6"/>
       <c r="R6" s="6"/>
-      <c r="S6" s="52"/>
+      <c r="S6" s="129"/>
     </row>
     <row r="7" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A7" s="1"/>
@@ -4337,7 +4449,7 @@
       <c r="P7" s="8"/>
       <c r="Q7" s="8"/>
       <c r="R7" s="8"/>
-      <c r="S7" s="52"/>
+      <c r="S7" s="129"/>
     </row>
     <row r="8" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" s="1"/>
@@ -4358,11 +4470,11 @@
       <c r="P8" s="8"/>
       <c r="Q8" s="8"/>
       <c r="R8" s="8"/>
-      <c r="S8" s="52"/>
+      <c r="S8" s="129"/>
     </row>
     <row r="9" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A9" s="1"/>
-      <c r="B9" s="55" t="s">
+      <c r="B9" s="49" t="s">
         <v>4</v>
       </c>
       <c r="C9" s="30" t="s">
@@ -4419,11 +4531,11 @@
     </row>
     <row r="10" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A10" s="1"/>
-      <c r="B10" s="69">
+      <c r="B10" s="61">
         <f>ROW(B10) - ROW($B$9)</f>
         <v>1</v>
       </c>
-      <c r="C10" s="58" t="s">
+      <c r="C10" s="52" t="s">
         <v>7</v>
       </c>
       <c r="D10" s="39" t="s">
@@ -4444,7 +4556,7 @@
       <c r="I10" s="38" t="s">
         <v>176</v>
       </c>
-      <c r="J10" s="79" t="s">
+      <c r="J10" s="71" t="s">
         <v>146</v>
       </c>
       <c r="K10" s="38" t="s">
@@ -4457,25 +4569,29 @@
         <f>L10*1000</f>
         <v>1000</v>
       </c>
-      <c r="N10" s="39"/>
-      <c r="O10" s="102" t="s">
+      <c r="N10" s="39">
+        <v>1060</v>
+      </c>
+      <c r="O10" s="94" t="s">
         <v>152</v>
       </c>
-      <c r="P10" s="96"/>
+      <c r="P10" s="88">
+        <v>1.17E-2</v>
+      </c>
       <c r="Q10" s="42">
-        <f>P10*N10</f>
-        <v>0</v>
+        <f t="shared" ref="Q10:Q30" si="0">P10*N10</f>
+        <v>12.402000000000001</v>
       </c>
       <c r="R10" s="39"/>
       <c r="S10" s="43"/>
     </row>
     <row r="11" spans="1:19" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A11" s="1"/>
-      <c r="B11" s="61">
-        <f t="shared" ref="B11:B38" si="0">ROW(B11) - ROW($B$9)</f>
+      <c r="B11" s="55">
+        <f t="shared" ref="B11:B38" si="1">ROW(B11) - ROW($B$9)</f>
         <v>2</v>
       </c>
-      <c r="C11" s="59" t="s">
+      <c r="C11" s="53" t="s">
         <v>7</v>
       </c>
       <c r="D11" s="41" t="s">
@@ -4506,80 +4622,88 @@
         <v>17</v>
       </c>
       <c r="M11" s="40">
-        <f t="shared" ref="M11:M39" si="1">L11*1000</f>
+        <f t="shared" ref="M11:M39" si="2">L11*1000</f>
         <v>17000</v>
       </c>
-      <c r="N11" s="41"/>
-      <c r="O11" s="88" t="s">
+      <c r="N11" s="41">
+        <v>17100</v>
+      </c>
+      <c r="O11" s="80" t="s">
         <v>152</v>
       </c>
-      <c r="P11" s="97"/>
-      <c r="Q11" s="93">
-        <f>P11*N11</f>
-        <v>0</v>
+      <c r="P11" s="89">
+        <v>2.8999999999999998E-3</v>
+      </c>
+      <c r="Q11" s="85">
+        <f t="shared" si="0"/>
+        <v>49.589999999999996</v>
       </c>
       <c r="R11" s="41"/>
       <c r="S11" s="44"/>
     </row>
-    <row r="12" spans="1:19" s="109" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="106"/>
-      <c r="B12" s="61">
+    <row r="12" spans="1:19" s="101" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="98"/>
+      <c r="B12" s="55">
         <f>ROW(B12) - ROW($B$9)</f>
         <v>3</v>
       </c>
-      <c r="C12" s="70" t="s">
+      <c r="C12" s="62" t="s">
         <v>7</v>
       </c>
-      <c r="D12" s="72" t="s">
+      <c r="D12" s="64" t="s">
         <v>13</v>
       </c>
-      <c r="E12" s="56" t="s">
+      <c r="E12" s="50" t="s">
         <v>43</v>
       </c>
-      <c r="F12" s="72" t="s">
+      <c r="F12" s="64" t="s">
         <v>73</v>
       </c>
-      <c r="G12" s="56" t="s">
+      <c r="G12" s="50" t="s">
         <v>95</v>
       </c>
-      <c r="H12" s="72" t="s">
+      <c r="H12" s="64" t="s">
         <v>114</v>
       </c>
-      <c r="I12" s="56" t="s">
-        <v>176</v>
-      </c>
-      <c r="J12" s="80" t="s">
+      <c r="I12" s="50" t="s">
+        <v>176</v>
+      </c>
+      <c r="J12" s="72" t="s">
         <v>154</v>
       </c>
-      <c r="K12" s="56" t="s">
+      <c r="K12" s="50" t="s">
         <v>133</v>
       </c>
-      <c r="L12" s="72">
+      <c r="L12" s="64">
         <v>8</v>
       </c>
-      <c r="M12" s="56">
-        <f t="shared" si="1"/>
+      <c r="M12" s="50">
+        <f t="shared" si="2"/>
         <v>8000</v>
       </c>
-      <c r="N12" s="72"/>
-      <c r="O12" s="102" t="s">
+      <c r="N12" s="64">
+        <v>8100</v>
+      </c>
+      <c r="O12" s="94" t="s">
         <v>152</v>
       </c>
-      <c r="P12" s="98"/>
-      <c r="Q12" s="107">
-        <f>P12*N12</f>
-        <v>0</v>
-      </c>
-      <c r="R12" s="72"/>
-      <c r="S12" s="108"/>
+      <c r="P12" s="90">
+        <v>1.6999999999999999E-3</v>
+      </c>
+      <c r="Q12" s="99">
+        <f t="shared" si="0"/>
+        <v>13.77</v>
+      </c>
+      <c r="R12" s="64"/>
+      <c r="S12" s="100"/>
     </row>
     <row r="13" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A13" s="1"/>
-      <c r="B13" s="61">
-        <f t="shared" si="0"/>
+      <c r="B13" s="55">
+        <f t="shared" si="1"/>
         <v>4</v>
       </c>
-      <c r="C13" s="59" t="s">
+      <c r="C13" s="53" t="s">
         <v>7</v>
       </c>
       <c r="D13" s="41" t="s">
@@ -4610,80 +4734,88 @@
         <v>2</v>
       </c>
       <c r="M13" s="40">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>2000</v>
       </c>
-      <c r="N13" s="41"/>
-      <c r="O13" s="88" t="s">
+      <c r="N13" s="41">
+        <v>2100</v>
+      </c>
+      <c r="O13" s="80" t="s">
         <v>152</v>
       </c>
-      <c r="P13" s="97"/>
-      <c r="Q13" s="93">
-        <f>P13*N13</f>
-        <v>0</v>
+      <c r="P13" s="89">
+        <v>1.1661999999999999</v>
+      </c>
+      <c r="Q13" s="85">
+        <f t="shared" si="0"/>
+        <v>2449.02</v>
       </c>
       <c r="R13" s="41"/>
       <c r="S13" s="44"/>
     </row>
     <row r="14" spans="1:19" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A14" s="1"/>
-      <c r="B14" s="61">
+      <c r="B14" s="55">
         <f>ROW(B14) - ROW($B$9)</f>
         <v>5</v>
       </c>
-      <c r="C14" s="70" t="s">
+      <c r="C14" s="62" t="s">
         <v>7</v>
       </c>
-      <c r="D14" s="72" t="s">
+      <c r="D14" s="64" t="s">
         <v>15</v>
       </c>
-      <c r="E14" s="56" t="s">
+      <c r="E14" s="50" t="s">
         <v>45</v>
       </c>
-      <c r="F14" s="72" t="s">
+      <c r="F14" s="64" t="s">
         <v>72</v>
       </c>
-      <c r="G14" s="56" t="s">
+      <c r="G14" s="50" t="s">
         <v>97</v>
       </c>
-      <c r="H14" s="72" t="s">
+      <c r="H14" s="64" t="s">
         <v>114</v>
       </c>
-      <c r="I14" s="56" t="s">
-        <v>176</v>
-      </c>
-      <c r="J14" s="80" t="s">
+      <c r="I14" s="50" t="s">
+        <v>176</v>
+      </c>
+      <c r="J14" s="72" t="s">
         <v>155</v>
       </c>
-      <c r="K14" s="56" t="s">
+      <c r="K14" s="50" t="s">
         <v>135</v>
       </c>
-      <c r="L14" s="72">
+      <c r="L14" s="64">
         <v>12</v>
       </c>
-      <c r="M14" s="56">
+      <c r="M14" s="50">
+        <f t="shared" si="2"/>
+        <v>12000</v>
+      </c>
+      <c r="N14" s="64">
+        <v>12100</v>
+      </c>
+      <c r="O14" s="94" t="s">
+        <v>152</v>
+      </c>
+      <c r="P14" s="90">
+        <v>3.3999999999999998E-3</v>
+      </c>
+      <c r="Q14" s="86">
+        <f t="shared" si="0"/>
+        <v>41.14</v>
+      </c>
+      <c r="R14" s="64"/>
+      <c r="S14" s="92"/>
+    </row>
+    <row r="15" spans="1:19" s="101" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="98"/>
+      <c r="B15" s="55">
         <f t="shared" si="1"/>
-        <v>12000</v>
-      </c>
-      <c r="N14" s="72"/>
-      <c r="O14" s="102" t="s">
-        <v>152</v>
-      </c>
-      <c r="P14" s="98"/>
-      <c r="Q14" s="94">
-        <f>P14*N14</f>
-        <v>0</v>
-      </c>
-      <c r="R14" s="72"/>
-      <c r="S14" s="100"/>
-    </row>
-    <row r="15" spans="1:19" s="109" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="106"/>
-      <c r="B15" s="61">
-        <f t="shared" si="0"/>
         <v>6</v>
       </c>
-      <c r="C15" s="59" t="s">
+      <c r="C15" s="53" t="s">
         <v>7</v>
       </c>
       <c r="D15" s="41" t="s">
@@ -4714,80 +4846,88 @@
         <v>1</v>
       </c>
       <c r="M15" s="40">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>1000</v>
       </c>
-      <c r="N15" s="41"/>
-      <c r="O15" s="88" t="s">
+      <c r="N15" s="41">
+        <v>1050</v>
+      </c>
+      <c r="O15" s="80" t="s">
         <v>152</v>
       </c>
-      <c r="P15" s="97"/>
-      <c r="Q15" s="110">
-        <f>P15*N15</f>
-        <v>0</v>
+      <c r="P15" s="89">
+        <v>2.12E-2</v>
+      </c>
+      <c r="Q15" s="102">
+        <f t="shared" si="0"/>
+        <v>22.26</v>
       </c>
       <c r="R15" s="41"/>
-      <c r="S15" s="111"/>
+      <c r="S15" s="103"/>
     </row>
     <row r="16" spans="1:19" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A16" s="1"/>
-      <c r="B16" s="61">
+      <c r="B16" s="55">
         <f>ROW(B16) - ROW($B$9)</f>
         <v>7</v>
       </c>
-      <c r="C16" s="70" t="s">
+      <c r="C16" s="62" t="s">
         <v>7</v>
       </c>
-      <c r="D16" s="72" t="s">
+      <c r="D16" s="64" t="s">
         <v>17</v>
       </c>
-      <c r="E16" s="56" t="s">
+      <c r="E16" s="50" t="s">
         <v>47</v>
       </c>
-      <c r="F16" s="72" t="s">
+      <c r="F16" s="64" t="s">
         <v>72</v>
       </c>
-      <c r="G16" s="56" t="s">
+      <c r="G16" s="50" t="s">
         <v>99</v>
       </c>
-      <c r="H16" s="72" t="s">
+      <c r="H16" s="64" t="s">
         <v>114</v>
       </c>
-      <c r="I16" s="56" t="s">
-        <v>176</v>
-      </c>
-      <c r="J16" s="80" t="s">
+      <c r="I16" s="50" t="s">
+        <v>176</v>
+      </c>
+      <c r="J16" s="72" t="s">
         <v>157</v>
       </c>
-      <c r="K16" s="56" t="s">
+      <c r="K16" s="50" t="s">
         <v>137</v>
       </c>
-      <c r="L16" s="72">
+      <c r="L16" s="64">
         <v>6</v>
       </c>
-      <c r="M16" s="56">
+      <c r="M16" s="50">
+        <f t="shared" si="2"/>
+        <v>6000</v>
+      </c>
+      <c r="N16" s="64">
+        <v>6100</v>
+      </c>
+      <c r="O16" s="94" t="s">
+        <v>152</v>
+      </c>
+      <c r="P16" s="90">
+        <v>1.8E-3</v>
+      </c>
+      <c r="Q16" s="86">
+        <f t="shared" si="0"/>
+        <v>10.98</v>
+      </c>
+      <c r="R16" s="64"/>
+      <c r="S16" s="92"/>
+    </row>
+    <row r="17" spans="1:19" ht="51.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="1"/>
+      <c r="B17" s="55">
         <f t="shared" si="1"/>
-        <v>6000</v>
-      </c>
-      <c r="N16" s="72"/>
-      <c r="O16" s="102" t="s">
-        <v>152</v>
-      </c>
-      <c r="P16" s="98"/>
-      <c r="Q16" s="94">
-        <f>P16*N16</f>
-        <v>0</v>
-      </c>
-      <c r="R16" s="72"/>
-      <c r="S16" s="100"/>
-    </row>
-    <row r="17" spans="1:19" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="1"/>
-      <c r="B17" s="61">
-        <f t="shared" si="0"/>
         <v>8</v>
       </c>
-      <c r="C17" s="59" t="s">
+      <c r="C17" s="53" t="s">
         <v>7</v>
       </c>
       <c r="D17" s="41" t="s">
@@ -4818,80 +4958,90 @@
         <v>16</v>
       </c>
       <c r="M17" s="40">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>16000</v>
       </c>
-      <c r="N17" s="41"/>
-      <c r="O17" s="88" t="s">
+      <c r="N17" s="41">
+        <v>16100</v>
+      </c>
+      <c r="O17" s="80" t="s">
         <v>152</v>
       </c>
-      <c r="P17" s="97"/>
-      <c r="Q17" s="93">
-        <f>P17*N17</f>
-        <v>0</v>
-      </c>
-      <c r="R17" s="41"/>
+      <c r="P17" s="89">
+        <v>5.8999999999999999E-3</v>
+      </c>
+      <c r="Q17" s="85">
+        <f t="shared" si="0"/>
+        <v>94.99</v>
+      </c>
+      <c r="R17" s="136" t="s">
+        <v>218</v>
+      </c>
       <c r="S17" s="44"/>
     </row>
     <row r="18" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A18" s="1"/>
-      <c r="B18" s="61">
+      <c r="B18" s="55">
         <f>ROW(B18) - ROW($B$9)</f>
         <v>9</v>
       </c>
-      <c r="C18" s="70" t="s">
+      <c r="C18" s="62" t="s">
         <v>7</v>
       </c>
-      <c r="D18" s="72" t="s">
+      <c r="D18" s="64" t="s">
         <v>159</v>
       </c>
-      <c r="E18" s="56" t="s">
+      <c r="E18" s="50" t="s">
         <v>49</v>
       </c>
-      <c r="F18" s="72" t="s">
+      <c r="F18" s="64" t="s">
         <v>72</v>
       </c>
-      <c r="G18" s="56" t="s">
+      <c r="G18" s="50" t="s">
         <v>101</v>
       </c>
-      <c r="H18" s="72" t="s">
+      <c r="H18" s="64" t="s">
         <v>113</v>
       </c>
-      <c r="I18" s="56" t="s">
-        <v>176</v>
-      </c>
-      <c r="J18" s="80" t="s">
+      <c r="I18" s="50" t="s">
+        <v>176</v>
+      </c>
+      <c r="J18" s="72" t="s">
         <v>193</v>
       </c>
-      <c r="K18" s="56" t="s">
+      <c r="K18" s="50" t="s">
         <v>139</v>
       </c>
-      <c r="L18" s="72">
+      <c r="L18" s="64">
         <v>3</v>
       </c>
-      <c r="M18" s="56">
-        <f t="shared" si="1"/>
+      <c r="M18" s="50">
+        <f t="shared" si="2"/>
         <v>3000</v>
       </c>
-      <c r="N18" s="72"/>
-      <c r="O18" s="102" t="s">
+      <c r="N18" s="64">
+        <v>3100</v>
+      </c>
+      <c r="O18" s="94" t="s">
         <v>152</v>
       </c>
-      <c r="P18" s="98"/>
-      <c r="Q18" s="94">
-        <f>P18*N18</f>
-        <v>0</v>
-      </c>
-      <c r="R18" s="72"/>
-      <c r="S18" s="100"/>
-    </row>
-    <row r="19" spans="1:19" s="109" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="106"/>
-      <c r="B19" s="61">
+      <c r="P18" s="90">
+        <v>1.55E-2</v>
+      </c>
+      <c r="Q18" s="86">
+        <f t="shared" si="0"/>
+        <v>48.05</v>
+      </c>
+      <c r="R18" s="64"/>
+      <c r="S18" s="92"/>
+    </row>
+    <row r="19" spans="1:19" s="101" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A19" s="98"/>
+      <c r="B19" s="55">
         <f>ROW(B19) - ROW($B$9)</f>
         <v>10</v>
       </c>
-      <c r="C19" s="59" t="s">
+      <c r="C19" s="53" t="s">
         <v>7</v>
       </c>
       <c r="D19" s="41" t="s">
@@ -4922,80 +5072,90 @@
         <v>1</v>
       </c>
       <c r="M19" s="40">
+        <f t="shared" si="2"/>
+        <v>1000</v>
+      </c>
+      <c r="N19" s="41">
+        <v>1100</v>
+      </c>
+      <c r="O19" s="80" t="s">
+        <v>152</v>
+      </c>
+      <c r="P19" s="89">
+        <v>2.5000000000000001E-3</v>
+      </c>
+      <c r="Q19" s="102">
+        <f t="shared" si="0"/>
+        <v>2.75</v>
+      </c>
+      <c r="R19" s="41"/>
+      <c r="S19" s="103"/>
+    </row>
+    <row r="20" spans="1:19" ht="51.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A20" s="1"/>
+      <c r="B20" s="55">
         <f t="shared" si="1"/>
-        <v>1000</v>
-      </c>
-      <c r="N19" s="41"/>
-      <c r="O19" s="88" t="s">
+        <v>11</v>
+      </c>
+      <c r="C20" s="62" t="s">
+        <v>7</v>
+      </c>
+      <c r="D20" s="64" t="s">
+        <v>20</v>
+      </c>
+      <c r="E20" s="50" t="s">
+        <v>51</v>
+      </c>
+      <c r="F20" s="64" t="s">
+        <v>75</v>
+      </c>
+      <c r="G20" s="50" t="s">
+        <v>103</v>
+      </c>
+      <c r="H20" s="64" t="s">
+        <v>116</v>
+      </c>
+      <c r="I20" s="50" t="s">
+        <v>176</v>
+      </c>
+      <c r="J20" s="72" t="s">
+        <v>194</v>
+      </c>
+      <c r="K20" s="50" t="s">
+        <v>139</v>
+      </c>
+      <c r="L20" s="64">
+        <v>16</v>
+      </c>
+      <c r="M20" s="50">
+        <f t="shared" si="2"/>
+        <v>16000</v>
+      </c>
+      <c r="N20" s="64">
+        <v>16100</v>
+      </c>
+      <c r="O20" s="94" t="s">
         <v>152</v>
       </c>
-      <c r="P19" s="97"/>
-      <c r="Q19" s="110">
-        <f>P19*N19</f>
-        <v>0</v>
-      </c>
-      <c r="R19" s="41"/>
-      <c r="S19" s="111"/>
-    </row>
-    <row r="20" spans="1:19" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="1"/>
-      <c r="B20" s="61">
+      <c r="P20" s="90">
+        <v>4.5999999999999999E-2</v>
+      </c>
+      <c r="Q20" s="86">
         <f t="shared" si="0"/>
-        <v>11</v>
-      </c>
-      <c r="C20" s="70" t="s">
-        <v>7</v>
-      </c>
-      <c r="D20" s="72" t="s">
-        <v>20</v>
-      </c>
-      <c r="E20" s="56" t="s">
-        <v>51</v>
-      </c>
-      <c r="F20" s="72" t="s">
-        <v>75</v>
-      </c>
-      <c r="G20" s="56" t="s">
-        <v>103</v>
-      </c>
-      <c r="H20" s="72" t="s">
-        <v>116</v>
-      </c>
-      <c r="I20" s="56" t="s">
-        <v>176</v>
-      </c>
-      <c r="J20" s="80" t="s">
-        <v>194</v>
-      </c>
-      <c r="K20" s="56" t="s">
-        <v>139</v>
-      </c>
-      <c r="L20" s="72">
-        <v>16</v>
-      </c>
-      <c r="M20" s="56">
-        <f t="shared" si="1"/>
-        <v>16000</v>
-      </c>
-      <c r="N20" s="72"/>
-      <c r="O20" s="102" t="s">
-        <v>152</v>
-      </c>
-      <c r="P20" s="98"/>
-      <c r="Q20" s="94">
-        <f>P20*N20</f>
-        <v>0</v>
-      </c>
-      <c r="R20" s="72"/>
-      <c r="S20" s="100"/>
-    </row>
-    <row r="21" spans="1:19" s="109" customFormat="1" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="106"/>
-      <c r="B21" s="61">
+        <v>740.6</v>
+      </c>
+      <c r="R20" s="137" t="s">
+        <v>218</v>
+      </c>
+      <c r="S20" s="92"/>
+    </row>
+    <row r="21" spans="1:19" s="101" customFormat="1" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A21" s="98"/>
+      <c r="B21" s="55">
         <f>ROW(B21) - ROW($B$9)</f>
         <v>12</v>
       </c>
-      <c r="C21" s="59" t="s">
+      <c r="C21" s="53" t="s">
         <v>163</v>
       </c>
       <c r="D21" s="41" t="s">
@@ -5004,7 +5164,7 @@
       <c r="E21" s="40" t="s">
         <v>52</v>
       </c>
-      <c r="F21" s="76" t="s">
+      <c r="F21" s="68" t="s">
         <v>171</v>
       </c>
       <c r="G21" s="40" t="s">
@@ -5026,80 +5186,88 @@
         <v>1</v>
       </c>
       <c r="M21" s="40">
+        <f t="shared" si="2"/>
+        <v>1000</v>
+      </c>
+      <c r="N21" s="41">
+        <v>1050</v>
+      </c>
+      <c r="O21" s="80" t="s">
+        <v>152</v>
+      </c>
+      <c r="P21" s="89">
+        <v>2.8899999999999999E-2</v>
+      </c>
+      <c r="Q21" s="102">
+        <f t="shared" si="0"/>
+        <v>30.344999999999999</v>
+      </c>
+      <c r="R21" s="41"/>
+      <c r="S21" s="103"/>
+    </row>
+    <row r="22" spans="1:19" s="101" customFormat="1" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A22" s="98"/>
+      <c r="B22" s="55">
         <f t="shared" si="1"/>
+        <v>13</v>
+      </c>
+      <c r="C22" s="62" t="s">
+        <v>163</v>
+      </c>
+      <c r="D22" s="64" t="s">
+        <v>22</v>
+      </c>
+      <c r="E22" s="50" t="s">
+        <v>53</v>
+      </c>
+      <c r="F22" s="64" t="s">
+        <v>77</v>
+      </c>
+      <c r="G22" s="50" t="s">
+        <v>104</v>
+      </c>
+      <c r="H22" s="64" t="s">
+        <v>118</v>
+      </c>
+      <c r="I22" s="50" t="s">
+        <v>176</v>
+      </c>
+      <c r="J22" s="72" t="s">
+        <v>173</v>
+      </c>
+      <c r="K22" s="50" t="s">
+        <v>176</v>
+      </c>
+      <c r="L22" s="64">
+        <v>1</v>
+      </c>
+      <c r="M22" s="50">
+        <f t="shared" si="2"/>
         <v>1000</v>
       </c>
-      <c r="N21" s="41"/>
-      <c r="O21" s="88" t="s">
+      <c r="N22" s="64">
+        <v>1050</v>
+      </c>
+      <c r="O22" s="81" t="s">
         <v>152</v>
       </c>
-      <c r="P21" s="97"/>
-      <c r="Q21" s="110">
-        <f>P21*N21</f>
-        <v>0</v>
-      </c>
-      <c r="R21" s="41"/>
-      <c r="S21" s="111"/>
-    </row>
-    <row r="22" spans="1:19" s="109" customFormat="1" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="106"/>
-      <c r="B22" s="61">
+      <c r="P22" s="90">
+        <v>2.12E-2</v>
+      </c>
+      <c r="Q22" s="99">
         <f t="shared" si="0"/>
-        <v>13</v>
-      </c>
-      <c r="C22" s="70" t="s">
-        <v>163</v>
-      </c>
-      <c r="D22" s="72" t="s">
-        <v>22</v>
-      </c>
-      <c r="E22" s="56" t="s">
-        <v>53</v>
-      </c>
-      <c r="F22" s="72" t="s">
-        <v>77</v>
-      </c>
-      <c r="G22" s="56" t="s">
-        <v>104</v>
-      </c>
-      <c r="H22" s="72" t="s">
-        <v>118</v>
-      </c>
-      <c r="I22" s="56" t="s">
-        <v>176</v>
-      </c>
-      <c r="J22" s="80" t="s">
-        <v>173</v>
-      </c>
-      <c r="K22" s="56" t="s">
-        <v>176</v>
-      </c>
-      <c r="L22" s="72">
-        <v>1</v>
-      </c>
-      <c r="M22" s="56">
-        <f t="shared" si="1"/>
-        <v>1000</v>
-      </c>
-      <c r="N22" s="72"/>
-      <c r="O22" s="89" t="s">
-        <v>152</v>
-      </c>
-      <c r="P22" s="98"/>
-      <c r="Q22" s="107">
-        <f>P22*N22</f>
-        <v>0</v>
-      </c>
-      <c r="R22" s="72"/>
-      <c r="S22" s="108"/>
-    </row>
-    <row r="23" spans="1:19" s="109" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="106"/>
-      <c r="B23" s="61">
+        <v>22.26</v>
+      </c>
+      <c r="R22" s="64"/>
+      <c r="S22" s="100"/>
+    </row>
+    <row r="23" spans="1:19" s="101" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A23" s="98"/>
+      <c r="B23" s="55">
         <f>ROW(B23) - ROW($B$9)</f>
         <v>14</v>
       </c>
-      <c r="C23" s="59" t="s">
+      <c r="C23" s="53" t="s">
         <v>164</v>
       </c>
       <c r="D23" s="41" t="s">
@@ -5111,7 +5279,7 @@
       <c r="F23" s="41" t="s">
         <v>78</v>
       </c>
-      <c r="G23" s="40" t="s">
+      <c r="G23" s="95" t="s">
         <v>105</v>
       </c>
       <c r="H23" s="41" t="s">
@@ -5120,7 +5288,7 @@
       <c r="I23" s="40" t="s">
         <v>196</v>
       </c>
-      <c r="J23" s="81" t="s">
+      <c r="J23" s="73" t="s">
         <v>195</v>
       </c>
       <c r="K23" s="40" t="s">
@@ -5130,80 +5298,88 @@
         <v>1</v>
       </c>
       <c r="M23" s="40">
+        <f t="shared" si="2"/>
+        <v>1000</v>
+      </c>
+      <c r="N23" s="41">
+        <v>1100</v>
+      </c>
+      <c r="O23" s="96" t="s">
+        <v>152</v>
+      </c>
+      <c r="P23" s="89">
+        <v>1.84E-2</v>
+      </c>
+      <c r="Q23" s="102">
+        <f t="shared" si="0"/>
+        <v>20.239999999999998</v>
+      </c>
+      <c r="R23" s="41"/>
+      <c r="S23" s="103"/>
+    </row>
+    <row r="24" spans="1:19" s="101" customFormat="1" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A24" s="98"/>
+      <c r="B24" s="55">
         <f t="shared" si="1"/>
+        <v>15</v>
+      </c>
+      <c r="C24" s="62" t="s">
+        <v>165</v>
+      </c>
+      <c r="D24" s="64" t="s">
+        <v>24</v>
+      </c>
+      <c r="E24" s="50" t="s">
+        <v>55</v>
+      </c>
+      <c r="F24" s="64" t="s">
+        <v>175</v>
+      </c>
+      <c r="G24" s="50" t="s">
+        <v>79</v>
+      </c>
+      <c r="H24" s="64" t="s">
+        <v>120</v>
+      </c>
+      <c r="I24" s="50" t="s">
+        <v>176</v>
+      </c>
+      <c r="J24" s="74" t="s">
+        <v>185</v>
+      </c>
+      <c r="K24" s="50" t="s">
+        <v>176</v>
+      </c>
+      <c r="L24" s="64">
+        <v>1</v>
+      </c>
+      <c r="M24" s="50">
+        <f t="shared" si="2"/>
         <v>1000</v>
       </c>
-      <c r="N23" s="41"/>
-      <c r="O23" s="104" t="s">
+      <c r="N24" s="64">
+        <v>1050</v>
+      </c>
+      <c r="O24" s="82" t="s">
         <v>152</v>
       </c>
-      <c r="P23" s="97"/>
-      <c r="Q23" s="110">
-        <f>P23*N23</f>
-        <v>0</v>
-      </c>
-      <c r="R23" s="41"/>
-      <c r="S23" s="111"/>
-    </row>
-    <row r="24" spans="1:19" s="109" customFormat="1" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="106"/>
-      <c r="B24" s="61">
+      <c r="P24" s="90">
+        <v>3.2199999999999999E-2</v>
+      </c>
+      <c r="Q24" s="99">
         <f t="shared" si="0"/>
-        <v>15</v>
-      </c>
-      <c r="C24" s="70" t="s">
-        <v>165</v>
-      </c>
-      <c r="D24" s="72" t="s">
-        <v>24</v>
-      </c>
-      <c r="E24" s="56" t="s">
-        <v>55</v>
-      </c>
-      <c r="F24" s="72" t="s">
-        <v>175</v>
-      </c>
-      <c r="G24" s="56" t="s">
-        <v>79</v>
-      </c>
-      <c r="H24" s="72" t="s">
-        <v>120</v>
-      </c>
-      <c r="I24" s="56" t="s">
-        <v>176</v>
-      </c>
-      <c r="J24" s="82" t="s">
-        <v>185</v>
-      </c>
-      <c r="K24" s="56" t="s">
-        <v>176</v>
-      </c>
-      <c r="L24" s="72">
-        <v>1</v>
-      </c>
-      <c r="M24" s="56">
-        <f t="shared" si="1"/>
-        <v>1000</v>
-      </c>
-      <c r="N24" s="72"/>
-      <c r="O24" s="90" t="s">
-        <v>152</v>
-      </c>
-      <c r="P24" s="98"/>
-      <c r="Q24" s="107">
-        <f>P24*N24</f>
-        <v>0</v>
-      </c>
-      <c r="R24" s="72"/>
-      <c r="S24" s="108"/>
+        <v>33.81</v>
+      </c>
+      <c r="R24" s="64"/>
+      <c r="S24" s="100"/>
     </row>
     <row r="25" spans="1:19" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A25" s="1"/>
-      <c r="B25" s="61">
+      <c r="B25" s="55">
         <f>ROW(B25) - ROW($B$9)</f>
         <v>16</v>
       </c>
-      <c r="C25" s="59" t="s">
+      <c r="C25" s="53" t="s">
         <v>8</v>
       </c>
       <c r="D25" s="41" t="s">
@@ -5224,84 +5400,98 @@
       <c r="I25" s="40" t="s">
         <v>176</v>
       </c>
-      <c r="J25" s="41"/>
-      <c r="K25" s="40"/>
+      <c r="J25" s="41" t="s">
+        <v>176</v>
+      </c>
+      <c r="K25" s="40" t="s">
+        <v>176</v>
+      </c>
       <c r="L25" s="41">
         <v>8</v>
       </c>
       <c r="M25" s="40">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>8000</v>
       </c>
-      <c r="N25" s="41"/>
-      <c r="O25" s="57"/>
-      <c r="P25" s="97"/>
-      <c r="Q25" s="93">
-        <f>P25*N25</f>
-        <v>0</v>
+      <c r="N25" s="41">
+        <v>8100</v>
+      </c>
+      <c r="O25" s="84" t="s">
+        <v>212</v>
+      </c>
+      <c r="P25" s="89">
+        <v>1.2749999999999999</v>
+      </c>
+      <c r="Q25" s="85">
+        <f t="shared" si="0"/>
+        <v>10327.5</v>
       </c>
       <c r="R25" s="41"/>
       <c r="S25" s="44"/>
     </row>
-    <row r="26" spans="1:19" s="109" customFormat="1" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="106"/>
-      <c r="B26" s="61">
+    <row r="26" spans="1:19" s="101" customFormat="1" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A26" s="98"/>
+      <c r="B26" s="55">
+        <f t="shared" si="1"/>
+        <v>17</v>
+      </c>
+      <c r="C26" s="62" t="s">
+        <v>164</v>
+      </c>
+      <c r="D26" s="64" t="s">
+        <v>26</v>
+      </c>
+      <c r="E26" s="50" t="s">
+        <v>57</v>
+      </c>
+      <c r="F26" s="64" t="s">
+        <v>81</v>
+      </c>
+      <c r="G26" s="97">
+        <v>61300611121</v>
+      </c>
+      <c r="H26" s="64" t="s">
+        <v>122</v>
+      </c>
+      <c r="I26" s="50" t="s">
+        <v>197</v>
+      </c>
+      <c r="J26" s="72" t="s">
+        <v>197</v>
+      </c>
+      <c r="K26" s="50" t="s">
+        <v>176</v>
+      </c>
+      <c r="L26" s="64">
+        <v>1</v>
+      </c>
+      <c r="M26" s="50">
+        <f t="shared" si="2"/>
+        <v>1000</v>
+      </c>
+      <c r="N26" s="64">
+        <v>1100</v>
+      </c>
+      <c r="O26" s="94" t="s">
+        <v>152</v>
+      </c>
+      <c r="P26" s="90">
+        <v>1.9400000000000001E-2</v>
+      </c>
+      <c r="Q26" s="99">
         <f t="shared" si="0"/>
-        <v>17</v>
-      </c>
-      <c r="C26" s="70" t="s">
-        <v>164</v>
-      </c>
-      <c r="D26" s="72" t="s">
-        <v>26</v>
-      </c>
-      <c r="E26" s="56" t="s">
-        <v>57</v>
-      </c>
-      <c r="F26" s="72" t="s">
-        <v>81</v>
-      </c>
-      <c r="G26" s="56">
-        <v>61300611121</v>
-      </c>
-      <c r="H26" s="72" t="s">
-        <v>122</v>
-      </c>
-      <c r="I26" s="56" t="s">
-        <v>197</v>
-      </c>
-      <c r="J26" s="80" t="s">
-        <v>197</v>
-      </c>
-      <c r="K26" s="56" t="s">
-        <v>176</v>
-      </c>
-      <c r="L26" s="72">
-        <v>1</v>
-      </c>
-      <c r="M26" s="56">
-        <f t="shared" si="1"/>
-        <v>1000</v>
-      </c>
-      <c r="N26" s="72"/>
-      <c r="O26" s="102" t="s">
-        <v>152</v>
-      </c>
-      <c r="P26" s="98"/>
-      <c r="Q26" s="107">
-        <f>P26*N26</f>
-        <v>0</v>
-      </c>
-      <c r="R26" s="72"/>
-      <c r="S26" s="108"/>
-    </row>
-    <row r="27" spans="1:19" s="109" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="106"/>
-      <c r="B27" s="61">
+        <v>21.34</v>
+      </c>
+      <c r="R26" s="64"/>
+      <c r="S26" s="100"/>
+    </row>
+    <row r="27" spans="1:19" s="101" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A27" s="98"/>
+      <c r="B27" s="55">
         <f>ROW(B27) - ROW($B$9)</f>
         <v>18</v>
       </c>
-      <c r="C27" s="59" t="s">
+      <c r="C27" s="53" t="s">
         <v>166</v>
       </c>
       <c r="D27" s="41" t="s">
@@ -5313,16 +5503,16 @@
       <c r="F27" s="41" t="s">
         <v>82</v>
       </c>
-      <c r="G27" s="40" t="s">
+      <c r="G27" s="95" t="s">
         <v>106</v>
       </c>
       <c r="H27" s="41" t="s">
         <v>119</v>
       </c>
-      <c r="I27" s="78" t="s">
+      <c r="I27" s="70" t="s">
         <v>182</v>
       </c>
-      <c r="J27" s="83" t="s">
+      <c r="J27" s="75" t="s">
         <v>181</v>
       </c>
       <c r="K27" s="40" t="s">
@@ -5332,80 +5522,88 @@
         <v>3</v>
       </c>
       <c r="M27" s="40">
+        <f t="shared" si="2"/>
+        <v>3000</v>
+      </c>
+      <c r="N27" s="41">
+        <v>3100</v>
+      </c>
+      <c r="O27" s="96" t="s">
+        <v>152</v>
+      </c>
+      <c r="P27" s="89">
+        <v>6.9999999999999999E-4</v>
+      </c>
+      <c r="Q27" s="102">
+        <f t="shared" si="0"/>
+        <v>2.17</v>
+      </c>
+      <c r="R27" s="41"/>
+      <c r="S27" s="103"/>
+    </row>
+    <row r="28" spans="1:19" s="101" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A28" s="98"/>
+      <c r="B28" s="55">
         <f t="shared" si="1"/>
+        <v>19</v>
+      </c>
+      <c r="C28" s="62" t="s">
+        <v>166</v>
+      </c>
+      <c r="D28" s="64" t="s">
+        <v>28</v>
+      </c>
+      <c r="E28" s="50" t="s">
+        <v>59</v>
+      </c>
+      <c r="F28" s="64" t="s">
+        <v>82</v>
+      </c>
+      <c r="G28" s="50" t="s">
+        <v>107</v>
+      </c>
+      <c r="H28" s="64" t="s">
+        <v>114</v>
+      </c>
+      <c r="I28" s="50" t="s">
+        <v>176</v>
+      </c>
+      <c r="J28" s="72" t="s">
+        <v>183</v>
+      </c>
+      <c r="K28" s="50" t="s">
+        <v>142</v>
+      </c>
+      <c r="L28" s="64">
+        <v>3</v>
+      </c>
+      <c r="M28" s="50">
+        <f t="shared" si="2"/>
         <v>3000</v>
       </c>
-      <c r="N27" s="41"/>
-      <c r="O27" s="104" t="s">
+      <c r="N28" s="64">
+        <v>3100</v>
+      </c>
+      <c r="O28" s="83" t="s">
         <v>152</v>
       </c>
-      <c r="P27" s="97"/>
-      <c r="Q27" s="110">
-        <f>P27*N27</f>
-        <v>0</v>
-      </c>
-      <c r="R27" s="41"/>
-      <c r="S27" s="111"/>
-    </row>
-    <row r="28" spans="1:19" s="109" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A28" s="106"/>
-      <c r="B28" s="61">
+      <c r="P28" s="90">
+        <v>8.0000000000000004E-4</v>
+      </c>
+      <c r="Q28" s="99">
         <f t="shared" si="0"/>
-        <v>19</v>
-      </c>
-      <c r="C28" s="70" t="s">
-        <v>166</v>
-      </c>
-      <c r="D28" s="72" t="s">
-        <v>28</v>
-      </c>
-      <c r="E28" s="56" t="s">
-        <v>59</v>
-      </c>
-      <c r="F28" s="72" t="s">
-        <v>82</v>
-      </c>
-      <c r="G28" s="56" t="s">
-        <v>107</v>
-      </c>
-      <c r="H28" s="72" t="s">
-        <v>114</v>
-      </c>
-      <c r="I28" s="56" t="s">
-        <v>176</v>
-      </c>
-      <c r="J28" s="80" t="s">
-        <v>183</v>
-      </c>
-      <c r="K28" s="56" t="s">
-        <v>142</v>
-      </c>
-      <c r="L28" s="72">
-        <v>3</v>
-      </c>
-      <c r="M28" s="56">
-        <f t="shared" si="1"/>
-        <v>3000</v>
-      </c>
-      <c r="N28" s="72"/>
-      <c r="O28" s="91" t="s">
-        <v>152</v>
-      </c>
-      <c r="P28" s="98"/>
-      <c r="Q28" s="107">
-        <f>P28*N28</f>
-        <v>0</v>
-      </c>
-      <c r="R28" s="72"/>
-      <c r="S28" s="108"/>
-    </row>
-    <row r="29" spans="1:19" s="109" customFormat="1" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A29" s="106"/>
-      <c r="B29" s="61">
+        <v>2.48</v>
+      </c>
+      <c r="R28" s="64"/>
+      <c r="S28" s="100"/>
+    </row>
+    <row r="29" spans="1:19" s="101" customFormat="1" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A29" s="98"/>
+      <c r="B29" s="55">
         <f>ROW(B29) - ROW($B$9)</f>
         <v>20</v>
       </c>
-      <c r="C29" s="59" t="s">
+      <c r="C29" s="53" t="s">
         <v>166</v>
       </c>
       <c r="D29" s="41" t="s">
@@ -5426,7 +5624,7 @@
       <c r="I29" s="40" t="s">
         <v>176</v>
       </c>
-      <c r="J29" s="83" t="s">
+      <c r="J29" s="75" t="s">
         <v>184</v>
       </c>
       <c r="K29" s="40" t="s">
@@ -5436,80 +5634,88 @@
         <v>2</v>
       </c>
       <c r="M29" s="40">
+        <f t="shared" si="2"/>
+        <v>2000</v>
+      </c>
+      <c r="N29" s="41">
+        <v>2100</v>
+      </c>
+      <c r="O29" s="84" t="s">
+        <v>152</v>
+      </c>
+      <c r="P29" s="89">
+        <v>8.0000000000000004E-4</v>
+      </c>
+      <c r="Q29" s="102">
+        <f t="shared" si="0"/>
+        <v>1.6800000000000002</v>
+      </c>
+      <c r="R29" s="41"/>
+      <c r="S29" s="103"/>
+    </row>
+    <row r="30" spans="1:19" s="101" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A30" s="98"/>
+      <c r="B30" s="55">
         <f t="shared" si="1"/>
-        <v>2000</v>
-      </c>
-      <c r="N29" s="41"/>
-      <c r="O29" s="92" t="s">
+        <v>21</v>
+      </c>
+      <c r="C30" s="62" t="s">
+        <v>166</v>
+      </c>
+      <c r="D30" s="64" t="s">
+        <v>30</v>
+      </c>
+      <c r="E30" s="50" t="s">
+        <v>61</v>
+      </c>
+      <c r="F30" s="64" t="s">
+        <v>82</v>
+      </c>
+      <c r="G30" s="50" t="s">
+        <v>109</v>
+      </c>
+      <c r="H30" s="64" t="s">
+        <v>114</v>
+      </c>
+      <c r="I30" s="50" t="s">
+        <v>176</v>
+      </c>
+      <c r="J30" s="72" t="s">
+        <v>198</v>
+      </c>
+      <c r="K30" s="50" t="s">
+        <v>144</v>
+      </c>
+      <c r="L30" s="64">
+        <v>1</v>
+      </c>
+      <c r="M30" s="50">
+        <f t="shared" si="2"/>
+        <v>1000</v>
+      </c>
+      <c r="N30" s="64">
+        <v>1100</v>
+      </c>
+      <c r="O30" s="94" t="s">
         <v>152</v>
       </c>
-      <c r="P29" s="97"/>
-      <c r="Q29" s="110">
-        <f>P29*N29</f>
-        <v>0</v>
-      </c>
-      <c r="R29" s="41"/>
-      <c r="S29" s="111"/>
-    </row>
-    <row r="30" spans="1:19" s="109" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A30" s="106"/>
-      <c r="B30" s="61">
+      <c r="P30" s="90">
+        <v>8.0000000000000004E-4</v>
+      </c>
+      <c r="Q30" s="99">
         <f t="shared" si="0"/>
-        <v>21</v>
-      </c>
-      <c r="C30" s="70" t="s">
-        <v>166</v>
-      </c>
-      <c r="D30" s="72" t="s">
-        <v>30</v>
-      </c>
-      <c r="E30" s="56" t="s">
-        <v>61</v>
-      </c>
-      <c r="F30" s="72" t="s">
-        <v>82</v>
-      </c>
-      <c r="G30" s="56" t="s">
-        <v>109</v>
-      </c>
-      <c r="H30" s="72" t="s">
-        <v>114</v>
-      </c>
-      <c r="I30" s="56" t="s">
-        <v>176</v>
-      </c>
-      <c r="J30" s="80" t="s">
-        <v>198</v>
-      </c>
-      <c r="K30" s="56" t="s">
-        <v>144</v>
-      </c>
-      <c r="L30" s="72">
-        <v>1</v>
-      </c>
-      <c r="M30" s="56">
-        <f t="shared" si="1"/>
-        <v>1000</v>
-      </c>
-      <c r="N30" s="72"/>
-      <c r="O30" s="102" t="s">
-        <v>152</v>
-      </c>
-      <c r="P30" s="98"/>
-      <c r="Q30" s="107">
-        <f>P30*N30</f>
-        <v>0</v>
-      </c>
-      <c r="R30" s="72"/>
-      <c r="S30" s="108"/>
+        <v>0.88</v>
+      </c>
+      <c r="R30" s="64"/>
+      <c r="S30" s="100"/>
     </row>
     <row r="31" spans="1:19" ht="120.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A31" s="1"/>
-      <c r="B31" s="61">
+      <c r="B31" s="55">
         <f>ROW(B31) - ROW($B$9)</f>
         <v>22</v>
       </c>
-      <c r="C31" s="59" t="s">
+      <c r="C31" s="53" t="s">
         <v>167</v>
       </c>
       <c r="D31" s="41" t="s">
@@ -5540,87 +5746,93 @@
         <v>48</v>
       </c>
       <c r="M31" s="40">
+        <f t="shared" si="2"/>
+        <v>48000</v>
+      </c>
+      <c r="N31" s="41" t="s">
+        <v>176</v>
+      </c>
+      <c r="O31" s="51" t="s">
+        <v>176</v>
+      </c>
+      <c r="P31" s="89" t="s">
+        <v>176</v>
+      </c>
+      <c r="Q31" s="85" t="s">
+        <v>176</v>
+      </c>
+      <c r="R31" s="41" t="s">
+        <v>176</v>
+      </c>
+      <c r="S31" s="54" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="32" spans="1:19" s="101" customFormat="1" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A32" s="98"/>
+      <c r="B32" s="55">
         <f t="shared" si="1"/>
-        <v>48000</v>
-      </c>
-      <c r="N31" s="41" t="s">
-        <v>176</v>
-      </c>
-      <c r="O31" s="57" t="s">
-        <v>176</v>
-      </c>
-      <c r="P31" s="97" t="s">
-        <v>176</v>
-      </c>
-      <c r="Q31" s="93" t="s">
-        <v>176</v>
-      </c>
-      <c r="R31" s="41" t="s">
-        <v>176</v>
-      </c>
-      <c r="S31" s="60" t="s">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="32" spans="1:19" s="109" customFormat="1" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A32" s="106"/>
-      <c r="B32" s="61">
-        <f t="shared" si="0"/>
         <v>23</v>
       </c>
-      <c r="C32" s="70" t="s">
+      <c r="C32" s="62" t="s">
         <v>168</v>
       </c>
-      <c r="D32" s="72" t="s">
+      <c r="D32" s="64" t="s">
         <v>32</v>
       </c>
-      <c r="E32" s="56" t="s">
+      <c r="E32" s="50" t="s">
         <v>63</v>
       </c>
-      <c r="F32" s="72" t="s">
+      <c r="F32" s="64" t="s">
         <v>175</v>
       </c>
-      <c r="G32" s="112" t="s">
+      <c r="G32" s="104" t="s">
         <v>84</v>
       </c>
-      <c r="H32" s="72" t="s">
+      <c r="H32" s="64" t="s">
         <v>120</v>
       </c>
-      <c r="I32" s="56" t="s">
-        <v>176</v>
-      </c>
-      <c r="J32" s="80" t="s">
+      <c r="I32" s="50" t="s">
+        <v>176</v>
+      </c>
+      <c r="J32" s="72" t="s">
         <v>174</v>
       </c>
-      <c r="K32" s="56" t="s">
-        <v>176</v>
-      </c>
-      <c r="L32" s="72">
+      <c r="K32" s="50" t="s">
+        <v>176</v>
+      </c>
+      <c r="L32" s="64">
         <v>1</v>
       </c>
-      <c r="M32" s="56">
-        <f t="shared" si="1"/>
+      <c r="M32" s="50">
+        <f t="shared" si="2"/>
         <v>1000</v>
       </c>
-      <c r="N32" s="72"/>
-      <c r="O32" s="102" t="s">
-        <v>152</v>
-      </c>
-      <c r="P32" s="98"/>
-      <c r="Q32" s="107">
-        <f>P32*N32</f>
-        <v>0</v>
-      </c>
-      <c r="R32" s="72"/>
-      <c r="S32" s="108"/>
-    </row>
-    <row r="33" spans="1:19" s="109" customFormat="1" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A33" s="106"/>
-      <c r="B33" s="61">
+      <c r="N32" s="64">
+        <v>1050</v>
+      </c>
+      <c r="O32" s="94" t="s">
+        <v>212</v>
+      </c>
+      <c r="P32" s="90">
+        <v>1.6E-2</v>
+      </c>
+      <c r="Q32" s="99">
+        <f t="shared" ref="Q32:Q39" si="3">P32*N32</f>
+        <v>16.8</v>
+      </c>
+      <c r="R32" s="137" t="s">
+        <v>213</v>
+      </c>
+      <c r="S32" s="100"/>
+    </row>
+    <row r="33" spans="1:19" s="101" customFormat="1" ht="26.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A33" s="98"/>
+      <c r="B33" s="55">
         <f>ROW(B33) - ROW($B$9)</f>
         <v>24</v>
       </c>
-      <c r="C33" s="59" t="s">
+      <c r="C33" s="53" t="s">
         <v>9</v>
       </c>
       <c r="D33" s="41" t="s">
@@ -5642,7 +5854,7 @@
         <v>176</v>
       </c>
       <c r="J33" s="41" t="s">
-        <v>130</v>
+        <v>176</v>
       </c>
       <c r="K33" s="40" t="s">
         <v>176</v>
@@ -5651,80 +5863,90 @@
         <v>1</v>
       </c>
       <c r="M33" s="40">
+        <f t="shared" si="2"/>
+        <v>1000</v>
+      </c>
+      <c r="N33" s="41">
+        <v>1020</v>
+      </c>
+      <c r="O33" s="80" t="s">
+        <v>212</v>
+      </c>
+      <c r="P33" s="89">
+        <v>3.12</v>
+      </c>
+      <c r="Q33" s="102">
+        <f t="shared" si="3"/>
+        <v>3182.4</v>
+      </c>
+      <c r="R33" s="136" t="s">
+        <v>213</v>
+      </c>
+      <c r="S33" s="103"/>
+    </row>
+    <row r="34" spans="1:19" s="101" customFormat="1" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A34" s="98"/>
+      <c r="B34" s="55">
         <f t="shared" si="1"/>
+        <v>25</v>
+      </c>
+      <c r="C34" s="62" t="s">
+        <v>169</v>
+      </c>
+      <c r="D34" s="64" t="s">
+        <v>34</v>
+      </c>
+      <c r="E34" s="50" t="s">
+        <v>65</v>
+      </c>
+      <c r="F34" s="64" t="s">
+        <v>86</v>
+      </c>
+      <c r="G34" s="50" t="s">
+        <v>110</v>
+      </c>
+      <c r="H34" s="64" t="s">
+        <v>124</v>
+      </c>
+      <c r="I34" s="50" t="s">
+        <v>176</v>
+      </c>
+      <c r="J34" s="76" t="s">
+        <v>179</v>
+      </c>
+      <c r="K34" s="50" t="s">
+        <v>176</v>
+      </c>
+      <c r="L34" s="64">
+        <v>1</v>
+      </c>
+      <c r="M34" s="50">
+        <f t="shared" si="2"/>
         <v>1000</v>
       </c>
-      <c r="N33" s="41"/>
-      <c r="O33" s="88" t="s">
+      <c r="N34" s="64">
+        <v>1020</v>
+      </c>
+      <c r="O34" s="94" t="s">
         <v>152</v>
       </c>
-      <c r="P33" s="97"/>
-      <c r="Q33" s="110">
-        <f>P33*N33</f>
-        <v>0</v>
-      </c>
-      <c r="R33" s="41"/>
-      <c r="S33" s="111"/>
-    </row>
-    <row r="34" spans="1:19" s="109" customFormat="1" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A34" s="106"/>
-      <c r="B34" s="61">
-        <f t="shared" si="0"/>
-        <v>25</v>
-      </c>
-      <c r="C34" s="70" t="s">
-        <v>169</v>
-      </c>
-      <c r="D34" s="72" t="s">
-        <v>34</v>
-      </c>
-      <c r="E34" s="56" t="s">
-        <v>65</v>
-      </c>
-      <c r="F34" s="72" t="s">
-        <v>86</v>
-      </c>
-      <c r="G34" s="56" t="s">
-        <v>110</v>
-      </c>
-      <c r="H34" s="72" t="s">
-        <v>124</v>
-      </c>
-      <c r="I34" s="56" t="s">
-        <v>176</v>
-      </c>
-      <c r="J34" s="84" t="s">
-        <v>179</v>
-      </c>
-      <c r="K34" s="56" t="s">
-        <v>176</v>
-      </c>
-      <c r="L34" s="72">
-        <v>1</v>
-      </c>
-      <c r="M34" s="56">
-        <f t="shared" si="1"/>
-        <v>1000</v>
-      </c>
-      <c r="N34" s="72"/>
-      <c r="O34" s="102" t="s">
-        <v>152</v>
-      </c>
-      <c r="P34" s="98"/>
-      <c r="Q34" s="107">
-        <f>P34*N34</f>
-        <v>0</v>
-      </c>
-      <c r="R34" s="72"/>
-      <c r="S34" s="108"/>
-    </row>
-    <row r="35" spans="1:19" s="109" customFormat="1" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A35" s="106"/>
-      <c r="B35" s="61">
+      <c r="P34" s="90">
+        <v>0.29759999999999998</v>
+      </c>
+      <c r="Q34" s="99">
+        <f t="shared" si="3"/>
+        <v>303.55199999999996</v>
+      </c>
+      <c r="R34" s="64"/>
+      <c r="S34" s="100"/>
+    </row>
+    <row r="35" spans="1:19" s="101" customFormat="1" ht="26.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A35" s="98"/>
+      <c r="B35" s="55">
         <f>ROW(B35) - ROW($B$9)</f>
         <v>26</v>
       </c>
-      <c r="C35" s="59" t="s">
+      <c r="C35" s="53" t="s">
         <v>169</v>
       </c>
       <c r="D35" s="41" t="s">
@@ -5742,85 +5964,105 @@
       <c r="H35" s="41" t="s">
         <v>118</v>
       </c>
-      <c r="I35" s="40"/>
-      <c r="J35" s="41"/>
-      <c r="K35" s="40"/>
+      <c r="I35" s="40" t="s">
+        <v>176</v>
+      </c>
+      <c r="J35" s="41" t="s">
+        <v>176</v>
+      </c>
+      <c r="K35" s="40" t="s">
+        <v>176</v>
+      </c>
       <c r="L35" s="41">
         <v>1</v>
       </c>
       <c r="M35" s="40">
+        <f t="shared" si="2"/>
+        <v>1000</v>
+      </c>
+      <c r="N35" s="41">
+        <v>1020</v>
+      </c>
+      <c r="O35" s="80" t="s">
+        <v>212</v>
+      </c>
+      <c r="P35" s="89">
+        <v>14.82</v>
+      </c>
+      <c r="Q35" s="102">
+        <f t="shared" si="3"/>
+        <v>15116.4</v>
+      </c>
+      <c r="R35" s="136" t="s">
+        <v>213</v>
+      </c>
+      <c r="S35" s="103"/>
+    </row>
+    <row r="36" spans="1:19" s="101" customFormat="1" ht="26.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A36" s="98"/>
+      <c r="B36" s="55">
         <f t="shared" si="1"/>
-        <v>1000</v>
-      </c>
-      <c r="N35" s="41"/>
-      <c r="O35" s="57"/>
-      <c r="P35" s="97"/>
-      <c r="Q35" s="110">
-        <f>P35*N35</f>
-        <v>0</v>
-      </c>
-      <c r="R35" s="41"/>
-      <c r="S35" s="111"/>
-    </row>
-    <row r="36" spans="1:19" s="109" customFormat="1" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A36" s="106"/>
-      <c r="B36" s="61">
-        <f t="shared" si="0"/>
         <v>27</v>
       </c>
-      <c r="C36" s="70" t="s">
+      <c r="C36" s="62" t="s">
         <v>169</v>
       </c>
-      <c r="D36" s="72" t="s">
+      <c r="D36" s="64" t="s">
         <v>36</v>
       </c>
-      <c r="E36" s="56" t="s">
+      <c r="E36" s="50" t="s">
         <v>67</v>
       </c>
-      <c r="F36" s="72" t="s">
+      <c r="F36" s="64" t="s">
         <v>186</v>
       </c>
-      <c r="G36" s="56" t="s">
+      <c r="G36" s="50" t="s">
         <v>88</v>
       </c>
-      <c r="H36" s="72" t="s">
+      <c r="H36" s="64" t="s">
         <v>118</v>
       </c>
-      <c r="I36" s="56" t="s">
-        <v>176</v>
-      </c>
-      <c r="J36" s="80" t="s">
+      <c r="I36" s="50" t="s">
+        <v>176</v>
+      </c>
+      <c r="J36" s="72" t="s">
         <v>199</v>
       </c>
-      <c r="K36" s="56" t="s">
-        <v>176</v>
-      </c>
-      <c r="L36" s="72">
+      <c r="K36" s="50" t="s">
+        <v>176</v>
+      </c>
+      <c r="L36" s="64">
         <v>2</v>
       </c>
-      <c r="M36" s="56">
-        <f t="shared" si="1"/>
+      <c r="M36" s="50">
+        <f t="shared" si="2"/>
         <v>2000</v>
       </c>
-      <c r="N36" s="72"/>
-      <c r="O36" s="102" t="s">
+      <c r="N36" s="64">
+        <v>2020</v>
+      </c>
+      <c r="O36" s="143" t="s">
         <v>152</v>
       </c>
-      <c r="P36" s="98"/>
-      <c r="Q36" s="107">
-        <f>P36*N36</f>
-        <v>0</v>
-      </c>
-      <c r="R36" s="72"/>
-      <c r="S36" s="108"/>
-    </row>
-    <row r="37" spans="1:19" s="109" customFormat="1" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A37" s="106"/>
-      <c r="B37" s="61">
+      <c r="P36" s="90">
+        <v>2.6855000000000002</v>
+      </c>
+      <c r="Q36" s="145">
+        <f t="shared" si="3"/>
+        <v>5424.71</v>
+      </c>
+      <c r="R36" s="137" t="s">
+        <v>215</v>
+      </c>
+      <c r="S36" s="100"/>
+    </row>
+    <row r="37" spans="1:19" s="101" customFormat="1" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A37" s="98"/>
+      <c r="B37" s="55">
         <f>ROW(B37) - ROW($B$9)</f>
         <v>28</v>
       </c>
-      <c r="C37" s="59" t="s">
+      <c r="C37" s="53" t="s">
         <v>169</v>
       </c>
       <c r="D37" s="41" t="s">
@@ -5829,7 +6071,9 @@
       <c r="E37" s="40" t="s">
         <v>68</v>
       </c>
-      <c r="F37" s="41"/>
+      <c r="F37" s="41" t="s">
+        <v>200</v>
+      </c>
       <c r="G37" s="40" t="s">
         <v>89</v>
       </c>
@@ -5839,7 +6083,7 @@
       <c r="I37" s="40" t="s">
         <v>176</v>
       </c>
-      <c r="J37" s="85" t="s">
+      <c r="J37" s="77" t="s">
         <v>180</v>
       </c>
       <c r="K37" s="40" t="s">
@@ -5849,148 +6093,166 @@
         <v>1</v>
       </c>
       <c r="M37" s="40">
+        <f t="shared" si="2"/>
+        <v>1000</v>
+      </c>
+      <c r="N37" s="41">
+        <v>1020</v>
+      </c>
+      <c r="O37" s="80" t="s">
+        <v>152</v>
+      </c>
+      <c r="P37" s="89">
+        <v>4.19E-2</v>
+      </c>
+      <c r="Q37" s="102">
+        <f t="shared" si="3"/>
+        <v>42.738</v>
+      </c>
+      <c r="R37" s="136" t="s">
+        <v>216</v>
+      </c>
+      <c r="S37" s="103"/>
+    </row>
+    <row r="38" spans="1:19" s="101" customFormat="1" ht="48.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A38" s="98"/>
+      <c r="B38" s="55">
         <f t="shared" si="1"/>
+        <v>29</v>
+      </c>
+      <c r="C38" s="62" t="s">
+        <v>170</v>
+      </c>
+      <c r="D38" s="64" t="s">
+        <v>38</v>
+      </c>
+      <c r="E38" s="50" t="s">
+        <v>69</v>
+      </c>
+      <c r="F38" s="64" t="s">
+        <v>175</v>
+      </c>
+      <c r="G38" s="50" t="s">
+        <v>90</v>
+      </c>
+      <c r="H38" s="64" t="s">
+        <v>126</v>
+      </c>
+      <c r="I38" s="50" t="s">
+        <v>176</v>
+      </c>
+      <c r="J38" s="78" t="s">
+        <v>177</v>
+      </c>
+      <c r="K38" s="50" t="s">
+        <v>187</v>
+      </c>
+      <c r="L38" s="64">
+        <v>1</v>
+      </c>
+      <c r="M38" s="50">
+        <f t="shared" si="2"/>
         <v>1000</v>
       </c>
-      <c r="N37" s="41"/>
-      <c r="O37" s="88" t="s">
+      <c r="N38" s="64">
+        <v>1020</v>
+      </c>
+      <c r="O38" s="94" t="s">
         <v>152</v>
       </c>
-      <c r="P37" s="97"/>
-      <c r="Q37" s="110">
-        <f>P37*N37</f>
-        <v>0</v>
-      </c>
-      <c r="R37" s="41"/>
-      <c r="S37" s="111"/>
-    </row>
-    <row r="38" spans="1:19" s="109" customFormat="1" ht="48.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A38" s="106"/>
-      <c r="B38" s="61">
-        <f t="shared" si="0"/>
-        <v>29</v>
-      </c>
-      <c r="C38" s="70" t="s">
-        <v>170</v>
-      </c>
-      <c r="D38" s="72" t="s">
-        <v>38</v>
-      </c>
-      <c r="E38" s="56" t="s">
-        <v>69</v>
-      </c>
-      <c r="F38" s="72" t="s">
-        <v>175</v>
-      </c>
-      <c r="G38" s="56" t="s">
-        <v>90</v>
-      </c>
-      <c r="H38" s="72" t="s">
-        <v>126</v>
-      </c>
-      <c r="I38" s="56" t="s">
-        <v>176</v>
-      </c>
-      <c r="J38" s="86" t="s">
-        <v>177</v>
-      </c>
-      <c r="K38" s="56" t="s">
-        <v>187</v>
-      </c>
-      <c r="L38" s="72">
-        <v>1</v>
-      </c>
-      <c r="M38" s="56">
-        <f t="shared" si="1"/>
-        <v>1000</v>
-      </c>
-      <c r="N38" s="72"/>
-      <c r="O38" s="102" t="s">
-        <v>152</v>
-      </c>
-      <c r="P38" s="98"/>
-      <c r="Q38" s="107">
-        <f>P38*N38</f>
-        <v>0</v>
-      </c>
-      <c r="R38" s="72"/>
-      <c r="S38" s="108"/>
-    </row>
-    <row r="39" spans="1:19" s="109" customFormat="1" ht="48.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A39" s="106"/>
-      <c r="B39" s="61">
+      <c r="P38" s="90">
+        <v>0.10050000000000001</v>
+      </c>
+      <c r="Q38" s="99">
+        <f t="shared" si="3"/>
+        <v>102.51</v>
+      </c>
+      <c r="R38" s="64"/>
+      <c r="S38" s="100"/>
+    </row>
+    <row r="39" spans="1:19" s="101" customFormat="1" ht="48.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A39" s="98"/>
+      <c r="B39" s="55">
         <f>ROW(B39) - ROW($B$9)</f>
         <v>30</v>
       </c>
-      <c r="C39" s="71"/>
-      <c r="D39" s="75" t="s">
+      <c r="C39" s="63" t="s">
+        <v>170</v>
+      </c>
+      <c r="D39" s="67" t="s">
         <v>39</v>
       </c>
-      <c r="E39" s="73" t="s">
+      <c r="E39" s="65" t="s">
         <v>70</v>
       </c>
-      <c r="F39" s="75" t="s">
+      <c r="F39" s="67" t="s">
         <v>175</v>
       </c>
-      <c r="G39" s="73" t="s">
+      <c r="G39" s="65" t="s">
         <v>91</v>
       </c>
-      <c r="H39" s="75" t="s">
+      <c r="H39" s="67" t="s">
         <v>127</v>
       </c>
-      <c r="I39" s="73" t="s">
-        <v>176</v>
-      </c>
-      <c r="J39" s="87" t="s">
+      <c r="I39" s="65" t="s">
+        <v>176</v>
+      </c>
+      <c r="J39" s="79" t="s">
         <v>178</v>
       </c>
-      <c r="K39" s="73" t="s">
+      <c r="K39" s="65" t="s">
         <v>188</v>
       </c>
-      <c r="L39" s="75">
+      <c r="L39" s="67">
         <v>2</v>
       </c>
-      <c r="M39" s="73">
-        <f t="shared" si="1"/>
+      <c r="M39" s="65">
+        <f t="shared" si="2"/>
         <v>2000</v>
       </c>
-      <c r="N39" s="75"/>
-      <c r="O39" s="115" t="s">
+      <c r="N39" s="67">
+        <v>2050</v>
+      </c>
+      <c r="O39" s="107" t="s">
         <v>152</v>
       </c>
-      <c r="P39" s="99"/>
-      <c r="Q39" s="113">
-        <f>P39*N39</f>
-        <v>0</v>
-      </c>
-      <c r="R39" s="75"/>
-      <c r="S39" s="114"/>
+      <c r="P39" s="91">
+        <v>4.0500000000000001E-2</v>
+      </c>
+      <c r="Q39" s="105">
+        <f t="shared" si="3"/>
+        <v>83.025000000000006</v>
+      </c>
+      <c r="R39" s="136" t="s">
+        <v>217</v>
+      </c>
+      <c r="S39" s="106"/>
     </row>
     <row r="40" spans="1:19" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A40" s="1"/>
-      <c r="B40" s="74"/>
-      <c r="C40" s="62"/>
-      <c r="D40" s="63"/>
-      <c r="E40" s="64"/>
-      <c r="F40" s="65"/>
-      <c r="G40" s="66"/>
-      <c r="H40" s="65"/>
-      <c r="I40" s="66"/>
-      <c r="J40" s="65"/>
-      <c r="K40" s="66"/>
-      <c r="L40" s="66"/>
-      <c r="M40" s="66"/>
+      <c r="B40" s="66"/>
+      <c r="C40" s="56"/>
+      <c r="D40" s="57"/>
+      <c r="E40" s="58"/>
+      <c r="F40" s="59"/>
+      <c r="G40" s="60"/>
+      <c r="H40" s="59"/>
+      <c r="I40" s="60"/>
+      <c r="J40" s="59"/>
+      <c r="K40" s="60"/>
+      <c r="L40" s="60"/>
+      <c r="M40" s="60"/>
       <c r="N40" s="134" t="s">
         <v>209</v>
       </c>
       <c r="O40" s="135"/>
       <c r="P40" s="135"/>
-      <c r="Q40" s="136" t="e">
-        <f>SUM(#REF!)</f>
-        <v>#REF!</v>
-      </c>
-      <c r="R40" s="67"/>
-      <c r="S40" s="68"/>
+      <c r="Q40" s="124">
+        <f>SUM(Q10:Q39)</f>
+        <v>38220.392</v>
+      </c>
+      <c r="R40" s="130"/>
+      <c r="S40" s="131"/>
     </row>
     <row r="41" spans="1:19" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A41" s="1"/>
@@ -6011,12 +6273,15 @@
       </c>
       <c r="O41" s="135"/>
       <c r="P41" s="135"/>
-      <c r="Q41" s="137" t="e">
-        <f>Q40/5</f>
-        <v>#REF!</v>
-      </c>
-      <c r="R41" s="53"/>
-      <c r="S41" s="54"/>
+      <c r="Q41" s="125">
+        <f>Q40/1000</f>
+        <v>38.220391999999997</v>
+      </c>
+      <c r="R41" s="132"/>
+      <c r="S41" s="133"/>
+    </row>
+    <row r="43" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="P43" s="138"/>
     </row>
   </sheetData>
   <mergeCells count="5">
@@ -6026,8 +6291,8 @@
     <mergeCell ref="N40:P40"/>
     <mergeCell ref="N41:P41"/>
   </mergeCells>
-  <conditionalFormatting sqref="O13 O25 O31 O33 O35 O15 O17 O19">
-    <cfRule type="dataBar" priority="5">
+  <conditionalFormatting sqref="O13 O31 O33 O15 O17 O19">
+    <cfRule type="dataBar" priority="6">
       <dataBar>
         <cfvo type="min"/>
         <cfvo type="max"/>
@@ -6041,7 +6306,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="O21:O22">
-    <cfRule type="dataBar" priority="4">
+    <cfRule type="dataBar" priority="5">
       <dataBar>
         <cfvo type="min"/>
         <cfvo type="max"/>
@@ -6055,7 +6320,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="O37">
-    <cfRule type="dataBar" priority="3">
+    <cfRule type="dataBar" priority="4">
       <dataBar>
         <cfvo type="min"/>
         <cfvo type="max"/>
@@ -6069,7 +6334,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="O39">
-    <cfRule type="dataBar" priority="2">
+    <cfRule type="dataBar" priority="3">
       <dataBar>
         <cfvo type="min"/>
         <cfvo type="max"/>
@@ -6083,6 +6348,20 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="O11">
+    <cfRule type="dataBar" priority="2">
+      <dataBar>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="FF638EC6"/>
+      </dataBar>
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
+          <x14:id>{091C421B-9F30-42F5-8771-D2F3CEDE36ED}</x14:id>
+        </ext>
+      </extLst>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="O35">
     <cfRule type="dataBar" priority="1">
       <dataBar>
         <cfvo type="min"/>
@@ -6091,7 +6370,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{091C421B-9F30-42F5-8771-D2F3CEDE36ED}</x14:id>
+          <x14:id>{8F5790F9-3EFC-4FD8-AC02-A33DAF194EC9}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -6121,12 +6400,10 @@
     <hyperlink ref="O24" r:id="rId22" xr:uid="{9768DC2D-5687-4B0D-BDA7-404F744B5E2B}"/>
     <hyperlink ref="O26" r:id="rId23" xr:uid="{61E1E6A6-4B08-476D-AAC0-043E86BF3138}"/>
     <hyperlink ref="O30" r:id="rId24" xr:uid="{82227681-4BC0-4ED4-BC31-2CAE976DF066}"/>
-    <hyperlink ref="O32" r:id="rId25" xr:uid="{7DDC25CB-CAFA-48CA-8C35-40D812D1C462}"/>
-    <hyperlink ref="O33" r:id="rId26" xr:uid="{576AD24A-02FB-46B1-8334-C2DC948AFD2D}"/>
-    <hyperlink ref="O36" r:id="rId27" xr:uid="{C9104653-C330-4548-8691-0766A17FEC19}"/>
+    <hyperlink ref="O36" r:id="rId25" xr:uid="{C9104653-C330-4548-8691-0766A17FEC19}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId28"/>
+  <drawing r:id="rId26"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
@@ -6141,7 +6418,7 @@
               <x14:axisColor rgb="FF000000"/>
             </x14:dataBar>
           </x14:cfRule>
-          <xm:sqref>O13 O25 O31 O33 O35 O15 O17 O19</xm:sqref>
+          <xm:sqref>O13 O31 O33 O15 O17 O19</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
           <x14:cfRule type="dataBar" id="{25B37203-BC10-4A2E-9962-FBD4D106E38D}">
@@ -6195,6 +6472,19 @@
           </x14:cfRule>
           <xm:sqref>O11</xm:sqref>
         </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="dataBar" id="{8F5790F9-3EFC-4FD8-AC02-A33DAF194EC9}">
+            <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
+              <x14:cfvo type="autoMin"/>
+              <x14:cfvo type="autoMax"/>
+              <x14:borderColor rgb="FF638EC6"/>
+              <x14:negativeFillColor rgb="FFFF0000"/>
+              <x14:negativeBorderColor rgb="FFFF0000"/>
+              <x14:axisColor rgb="FF000000"/>
+            </x14:dataBar>
+          </x14:cfRule>
+          <xm:sqref>O35</xm:sqref>
+        </x14:conditionalFormatting>
       </x14:conditionalFormattings>
     </ext>
   </extLst>
@@ -6203,7 +6493,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{66942F49-9E9D-40E5-8442-6D9FA1F2D4FE}">
-  <dimension ref="A1:S41"/>
+  <dimension ref="A1:X41"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="3" bestFit="1" customWidth="1"/>
@@ -6219,13 +6509,15 @@
     <col min="12" max="12" width="8.7109375" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="21.42578125" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="18.28515625" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="15.7109375" bestFit="1" customWidth="1"/>
     <col min="16" max="16" width="21.85546875" bestFit="1" customWidth="1"/>
     <col min="17" max="17" width="22.42578125" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="8.5703125" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="15.85546875" customWidth="1"/>
     <col min="19" max="19" width="26.140625" customWidth="1"/>
+    <col min="22" max="22" width="22.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:24" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1"/>
       <c r="B1" s="20"/>
       <c r="C1" s="20"/>
@@ -6236,17 +6528,17 @@
       <c r="H1" s="2"/>
       <c r="I1" s="2"/>
       <c r="J1" s="2"/>
-      <c r="K1" s="49"/>
-      <c r="L1" s="49"/>
-      <c r="M1" s="49"/>
-      <c r="N1" s="49"/>
-      <c r="O1" s="49"/>
-      <c r="P1" s="49"/>
-      <c r="Q1" s="49"/>
-      <c r="R1" s="49"/>
-      <c r="S1" s="50"/>
-    </row>
-    <row r="2" spans="1:19" ht="32.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="K1" s="126"/>
+      <c r="L1" s="126"/>
+      <c r="M1" s="126"/>
+      <c r="N1" s="126"/>
+      <c r="O1" s="126"/>
+      <c r="P1" s="126"/>
+      <c r="Q1" s="126"/>
+      <c r="R1" s="126"/>
+      <c r="S1" s="127"/>
+    </row>
+    <row r="2" spans="1:24" ht="32.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1"/>
       <c r="B2" s="21"/>
       <c r="C2" s="32"/>
@@ -6271,7 +6563,7 @@
       <c r="R2" s="4"/>
       <c r="S2" s="3"/>
     </row>
-    <row r="3" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A3" s="1"/>
       <c r="B3" s="22"/>
       <c r="C3" s="33"/>
@@ -6294,9 +6586,9 @@
       <c r="P3" s="5"/>
       <c r="Q3" s="5"/>
       <c r="R3" s="5"/>
-      <c r="S3" s="51"/>
-    </row>
-    <row r="4" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="S3" s="128"/>
+    </row>
+    <row r="4" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A4" s="1"/>
       <c r="B4" s="22"/>
       <c r="C4" s="33"/>
@@ -6319,9 +6611,9 @@
       <c r="P4" s="6"/>
       <c r="Q4" s="6"/>
       <c r="R4" s="6"/>
-      <c r="S4" s="52"/>
-    </row>
-    <row r="5" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="S4" s="129"/>
+    </row>
+    <row r="5" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A5" s="1"/>
       <c r="B5" s="22"/>
       <c r="C5" s="33"/>
@@ -6344,9 +6636,9 @@
       <c r="P5" s="6"/>
       <c r="Q5" s="6"/>
       <c r="R5" s="6"/>
-      <c r="S5" s="52"/>
-    </row>
-    <row r="6" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="S5" s="129"/>
+    </row>
+    <row r="6" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A6" s="1"/>
       <c r="B6" s="23"/>
       <c r="C6" s="34"/>
@@ -6365,9 +6657,9 @@
       <c r="P6" s="6"/>
       <c r="Q6" s="6"/>
       <c r="R6" s="6"/>
-      <c r="S6" s="52"/>
-    </row>
-    <row r="7" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="S6" s="129"/>
+    </row>
+    <row r="7" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A7" s="1"/>
       <c r="B7" s="24"/>
       <c r="C7" s="35"/>
@@ -6386,9 +6678,9 @@
       <c r="P7" s="8"/>
       <c r="Q7" s="8"/>
       <c r="R7" s="8"/>
-      <c r="S7" s="52"/>
-    </row>
-    <row r="8" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="S7" s="129"/>
+    </row>
+    <row r="8" spans="1:24" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" s="1"/>
       <c r="B8" s="27"/>
       <c r="C8" s="36"/>
@@ -6407,11 +6699,11 @@
       <c r="P8" s="8"/>
       <c r="Q8" s="8"/>
       <c r="R8" s="8"/>
-      <c r="S8" s="52"/>
-    </row>
-    <row r="9" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="S8" s="129"/>
+    </row>
+    <row r="9" spans="1:24" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A9" s="1"/>
-      <c r="B9" s="55" t="s">
+      <c r="B9" s="49" t="s">
         <v>4</v>
       </c>
       <c r="C9" s="30" t="s">
@@ -6459,72 +6751,76 @@
       <c r="Q9" s="30" t="s">
         <v>208</v>
       </c>
-      <c r="R9" s="31" t="s">
+      <c r="R9" s="30" t="s">
         <v>149</v>
       </c>
       <c r="S9" s="30" t="s">
         <v>150</v>
       </c>
     </row>
-    <row r="10" spans="1:19" s="124" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="117"/>
-      <c r="B10" s="118">
+    <row r="10" spans="1:24" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="1"/>
+      <c r="B10" s="109">
         <f>ROW(B10) - ROW($B$9)</f>
         <v>1</v>
       </c>
-      <c r="C10" s="119" t="s">
+      <c r="C10" s="110" t="s">
         <v>7</v>
       </c>
-      <c r="D10" s="120" t="s">
+      <c r="D10" s="111" t="s">
         <v>11</v>
       </c>
-      <c r="E10" s="121" t="s">
+      <c r="E10" s="112" t="s">
         <v>41</v>
       </c>
-      <c r="F10" s="120" t="s">
+      <c r="F10" s="111" t="s">
         <v>72</v>
       </c>
-      <c r="G10" s="121" t="s">
+      <c r="G10" s="112" t="s">
         <v>93</v>
       </c>
-      <c r="H10" s="120" t="s">
+      <c r="H10" s="111" t="s">
         <v>113</v>
       </c>
       <c r="I10" s="38" t="s">
         <v>176</v>
       </c>
-      <c r="J10" s="79" t="s">
+      <c r="J10" s="71" t="s">
         <v>146</v>
       </c>
       <c r="K10" s="38" t="s">
         <v>131</v>
       </c>
-      <c r="L10" s="120">
+      <c r="L10" s="111">
         <v>1</v>
       </c>
-      <c r="M10" s="121">
+      <c r="M10" s="112">
         <f>L10*5000</f>
         <v>5000</v>
       </c>
-      <c r="N10" s="120"/>
-      <c r="O10" s="102" t="s">
+      <c r="N10" s="111">
+        <v>5200</v>
+      </c>
+      <c r="O10" s="94" t="s">
         <v>152</v>
       </c>
-      <c r="P10" s="122"/>
-      <c r="Q10" s="123">
-        <f>P10*N10</f>
-        <v>0</v>
-      </c>
-      <c r="R10" s="120"/>
+      <c r="P10" s="113">
+        <v>1.0800000000000001E-2</v>
+      </c>
+      <c r="Q10" s="114">
+        <f t="shared" ref="Q10:Q30" si="0">P10*N10</f>
+        <v>56.160000000000004</v>
+      </c>
+      <c r="R10" s="112"/>
       <c r="S10" s="43"/>
     </row>
-    <row r="11" spans="1:19" s="109" customFormat="1" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="106"/>
-      <c r="B11" s="61">
-        <f t="shared" ref="B11:B38" si="0">ROW(B11) - ROW($B$9)</f>
+    <row r="11" spans="1:24" s="101" customFormat="1" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="98"/>
+      <c r="B11" s="55">
+        <f t="shared" ref="B11:B38" si="1">ROW(B11) - ROW($B$9)</f>
         <v>2</v>
       </c>
-      <c r="C11" s="59" t="s">
+      <c r="C11" s="53" t="s">
         <v>7</v>
       </c>
       <c r="D11" s="41" t="s">
@@ -6555,80 +6851,91 @@
         <v>17</v>
       </c>
       <c r="M11" s="40">
-        <f t="shared" ref="M11:M39" si="1">L11*5000</f>
+        <f t="shared" ref="M11:M39" si="2">L11*5000</f>
         <v>85000</v>
       </c>
-      <c r="N11" s="41"/>
-      <c r="O11" s="88" t="s">
+      <c r="N11" s="41">
+        <v>85200</v>
+      </c>
+      <c r="O11" s="80" t="s">
         <v>152</v>
       </c>
-      <c r="P11" s="97"/>
-      <c r="Q11" s="110">
-        <f>P11*N11</f>
-        <v>0</v>
-      </c>
-      <c r="R11" s="41"/>
-      <c r="S11" s="111"/>
-    </row>
-    <row r="12" spans="1:19" s="124" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="117"/>
-      <c r="B12" s="125">
+      <c r="P11" s="89">
+        <v>2.7000000000000001E-3</v>
+      </c>
+      <c r="Q11" s="102">
+        <f t="shared" si="0"/>
+        <v>230.04000000000002</v>
+      </c>
+      <c r="R11" s="40"/>
+      <c r="S11" s="103"/>
+      <c r="X11"/>
+    </row>
+    <row r="12" spans="1:24" s="101" customFormat="1" ht="39" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="98"/>
+      <c r="B12" s="55">
         <f>ROW(B12) - ROW($B$9)</f>
         <v>3</v>
       </c>
-      <c r="C12" s="130" t="s">
+      <c r="C12" s="62" t="s">
         <v>7</v>
       </c>
-      <c r="D12" s="131" t="s">
+      <c r="D12" s="64" t="s">
         <v>13</v>
       </c>
-      <c r="E12" s="132" t="s">
+      <c r="E12" s="50" t="s">
         <v>43</v>
       </c>
-      <c r="F12" s="131" t="s">
+      <c r="F12" s="64" t="s">
         <v>73</v>
       </c>
-      <c r="G12" s="132" t="s">
+      <c r="G12" s="50" t="s">
         <v>95</v>
       </c>
-      <c r="H12" s="131" t="s">
+      <c r="H12" s="64" t="s">
         <v>114</v>
       </c>
-      <c r="I12" s="56" t="s">
-        <v>176</v>
-      </c>
-      <c r="J12" s="80" t="s">
+      <c r="I12" s="50" t="s">
+        <v>176</v>
+      </c>
+      <c r="J12" s="78" t="s">
         <v>154</v>
       </c>
-      <c r="K12" s="56" t="s">
+      <c r="K12" s="50" t="s">
         <v>133</v>
       </c>
-      <c r="L12" s="131">
+      <c r="L12" s="64">
         <v>8</v>
       </c>
-      <c r="M12" s="132">
+      <c r="M12" s="50">
+        <f t="shared" si="2"/>
+        <v>40000</v>
+      </c>
+      <c r="N12" s="64">
+        <v>40200</v>
+      </c>
+      <c r="O12" s="146" t="s">
+        <v>152</v>
+      </c>
+      <c r="P12" s="90">
+        <v>1.5E-3</v>
+      </c>
+      <c r="Q12" s="99">
+        <f t="shared" si="0"/>
+        <v>60.300000000000004</v>
+      </c>
+      <c r="R12" s="148" t="s">
+        <v>218</v>
+      </c>
+      <c r="S12" s="100"/>
+    </row>
+    <row r="13" spans="1:24" s="101" customFormat="1" ht="39" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="98"/>
+      <c r="B13" s="55">
         <f t="shared" si="1"/>
-        <v>40000</v>
-      </c>
-      <c r="N12" s="131"/>
-      <c r="O12" s="102" t="s">
-        <v>152</v>
-      </c>
-      <c r="P12" s="133"/>
-      <c r="Q12" s="94">
-        <f>P12*N12</f>
-        <v>0</v>
-      </c>
-      <c r="R12" s="131"/>
-      <c r="S12" s="100"/>
-    </row>
-    <row r="13" spans="1:19" s="109" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="106"/>
-      <c r="B13" s="61">
-        <f t="shared" si="0"/>
         <v>4</v>
       </c>
-      <c r="C13" s="59" t="s">
+      <c r="C13" s="53" t="s">
         <v>7</v>
       </c>
       <c r="D13" s="41" t="s">
@@ -6659,95 +6966,106 @@
         <v>2</v>
       </c>
       <c r="M13" s="40">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>10000</v>
       </c>
-      <c r="N13" s="41"/>
-      <c r="O13" s="88" t="s">
+      <c r="N13" s="41">
+        <v>10100</v>
+      </c>
+      <c r="O13" s="147" t="s">
         <v>152</v>
       </c>
-      <c r="P13" s="97"/>
-      <c r="Q13" s="110">
-        <f>P13*N13</f>
-        <v>0</v>
-      </c>
-      <c r="R13" s="41"/>
-      <c r="S13" s="111"/>
-    </row>
-    <row r="14" spans="1:19" s="109" customFormat="1" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="106"/>
-      <c r="B14" s="61">
+      <c r="P13" s="89">
+        <v>1.1661999999999999</v>
+      </c>
+      <c r="Q13" s="102">
+        <f t="shared" si="0"/>
+        <v>11778.619999999999</v>
+      </c>
+      <c r="R13" s="149" t="s">
+        <v>218</v>
+      </c>
+      <c r="S13" s="103"/>
+    </row>
+    <row r="14" spans="1:24" s="101" customFormat="1" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="98"/>
+      <c r="B14" s="55">
         <f>ROW(B14) - ROW($B$9)</f>
         <v>5</v>
       </c>
-      <c r="C14" s="70" t="s">
+      <c r="C14" s="62" t="s">
         <v>7</v>
       </c>
-      <c r="D14" s="72" t="s">
+      <c r="D14" s="64" t="s">
         <v>15</v>
       </c>
-      <c r="E14" s="56" t="s">
+      <c r="E14" s="50" t="s">
         <v>45</v>
       </c>
-      <c r="F14" s="72" t="s">
+      <c r="F14" s="64" t="s">
         <v>72</v>
       </c>
-      <c r="G14" s="56" t="s">
+      <c r="G14" s="50" t="s">
         <v>97</v>
       </c>
-      <c r="H14" s="72" t="s">
+      <c r="H14" s="64" t="s">
         <v>114</v>
       </c>
-      <c r="I14" s="56" t="s">
-        <v>176</v>
-      </c>
-      <c r="J14" s="80" t="s">
+      <c r="I14" s="50" t="s">
+        <v>176</v>
+      </c>
+      <c r="J14" s="72" t="s">
         <v>155</v>
       </c>
-      <c r="K14" s="56" t="s">
+      <c r="K14" s="50" t="s">
         <v>135</v>
       </c>
-      <c r="L14" s="72">
+      <c r="L14" s="64">
         <v>12</v>
       </c>
-      <c r="M14" s="132">
+      <c r="M14" s="122">
+        <f t="shared" si="2"/>
+        <v>60000</v>
+      </c>
+      <c r="N14" s="64">
+        <v>60200</v>
+      </c>
+      <c r="O14" s="94" t="s">
+        <v>152</v>
+      </c>
+      <c r="P14" s="90">
+        <v>3.2000000000000002E-3</v>
+      </c>
+      <c r="Q14" s="99">
+        <f t="shared" si="0"/>
+        <v>192.64000000000001</v>
+      </c>
+      <c r="R14" s="50"/>
+      <c r="S14" s="100"/>
+      <c r="X14"/>
+    </row>
+    <row r="15" spans="1:24" ht="39" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="1"/>
+      <c r="B15" s="115">
         <f t="shared" si="1"/>
-        <v>60000</v>
-      </c>
-      <c r="N14" s="72"/>
-      <c r="O14" s="102" t="s">
-        <v>152</v>
-      </c>
-      <c r="P14" s="98"/>
-      <c r="Q14" s="107">
-        <f>P14*N14</f>
-        <v>0</v>
-      </c>
-      <c r="R14" s="72"/>
-      <c r="S14" s="108"/>
-    </row>
-    <row r="15" spans="1:19" s="124" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="117"/>
-      <c r="B15" s="125">
-        <f t="shared" si="0"/>
         <v>6</v>
       </c>
-      <c r="C15" s="126" t="s">
+      <c r="C15" s="116" t="s">
         <v>7</v>
       </c>
-      <c r="D15" s="127" t="s">
+      <c r="D15" s="117" t="s">
         <v>16</v>
       </c>
-      <c r="E15" s="128" t="s">
+      <c r="E15" s="118" t="s">
         <v>46</v>
       </c>
-      <c r="F15" s="127" t="s">
+      <c r="F15" s="117" t="s">
         <v>72</v>
       </c>
-      <c r="G15" s="128" t="s">
+      <c r="G15" s="118" t="s">
         <v>98</v>
       </c>
-      <c r="H15" s="127" t="s">
+      <c r="H15" s="117" t="s">
         <v>116</v>
       </c>
       <c r="I15" s="40" t="s">
@@ -6759,84 +7077,94 @@
       <c r="K15" s="40" t="s">
         <v>136</v>
       </c>
-      <c r="L15" s="127">
+      <c r="L15" s="117">
         <v>1</v>
       </c>
       <c r="M15" s="40">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>5000</v>
       </c>
-      <c r="N15" s="127"/>
-      <c r="O15" s="88" t="s">
+      <c r="N15" s="117">
+        <v>5100</v>
+      </c>
+      <c r="O15" s="80" t="s">
         <v>152</v>
       </c>
-      <c r="P15" s="129"/>
-      <c r="Q15" s="93">
-        <f>P15*N15</f>
-        <v>0</v>
-      </c>
-      <c r="R15" s="127"/>
+      <c r="P15" s="119">
+        <v>1.9199999999999998E-2</v>
+      </c>
+      <c r="Q15" s="85">
+        <f t="shared" si="0"/>
+        <v>97.919999999999987</v>
+      </c>
+      <c r="R15" s="149" t="s">
+        <v>218</v>
+      </c>
       <c r="S15" s="44"/>
     </row>
-    <row r="16" spans="1:19" s="124" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="117"/>
-      <c r="B16" s="125">
+    <row r="16" spans="1:24" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="1"/>
+      <c r="B16" s="115">
         <f>ROW(B16) - ROW($B$9)</f>
         <v>7</v>
       </c>
-      <c r="C16" s="130" t="s">
+      <c r="C16" s="120" t="s">
         <v>7</v>
       </c>
-      <c r="D16" s="131" t="s">
+      <c r="D16" s="121" t="s">
         <v>17</v>
       </c>
-      <c r="E16" s="132" t="s">
+      <c r="E16" s="122" t="s">
         <v>47</v>
       </c>
-      <c r="F16" s="131" t="s">
+      <c r="F16" s="121" t="s">
         <v>72</v>
       </c>
-      <c r="G16" s="132" t="s">
+      <c r="G16" s="122" t="s">
         <v>99</v>
       </c>
-      <c r="H16" s="131" t="s">
+      <c r="H16" s="121" t="s">
         <v>114</v>
       </c>
-      <c r="I16" s="56" t="s">
-        <v>176</v>
-      </c>
-      <c r="J16" s="80" t="s">
+      <c r="I16" s="50" t="s">
+        <v>176</v>
+      </c>
+      <c r="J16" s="72" t="s">
         <v>157</v>
       </c>
-      <c r="K16" s="56" t="s">
+      <c r="K16" s="50" t="s">
         <v>137</v>
       </c>
-      <c r="L16" s="131">
+      <c r="L16" s="121">
         <v>6</v>
       </c>
-      <c r="M16" s="132">
+      <c r="M16" s="122">
+        <f t="shared" si="2"/>
+        <v>30000</v>
+      </c>
+      <c r="N16" s="121">
+        <v>30200</v>
+      </c>
+      <c r="O16" s="94" t="s">
+        <v>152</v>
+      </c>
+      <c r="P16" s="123">
+        <v>1.6999999999999999E-3</v>
+      </c>
+      <c r="Q16" s="86">
+        <f t="shared" si="0"/>
+        <v>51.339999999999996</v>
+      </c>
+      <c r="R16" s="122"/>
+      <c r="S16" s="92"/>
+    </row>
+    <row r="17" spans="1:24" s="101" customFormat="1" ht="39" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="98"/>
+      <c r="B17" s="55">
         <f t="shared" si="1"/>
-        <v>30000</v>
-      </c>
-      <c r="N16" s="131"/>
-      <c r="O16" s="102" t="s">
-        <v>152</v>
-      </c>
-      <c r="P16" s="133"/>
-      <c r="Q16" s="94">
-        <f>P16*N16</f>
-        <v>0</v>
-      </c>
-      <c r="R16" s="131"/>
-      <c r="S16" s="100"/>
-    </row>
-    <row r="17" spans="1:19" s="109" customFormat="1" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="106"/>
-      <c r="B17" s="61">
-        <f t="shared" si="0"/>
         <v>8</v>
       </c>
-      <c r="C17" s="59" t="s">
+      <c r="C17" s="53" t="s">
         <v>7</v>
       </c>
       <c r="D17" s="41" t="s">
@@ -6867,95 +7195,107 @@
         <v>16</v>
       </c>
       <c r="M17" s="40">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>80000</v>
       </c>
-      <c r="N17" s="41"/>
-      <c r="O17" s="88" t="s">
+      <c r="N17" s="41">
+        <v>80200</v>
+      </c>
+      <c r="O17" s="80" t="s">
         <v>152</v>
       </c>
-      <c r="P17" s="97"/>
-      <c r="Q17" s="110">
-        <f>P17*N17</f>
-        <v>0</v>
-      </c>
-      <c r="R17" s="41"/>
-      <c r="S17" s="111"/>
-    </row>
-    <row r="18" spans="1:19" s="109" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="106"/>
-      <c r="B18" s="61">
+      <c r="P17" s="89">
+        <v>5.1000000000000004E-3</v>
+      </c>
+      <c r="Q17" s="102">
+        <f t="shared" si="0"/>
+        <v>409.02000000000004</v>
+      </c>
+      <c r="R17" s="149" t="s">
+        <v>218</v>
+      </c>
+      <c r="S17" s="103"/>
+      <c r="X17"/>
+    </row>
+    <row r="18" spans="1:24" s="101" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="98"/>
+      <c r="B18" s="55">
         <f>ROW(B18) - ROW($B$9)</f>
         <v>9</v>
       </c>
-      <c r="C18" s="70" t="s">
+      <c r="C18" s="62" t="s">
         <v>7</v>
       </c>
-      <c r="D18" s="72" t="s">
+      <c r="D18" s="64" t="s">
         <v>159</v>
       </c>
-      <c r="E18" s="56" t="s">
+      <c r="E18" s="50" t="s">
         <v>49</v>
       </c>
-      <c r="F18" s="72" t="s">
+      <c r="F18" s="64" t="s">
         <v>72</v>
       </c>
-      <c r="G18" s="56" t="s">
+      <c r="G18" s="50" t="s">
         <v>101</v>
       </c>
-      <c r="H18" s="72" t="s">
+      <c r="H18" s="64" t="s">
         <v>113</v>
       </c>
-      <c r="I18" s="56" t="s">
-        <v>176</v>
-      </c>
-      <c r="J18" s="80" t="s">
+      <c r="I18" s="50" t="s">
+        <v>176</v>
+      </c>
+      <c r="J18" s="72" t="s">
         <v>193</v>
       </c>
-      <c r="K18" s="56" t="s">
+      <c r="K18" s="50" t="s">
         <v>139</v>
       </c>
-      <c r="L18" s="72">
+      <c r="L18" s="64">
         <v>3</v>
       </c>
-      <c r="M18" s="132">
-        <f t="shared" si="1"/>
+      <c r="M18" s="122">
+        <f t="shared" si="2"/>
         <v>15000</v>
       </c>
-      <c r="N18" s="72"/>
-      <c r="O18" s="102" t="s">
+      <c r="N18" s="64">
+        <v>15200</v>
+      </c>
+      <c r="O18" s="94" t="s">
         <v>152</v>
       </c>
-      <c r="P18" s="98"/>
-      <c r="Q18" s="107">
-        <f>P18*N18</f>
-        <v>0</v>
-      </c>
-      <c r="R18" s="72"/>
-      <c r="S18" s="108"/>
-    </row>
-    <row r="19" spans="1:19" s="124" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="117"/>
-      <c r="B19" s="125">
+      <c r="P18" s="90">
+        <v>1.3299999999999999E-2</v>
+      </c>
+      <c r="Q18" s="99">
+        <f t="shared" si="0"/>
+        <v>202.16</v>
+      </c>
+      <c r="R18" s="50"/>
+      <c r="S18" s="100"/>
+      <c r="X18"/>
+    </row>
+    <row r="19" spans="1:24" ht="39" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A19" s="1"/>
+      <c r="B19" s="115">
         <f>ROW(B19) - ROW($B$9)</f>
         <v>10</v>
       </c>
-      <c r="C19" s="126" t="s">
+      <c r="C19" s="116" t="s">
         <v>7</v>
       </c>
-      <c r="D19" s="127" t="s">
+      <c r="D19" s="117" t="s">
         <v>19</v>
       </c>
-      <c r="E19" s="128" t="s">
+      <c r="E19" s="118" t="s">
         <v>50</v>
       </c>
-      <c r="F19" s="127" t="s">
+      <c r="F19" s="117" t="s">
         <v>72</v>
       </c>
-      <c r="G19" s="128" t="s">
+      <c r="G19" s="118" t="s">
         <v>102</v>
       </c>
-      <c r="H19" s="127" t="s">
+      <c r="H19" s="117" t="s">
         <v>114</v>
       </c>
       <c r="I19" s="40" t="s">
@@ -6967,84 +7307,97 @@
       <c r="K19" s="40" t="s">
         <v>140</v>
       </c>
-      <c r="L19" s="127">
+      <c r="L19" s="117">
         <v>1</v>
       </c>
       <c r="M19" s="40">
+        <f t="shared" si="2"/>
+        <v>5000</v>
+      </c>
+      <c r="N19" s="117">
+        <v>5100</v>
+      </c>
+      <c r="O19" s="80" t="s">
+        <v>152</v>
+      </c>
+      <c r="P19" s="119">
+        <v>2.2000000000000001E-3</v>
+      </c>
+      <c r="Q19" s="85">
+        <f t="shared" si="0"/>
+        <v>11.22</v>
+      </c>
+      <c r="R19" s="149" t="s">
+        <v>218</v>
+      </c>
+      <c r="S19" s="44"/>
+    </row>
+    <row r="20" spans="1:24" s="101" customFormat="1" ht="39" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A20" s="98"/>
+      <c r="B20" s="55">
         <f t="shared" si="1"/>
-        <v>5000</v>
-      </c>
-      <c r="N19" s="127"/>
-      <c r="O19" s="88" t="s">
+        <v>11</v>
+      </c>
+      <c r="C20" s="62" t="s">
+        <v>7</v>
+      </c>
+      <c r="D20" s="64" t="s">
+        <v>20</v>
+      </c>
+      <c r="E20" s="50" t="s">
+        <v>51</v>
+      </c>
+      <c r="F20" s="64" t="s">
+        <v>75</v>
+      </c>
+      <c r="G20" s="50" t="s">
+        <v>103</v>
+      </c>
+      <c r="H20" s="64" t="s">
+        <v>116</v>
+      </c>
+      <c r="I20" s="50" t="s">
+        <v>176</v>
+      </c>
+      <c r="J20" s="72" t="s">
+        <v>194</v>
+      </c>
+      <c r="K20" s="50" t="s">
+        <v>139</v>
+      </c>
+      <c r="L20" s="64">
+        <v>16</v>
+      </c>
+      <c r="M20" s="122">
+        <f t="shared" si="2"/>
+        <v>80000</v>
+      </c>
+      <c r="N20" s="64">
+        <v>80200</v>
+      </c>
+      <c r="O20" s="94" t="s">
         <v>152</v>
       </c>
-      <c r="P19" s="129"/>
-      <c r="Q19" s="93">
-        <f>P19*N19</f>
-        <v>0</v>
-      </c>
-      <c r="R19" s="127"/>
-      <c r="S19" s="44"/>
-    </row>
-    <row r="20" spans="1:19" s="109" customFormat="1" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="106"/>
-      <c r="B20" s="61">
+      <c r="P20" s="90">
+        <v>4.5999999999999999E-2</v>
+      </c>
+      <c r="Q20" s="99">
         <f t="shared" si="0"/>
-        <v>11</v>
-      </c>
-      <c r="C20" s="70" t="s">
-        <v>7</v>
-      </c>
-      <c r="D20" s="72" t="s">
-        <v>20</v>
-      </c>
-      <c r="E20" s="56" t="s">
-        <v>51</v>
-      </c>
-      <c r="F20" s="72" t="s">
-        <v>75</v>
-      </c>
-      <c r="G20" s="56" t="s">
-        <v>103</v>
-      </c>
-      <c r="H20" s="72" t="s">
-        <v>116</v>
-      </c>
-      <c r="I20" s="56" t="s">
-        <v>176</v>
-      </c>
-      <c r="J20" s="80" t="s">
-        <v>194</v>
-      </c>
-      <c r="K20" s="56" t="s">
-        <v>139</v>
-      </c>
-      <c r="L20" s="72">
-        <v>16</v>
-      </c>
-      <c r="M20" s="132">
-        <f t="shared" si="1"/>
-        <v>80000</v>
-      </c>
-      <c r="N20" s="72"/>
-      <c r="O20" s="102" t="s">
-        <v>152</v>
-      </c>
-      <c r="P20" s="98"/>
-      <c r="Q20" s="107">
-        <f>P20*N20</f>
-        <v>0</v>
-      </c>
-      <c r="R20" s="72"/>
-      <c r="S20" s="108"/>
-    </row>
-    <row r="21" spans="1:19" s="109" customFormat="1" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="106"/>
-      <c r="B21" s="61">
+        <v>3689.2</v>
+      </c>
+      <c r="R20" s="148" t="s">
+        <v>218</v>
+      </c>
+      <c r="S20" s="100"/>
+      <c r="X20"/>
+    </row>
+    <row r="21" spans="1:24" s="101" customFormat="1" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A21" s="98"/>
+      <c r="B21" s="55">
         <f>ROW(B21) - ROW($B$9)</f>
         <v>12</v>
       </c>
-      <c r="C21" s="59" t="s">
+      <c r="C21" s="53" t="s">
         <v>163</v>
       </c>
       <c r="D21" s="41" t="s">
@@ -7053,7 +7406,7 @@
       <c r="E21" s="40" t="s">
         <v>52</v>
       </c>
-      <c r="F21" s="76" t="s">
+      <c r="F21" s="68" t="s">
         <v>171</v>
       </c>
       <c r="G21" s="40" t="s">
@@ -7075,80 +7428,90 @@
         <v>1</v>
       </c>
       <c r="M21" s="40">
+        <f t="shared" si="2"/>
+        <v>5000</v>
+      </c>
+      <c r="N21" s="41">
+        <v>5100</v>
+      </c>
+      <c r="O21" s="80" t="s">
+        <v>152</v>
+      </c>
+      <c r="P21" s="89">
+        <v>2.58E-2</v>
+      </c>
+      <c r="Q21" s="102">
+        <f t="shared" si="0"/>
+        <v>131.58000000000001</v>
+      </c>
+      <c r="R21" s="40"/>
+      <c r="S21" s="103"/>
+      <c r="X21"/>
+    </row>
+    <row r="22" spans="1:24" s="101" customFormat="1" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A22" s="98"/>
+      <c r="B22" s="55">
         <f t="shared" si="1"/>
+        <v>13</v>
+      </c>
+      <c r="C22" s="62" t="s">
+        <v>163</v>
+      </c>
+      <c r="D22" s="64" t="s">
+        <v>22</v>
+      </c>
+      <c r="E22" s="50" t="s">
+        <v>53</v>
+      </c>
+      <c r="F22" s="64" t="s">
+        <v>77</v>
+      </c>
+      <c r="G22" s="50" t="s">
+        <v>104</v>
+      </c>
+      <c r="H22" s="64" t="s">
+        <v>118</v>
+      </c>
+      <c r="I22" s="50" t="s">
+        <v>176</v>
+      </c>
+      <c r="J22" s="72" t="s">
+        <v>173</v>
+      </c>
+      <c r="K22" s="50" t="s">
+        <v>176</v>
+      </c>
+      <c r="L22" s="64">
+        <v>1</v>
+      </c>
+      <c r="M22" s="122">
+        <f t="shared" si="2"/>
         <v>5000</v>
       </c>
-      <c r="N21" s="41"/>
-      <c r="O21" s="88" t="s">
+      <c r="N22" s="64">
+        <v>5100</v>
+      </c>
+      <c r="O22" s="81" t="s">
         <v>152</v>
       </c>
-      <c r="P21" s="97"/>
-      <c r="Q21" s="110">
-        <f>P21*N21</f>
-        <v>0</v>
-      </c>
-      <c r="R21" s="41"/>
-      <c r="S21" s="111"/>
-    </row>
-    <row r="22" spans="1:19" s="109" customFormat="1" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="106"/>
-      <c r="B22" s="61">
+      <c r="P22" s="90">
+        <v>1.95E-2</v>
+      </c>
+      <c r="Q22" s="99">
         <f t="shared" si="0"/>
-        <v>13</v>
-      </c>
-      <c r="C22" s="70" t="s">
-        <v>163</v>
-      </c>
-      <c r="D22" s="72" t="s">
-        <v>22</v>
-      </c>
-      <c r="E22" s="56" t="s">
-        <v>53</v>
-      </c>
-      <c r="F22" s="72" t="s">
-        <v>77</v>
-      </c>
-      <c r="G22" s="56" t="s">
-        <v>104</v>
-      </c>
-      <c r="H22" s="72" t="s">
-        <v>118</v>
-      </c>
-      <c r="I22" s="56" t="s">
-        <v>176</v>
-      </c>
-      <c r="J22" s="80" t="s">
-        <v>173</v>
-      </c>
-      <c r="K22" s="56" t="s">
-        <v>176</v>
-      </c>
-      <c r="L22" s="72">
-        <v>1</v>
-      </c>
-      <c r="M22" s="132">
-        <f t="shared" si="1"/>
-        <v>5000</v>
-      </c>
-      <c r="N22" s="72"/>
-      <c r="O22" s="89" t="s">
-        <v>152</v>
-      </c>
-      <c r="P22" s="98"/>
-      <c r="Q22" s="107">
-        <f>P22*N22</f>
-        <v>0</v>
-      </c>
-      <c r="R22" s="72"/>
-      <c r="S22" s="108"/>
-    </row>
-    <row r="23" spans="1:19" s="109" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="106"/>
-      <c r="B23" s="61">
+        <v>99.45</v>
+      </c>
+      <c r="R22" s="50"/>
+      <c r="S22" s="100"/>
+      <c r="X22"/>
+    </row>
+    <row r="23" spans="1:24" s="101" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A23" s="98"/>
+      <c r="B23" s="55">
         <f>ROW(B23) - ROW($B$9)</f>
         <v>14</v>
       </c>
-      <c r="C23" s="59" t="s">
+      <c r="C23" s="53" t="s">
         <v>164</v>
       </c>
       <c r="D23" s="41" t="s">
@@ -7160,7 +7523,7 @@
       <c r="F23" s="41" t="s">
         <v>78</v>
       </c>
-      <c r="G23" s="40" t="s">
+      <c r="G23" s="95" t="s">
         <v>105</v>
       </c>
       <c r="H23" s="41" t="s">
@@ -7169,7 +7532,7 @@
       <c r="I23" s="40" t="s">
         <v>196</v>
       </c>
-      <c r="J23" s="81" t="s">
+      <c r="J23" s="73" t="s">
         <v>195</v>
       </c>
       <c r="K23" s="40" t="s">
@@ -7179,80 +7542,90 @@
         <v>1</v>
       </c>
       <c r="M23" s="40">
+        <f t="shared" si="2"/>
+        <v>5000</v>
+      </c>
+      <c r="N23" s="41">
+        <v>5100</v>
+      </c>
+      <c r="O23" s="96" t="s">
+        <v>152</v>
+      </c>
+      <c r="P23" s="89">
+        <v>1.6799999999999999E-2</v>
+      </c>
+      <c r="Q23" s="102">
+        <f t="shared" si="0"/>
+        <v>85.679999999999993</v>
+      </c>
+      <c r="R23" s="40"/>
+      <c r="S23" s="103"/>
+      <c r="X23"/>
+    </row>
+    <row r="24" spans="1:24" s="101" customFormat="1" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A24" s="98"/>
+      <c r="B24" s="55">
         <f t="shared" si="1"/>
+        <v>15</v>
+      </c>
+      <c r="C24" s="62" t="s">
+        <v>165</v>
+      </c>
+      <c r="D24" s="64" t="s">
+        <v>24</v>
+      </c>
+      <c r="E24" s="50" t="s">
+        <v>55</v>
+      </c>
+      <c r="F24" s="64" t="s">
+        <v>175</v>
+      </c>
+      <c r="G24" s="50" t="s">
+        <v>79</v>
+      </c>
+      <c r="H24" s="64" t="s">
+        <v>120</v>
+      </c>
+      <c r="I24" s="50" t="s">
+        <v>176</v>
+      </c>
+      <c r="J24" s="74" t="s">
+        <v>185</v>
+      </c>
+      <c r="K24" s="50" t="s">
+        <v>176</v>
+      </c>
+      <c r="L24" s="64">
+        <v>1</v>
+      </c>
+      <c r="M24" s="122">
+        <f t="shared" si="2"/>
         <v>5000</v>
       </c>
-      <c r="N23" s="41"/>
-      <c r="O23" s="104" t="s">
+      <c r="N24" s="64">
+        <v>5050</v>
+      </c>
+      <c r="O24" s="82" t="s">
         <v>152</v>
       </c>
-      <c r="P23" s="97"/>
-      <c r="Q23" s="110">
-        <f>P23*N23</f>
-        <v>0</v>
-      </c>
-      <c r="R23" s="41"/>
-      <c r="S23" s="111"/>
-    </row>
-    <row r="24" spans="1:19" s="109" customFormat="1" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="106"/>
-      <c r="B24" s="61">
+      <c r="P24" s="90">
+        <v>2.9499999999999998E-2</v>
+      </c>
+      <c r="Q24" s="99">
         <f t="shared" si="0"/>
-        <v>15</v>
-      </c>
-      <c r="C24" s="70" t="s">
-        <v>165</v>
-      </c>
-      <c r="D24" s="72" t="s">
-        <v>24</v>
-      </c>
-      <c r="E24" s="56" t="s">
-        <v>55</v>
-      </c>
-      <c r="F24" s="72" t="s">
-        <v>175</v>
-      </c>
-      <c r="G24" s="56" t="s">
-        <v>79</v>
-      </c>
-      <c r="H24" s="72" t="s">
-        <v>120</v>
-      </c>
-      <c r="I24" s="56" t="s">
-        <v>176</v>
-      </c>
-      <c r="J24" s="82" t="s">
-        <v>185</v>
-      </c>
-      <c r="K24" s="56" t="s">
-        <v>176</v>
-      </c>
-      <c r="L24" s="72">
-        <v>1</v>
-      </c>
-      <c r="M24" s="132">
-        <f t="shared" si="1"/>
-        <v>5000</v>
-      </c>
-      <c r="N24" s="72"/>
-      <c r="O24" s="90" t="s">
-        <v>152</v>
-      </c>
-      <c r="P24" s="98"/>
-      <c r="Q24" s="107">
-        <f>P24*N24</f>
-        <v>0</v>
-      </c>
-      <c r="R24" s="72"/>
-      <c r="S24" s="108"/>
-    </row>
-    <row r="25" spans="1:19" s="109" customFormat="1" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="106"/>
-      <c r="B25" s="61">
+        <v>148.97499999999999</v>
+      </c>
+      <c r="R24" s="50"/>
+      <c r="S24" s="100"/>
+      <c r="X24"/>
+    </row>
+    <row r="25" spans="1:24" s="101" customFormat="1" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A25" s="98"/>
+      <c r="B25" s="55">
         <f>ROW(B25) - ROW($B$9)</f>
         <v>16</v>
       </c>
-      <c r="C25" s="59" t="s">
+      <c r="C25" s="53" t="s">
         <v>8</v>
       </c>
       <c r="D25" s="41" t="s">
@@ -7273,84 +7646,100 @@
       <c r="I25" s="40" t="s">
         <v>176</v>
       </c>
-      <c r="J25" s="41"/>
-      <c r="K25" s="40"/>
+      <c r="J25" s="41" t="s">
+        <v>176</v>
+      </c>
+      <c r="K25" s="40" t="s">
+        <v>176</v>
+      </c>
       <c r="L25" s="41">
         <v>8</v>
       </c>
       <c r="M25" s="40">
+        <f t="shared" si="2"/>
+        <v>40000</v>
+      </c>
+      <c r="N25" s="41">
+        <v>40200</v>
+      </c>
+      <c r="O25" s="96" t="s">
+        <v>212</v>
+      </c>
+      <c r="P25" s="89">
+        <v>1.2450000000000001</v>
+      </c>
+      <c r="Q25" s="102">
+        <f t="shared" si="0"/>
+        <v>50049.000000000007</v>
+      </c>
+      <c r="R25" s="40"/>
+      <c r="S25" s="103"/>
+      <c r="X25"/>
+    </row>
+    <row r="26" spans="1:24" s="101" customFormat="1" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A26" s="98"/>
+      <c r="B26" s="55">
         <f t="shared" si="1"/>
-        <v>40000</v>
-      </c>
-      <c r="N25" s="41"/>
-      <c r="O25" s="57"/>
-      <c r="P25" s="97"/>
-      <c r="Q25" s="110">
-        <f>P25*N25</f>
-        <v>0</v>
-      </c>
-      <c r="R25" s="41"/>
-      <c r="S25" s="111"/>
-    </row>
-    <row r="26" spans="1:19" s="109" customFormat="1" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="106"/>
-      <c r="B26" s="61">
+        <v>17</v>
+      </c>
+      <c r="C26" s="62" t="s">
+        <v>164</v>
+      </c>
+      <c r="D26" s="64" t="s">
+        <v>26</v>
+      </c>
+      <c r="E26" s="50" t="s">
+        <v>57</v>
+      </c>
+      <c r="F26" s="64" t="s">
+        <v>81</v>
+      </c>
+      <c r="G26" s="97">
+        <v>61300611121</v>
+      </c>
+      <c r="H26" s="64" t="s">
+        <v>122</v>
+      </c>
+      <c r="I26" s="50" t="s">
+        <v>197</v>
+      </c>
+      <c r="J26" s="72" t="s">
+        <v>197</v>
+      </c>
+      <c r="K26" s="50" t="s">
+        <v>176</v>
+      </c>
+      <c r="L26" s="64">
+        <v>1</v>
+      </c>
+      <c r="M26" s="122">
+        <f t="shared" si="2"/>
+        <v>5000</v>
+      </c>
+      <c r="N26" s="64">
+        <v>5100</v>
+      </c>
+      <c r="O26" s="94" t="s">
+        <v>152</v>
+      </c>
+      <c r="P26" s="90">
+        <v>1.55E-2</v>
+      </c>
+      <c r="Q26" s="99">
         <f t="shared" si="0"/>
-        <v>17</v>
-      </c>
-      <c r="C26" s="70" t="s">
-        <v>164</v>
-      </c>
-      <c r="D26" s="72" t="s">
-        <v>26</v>
-      </c>
-      <c r="E26" s="56" t="s">
-        <v>57</v>
-      </c>
-      <c r="F26" s="72" t="s">
-        <v>81</v>
-      </c>
-      <c r="G26" s="56">
-        <v>61300611121</v>
-      </c>
-      <c r="H26" s="72" t="s">
-        <v>122</v>
-      </c>
-      <c r="I26" s="56" t="s">
-        <v>197</v>
-      </c>
-      <c r="J26" s="80" t="s">
-        <v>197</v>
-      </c>
-      <c r="K26" s="56" t="s">
-        <v>176</v>
-      </c>
-      <c r="L26" s="72">
-        <v>1</v>
-      </c>
-      <c r="M26" s="132">
-        <f t="shared" si="1"/>
-        <v>5000</v>
-      </c>
-      <c r="N26" s="72"/>
-      <c r="O26" s="102" t="s">
-        <v>152</v>
-      </c>
-      <c r="P26" s="98"/>
-      <c r="Q26" s="107">
-        <f>P26*N26</f>
-        <v>0</v>
-      </c>
-      <c r="R26" s="72"/>
-      <c r="S26" s="108"/>
-    </row>
-    <row r="27" spans="1:19" s="109" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="106"/>
-      <c r="B27" s="61">
+        <v>79.05</v>
+      </c>
+      <c r="R26" s="50"/>
+      <c r="S26" s="100"/>
+      <c r="X26"/>
+    </row>
+    <row r="27" spans="1:24" s="101" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A27" s="98"/>
+      <c r="B27" s="55">
         <f>ROW(B27) - ROW($B$9)</f>
         <v>18</v>
       </c>
-      <c r="C27" s="59" t="s">
+      <c r="C27" s="53" t="s">
         <v>166</v>
       </c>
       <c r="D27" s="41" t="s">
@@ -7362,16 +7751,16 @@
       <c r="F27" s="41" t="s">
         <v>82</v>
       </c>
-      <c r="G27" s="40" t="s">
+      <c r="G27" s="95" t="s">
         <v>106</v>
       </c>
       <c r="H27" s="41" t="s">
         <v>119</v>
       </c>
-      <c r="I27" s="78" t="s">
+      <c r="I27" s="70" t="s">
         <v>182</v>
       </c>
-      <c r="J27" s="83" t="s">
+      <c r="J27" s="75" t="s">
         <v>181</v>
       </c>
       <c r="K27" s="40" t="s">
@@ -7381,80 +7770,90 @@
         <v>3</v>
       </c>
       <c r="M27" s="40">
+        <f t="shared" si="2"/>
+        <v>15000</v>
+      </c>
+      <c r="N27" s="41">
+        <v>15100</v>
+      </c>
+      <c r="O27" s="96" t="s">
+        <v>152</v>
+      </c>
+      <c r="P27" s="89">
+        <v>6.9999999999999999E-4</v>
+      </c>
+      <c r="Q27" s="102">
+        <f t="shared" si="0"/>
+        <v>10.57</v>
+      </c>
+      <c r="R27" s="40"/>
+      <c r="S27" s="103"/>
+      <c r="X27"/>
+    </row>
+    <row r="28" spans="1:24" s="101" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A28" s="98"/>
+      <c r="B28" s="55">
         <f t="shared" si="1"/>
+        <v>19</v>
+      </c>
+      <c r="C28" s="62" t="s">
+        <v>166</v>
+      </c>
+      <c r="D28" s="64" t="s">
+        <v>28</v>
+      </c>
+      <c r="E28" s="50" t="s">
+        <v>59</v>
+      </c>
+      <c r="F28" s="64" t="s">
+        <v>82</v>
+      </c>
+      <c r="G28" s="50" t="s">
+        <v>107</v>
+      </c>
+      <c r="H28" s="64" t="s">
+        <v>114</v>
+      </c>
+      <c r="I28" s="50" t="s">
+        <v>176</v>
+      </c>
+      <c r="J28" s="72" t="s">
+        <v>183</v>
+      </c>
+      <c r="K28" s="50" t="s">
+        <v>142</v>
+      </c>
+      <c r="L28" s="64">
+        <v>3</v>
+      </c>
+      <c r="M28" s="122">
+        <f t="shared" si="2"/>
         <v>15000</v>
       </c>
-      <c r="N27" s="41"/>
-      <c r="O27" s="104" t="s">
+      <c r="N28" s="64">
+        <v>15100</v>
+      </c>
+      <c r="O28" s="83" t="s">
         <v>152</v>
       </c>
-      <c r="P27" s="97"/>
-      <c r="Q27" s="110">
-        <f>P27*N27</f>
-        <v>0</v>
-      </c>
-      <c r="R27" s="41"/>
-      <c r="S27" s="111"/>
-    </row>
-    <row r="28" spans="1:19" s="109" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A28" s="106"/>
-      <c r="B28" s="61">
+      <c r="P28" s="90">
+        <v>5.9999999999999995E-4</v>
+      </c>
+      <c r="Q28" s="99">
         <f t="shared" si="0"/>
-        <v>19</v>
-      </c>
-      <c r="C28" s="70" t="s">
-        <v>166</v>
-      </c>
-      <c r="D28" s="72" t="s">
-        <v>28</v>
-      </c>
-      <c r="E28" s="56" t="s">
-        <v>59</v>
-      </c>
-      <c r="F28" s="72" t="s">
-        <v>82</v>
-      </c>
-      <c r="G28" s="56" t="s">
-        <v>107</v>
-      </c>
-      <c r="H28" s="72" t="s">
-        <v>114</v>
-      </c>
-      <c r="I28" s="56" t="s">
-        <v>176</v>
-      </c>
-      <c r="J28" s="80" t="s">
-        <v>183</v>
-      </c>
-      <c r="K28" s="56" t="s">
-        <v>142</v>
-      </c>
-      <c r="L28" s="72">
-        <v>3</v>
-      </c>
-      <c r="M28" s="132">
-        <f t="shared" si="1"/>
-        <v>15000</v>
-      </c>
-      <c r="N28" s="72"/>
-      <c r="O28" s="91" t="s">
-        <v>152</v>
-      </c>
-      <c r="P28" s="98"/>
-      <c r="Q28" s="107">
-        <f>P28*N28</f>
-        <v>0</v>
-      </c>
-      <c r="R28" s="72"/>
-      <c r="S28" s="108"/>
-    </row>
-    <row r="29" spans="1:19" s="109" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A29" s="106"/>
-      <c r="B29" s="61">
+        <v>9.0599999999999987</v>
+      </c>
+      <c r="R28" s="50"/>
+      <c r="S28" s="100"/>
+      <c r="X28"/>
+    </row>
+    <row r="29" spans="1:24" s="101" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A29" s="98"/>
+      <c r="B29" s="55">
         <f>ROW(B29) - ROW($B$9)</f>
         <v>20</v>
       </c>
-      <c r="C29" s="59" t="s">
+      <c r="C29" s="53" t="s">
         <v>166</v>
       </c>
       <c r="D29" s="41" t="s">
@@ -7475,7 +7874,7 @@
       <c r="I29" s="40" t="s">
         <v>176</v>
       </c>
-      <c r="J29" s="83" t="s">
+      <c r="J29" s="75" t="s">
         <v>184</v>
       </c>
       <c r="K29" s="40" t="s">
@@ -7485,80 +7884,90 @@
         <v>2</v>
       </c>
       <c r="M29" s="40">
+        <f t="shared" si="2"/>
+        <v>10000</v>
+      </c>
+      <c r="N29" s="41">
+        <v>10100</v>
+      </c>
+      <c r="O29" s="84" t="s">
+        <v>152</v>
+      </c>
+      <c r="P29" s="89">
+        <v>5.9999999999999995E-4</v>
+      </c>
+      <c r="Q29" s="102">
+        <f t="shared" si="0"/>
+        <v>6.06</v>
+      </c>
+      <c r="R29" s="40"/>
+      <c r="S29" s="103"/>
+      <c r="X29"/>
+    </row>
+    <row r="30" spans="1:24" s="101" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A30" s="98"/>
+      <c r="B30" s="55">
         <f t="shared" si="1"/>
-        <v>10000</v>
-      </c>
-      <c r="N29" s="41"/>
-      <c r="O29" s="92" t="s">
+        <v>21</v>
+      </c>
+      <c r="C30" s="62" t="s">
+        <v>166</v>
+      </c>
+      <c r="D30" s="64" t="s">
+        <v>30</v>
+      </c>
+      <c r="E30" s="50" t="s">
+        <v>61</v>
+      </c>
+      <c r="F30" s="64" t="s">
+        <v>82</v>
+      </c>
+      <c r="G30" s="50" t="s">
+        <v>109</v>
+      </c>
+      <c r="H30" s="64" t="s">
+        <v>114</v>
+      </c>
+      <c r="I30" s="50" t="s">
+        <v>176</v>
+      </c>
+      <c r="J30" s="72" t="s">
+        <v>198</v>
+      </c>
+      <c r="K30" s="50" t="s">
+        <v>144</v>
+      </c>
+      <c r="L30" s="64">
+        <v>1</v>
+      </c>
+      <c r="M30" s="122">
+        <f t="shared" si="2"/>
+        <v>5000</v>
+      </c>
+      <c r="N30" s="64">
+        <v>5100</v>
+      </c>
+      <c r="O30" s="94" t="s">
         <v>152</v>
       </c>
-      <c r="P29" s="97"/>
-      <c r="Q29" s="110">
-        <f>P29*N29</f>
-        <v>0</v>
-      </c>
-      <c r="R29" s="41"/>
-      <c r="S29" s="111"/>
-    </row>
-    <row r="30" spans="1:19" s="109" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A30" s="106"/>
-      <c r="B30" s="61">
+      <c r="P30" s="90">
+        <v>6.9999999999999999E-4</v>
+      </c>
+      <c r="Q30" s="99">
         <f t="shared" si="0"/>
-        <v>21</v>
-      </c>
-      <c r="C30" s="70" t="s">
-        <v>166</v>
-      </c>
-      <c r="D30" s="72" t="s">
-        <v>30</v>
-      </c>
-      <c r="E30" s="56" t="s">
-        <v>61</v>
-      </c>
-      <c r="F30" s="72" t="s">
-        <v>82</v>
-      </c>
-      <c r="G30" s="56" t="s">
-        <v>109</v>
-      </c>
-      <c r="H30" s="72" t="s">
-        <v>114</v>
-      </c>
-      <c r="I30" s="56" t="s">
-        <v>176</v>
-      </c>
-      <c r="J30" s="80" t="s">
-        <v>198</v>
-      </c>
-      <c r="K30" s="56" t="s">
-        <v>144</v>
-      </c>
-      <c r="L30" s="72">
-        <v>1</v>
-      </c>
-      <c r="M30" s="132">
-        <f t="shared" si="1"/>
-        <v>5000</v>
-      </c>
-      <c r="N30" s="72"/>
-      <c r="O30" s="102" t="s">
-        <v>152</v>
-      </c>
-      <c r="P30" s="98"/>
-      <c r="Q30" s="107">
-        <f>P30*N30</f>
-        <v>0</v>
-      </c>
-      <c r="R30" s="72"/>
-      <c r="S30" s="108"/>
-    </row>
-    <row r="31" spans="1:19" s="109" customFormat="1" ht="96.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A31" s="106"/>
-      <c r="B31" s="61">
+        <v>3.57</v>
+      </c>
+      <c r="R30" s="50"/>
+      <c r="S30" s="100"/>
+      <c r="X30"/>
+    </row>
+    <row r="31" spans="1:24" s="101" customFormat="1" ht="96.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A31" s="98"/>
+      <c r="B31" s="55">
         <f>ROW(B31) - ROW($B$9)</f>
         <v>22</v>
       </c>
-      <c r="C31" s="59" t="s">
+      <c r="C31" s="53" t="s">
         <v>167</v>
       </c>
       <c r="D31" s="41" t="s">
@@ -7589,87 +7998,93 @@
         <v>48</v>
       </c>
       <c r="M31" s="40">
+        <f t="shared" si="2"/>
+        <v>240000</v>
+      </c>
+      <c r="N31" s="41" t="s">
+        <v>176</v>
+      </c>
+      <c r="O31" s="51" t="s">
+        <v>176</v>
+      </c>
+      <c r="P31" s="89" t="s">
+        <v>176</v>
+      </c>
+      <c r="Q31" s="102" t="s">
+        <v>176</v>
+      </c>
+      <c r="R31" s="40" t="s">
+        <v>176</v>
+      </c>
+      <c r="S31" s="108" t="s">
+        <v>176</v>
+      </c>
+      <c r="X31"/>
+    </row>
+    <row r="32" spans="1:24" s="101" customFormat="1" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A32" s="98"/>
+      <c r="B32" s="55">
         <f t="shared" si="1"/>
-        <v>240000</v>
-      </c>
-      <c r="N31" s="41" t="s">
-        <v>176</v>
-      </c>
-      <c r="O31" s="57" t="s">
-        <v>176</v>
-      </c>
-      <c r="P31" s="97" t="s">
-        <v>176</v>
-      </c>
-      <c r="Q31" s="110" t="s">
-        <v>176</v>
-      </c>
-      <c r="R31" s="41" t="s">
-        <v>176</v>
-      </c>
-      <c r="S31" s="116" t="s">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="32" spans="1:19" s="109" customFormat="1" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A32" s="106"/>
-      <c r="B32" s="61">
-        <f t="shared" si="0"/>
         <v>23</v>
       </c>
-      <c r="C32" s="70" t="s">
+      <c r="C32" s="62" t="s">
         <v>168</v>
       </c>
-      <c r="D32" s="72" t="s">
+      <c r="D32" s="64" t="s">
         <v>32</v>
       </c>
-      <c r="E32" s="56" t="s">
+      <c r="E32" s="50" t="s">
         <v>63</v>
       </c>
-      <c r="F32" s="72" t="s">
+      <c r="F32" s="64" t="s">
         <v>175</v>
       </c>
-      <c r="G32" s="112" t="s">
+      <c r="G32" s="104" t="s">
         <v>84</v>
       </c>
-      <c r="H32" s="72" t="s">
+      <c r="H32" s="64" t="s">
         <v>120</v>
       </c>
-      <c r="I32" s="56" t="s">
-        <v>176</v>
-      </c>
-      <c r="J32" s="80" t="s">
-        <v>174</v>
-      </c>
-      <c r="K32" s="56" t="s">
-        <v>176</v>
-      </c>
-      <c r="L32" s="72">
+      <c r="I32" s="50" t="s">
+        <v>176</v>
+      </c>
+      <c r="J32" s="72" t="s">
+        <v>176</v>
+      </c>
+      <c r="K32" s="50" t="s">
+        <v>176</v>
+      </c>
+      <c r="L32" s="64">
         <v>1</v>
       </c>
-      <c r="M32" s="132">
-        <f t="shared" si="1"/>
+      <c r="M32" s="122">
+        <f t="shared" si="2"/>
         <v>5000</v>
       </c>
-      <c r="N32" s="72"/>
-      <c r="O32" s="102" t="s">
-        <v>152</v>
-      </c>
-      <c r="P32" s="98"/>
-      <c r="Q32" s="107">
-        <f>P32*N32</f>
-        <v>0</v>
-      </c>
-      <c r="R32" s="72"/>
-      <c r="S32" s="108"/>
-    </row>
-    <row r="33" spans="1:19" s="109" customFormat="1" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A33" s="106"/>
-      <c r="B33" s="61">
+      <c r="N32" s="64">
+        <v>5050</v>
+      </c>
+      <c r="O32" s="94" t="s">
+        <v>212</v>
+      </c>
+      <c r="P32" s="90">
+        <v>1.2E-2</v>
+      </c>
+      <c r="Q32" s="99">
+        <f t="shared" ref="Q32:Q39" si="3">P32*N32</f>
+        <v>60.6</v>
+      </c>
+      <c r="R32" s="50"/>
+      <c r="S32" s="100"/>
+      <c r="X32"/>
+    </row>
+    <row r="33" spans="1:24" s="101" customFormat="1" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A33" s="98"/>
+      <c r="B33" s="55">
         <f>ROW(B33) - ROW($B$9)</f>
         <v>24</v>
       </c>
-      <c r="C33" s="59" t="s">
+      <c r="C33" s="53" t="s">
         <v>9</v>
       </c>
       <c r="D33" s="41" t="s">
@@ -7691,7 +8106,7 @@
         <v>176</v>
       </c>
       <c r="J33" s="41" t="s">
-        <v>130</v>
+        <v>176</v>
       </c>
       <c r="K33" s="40" t="s">
         <v>176</v>
@@ -7700,80 +8115,90 @@
         <v>1</v>
       </c>
       <c r="M33" s="40">
+        <f t="shared" si="2"/>
+        <v>5000</v>
+      </c>
+      <c r="N33" s="41">
+        <v>5020</v>
+      </c>
+      <c r="O33" s="80" t="s">
+        <v>212</v>
+      </c>
+      <c r="P33" s="89">
+        <v>3.12</v>
+      </c>
+      <c r="Q33" s="102">
+        <f t="shared" si="3"/>
+        <v>15662.4</v>
+      </c>
+      <c r="R33" s="40"/>
+      <c r="S33" s="103"/>
+      <c r="X33"/>
+    </row>
+    <row r="34" spans="1:24" s="101" customFormat="1" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A34" s="98"/>
+      <c r="B34" s="55">
         <f t="shared" si="1"/>
+        <v>25</v>
+      </c>
+      <c r="C34" s="62" t="s">
+        <v>169</v>
+      </c>
+      <c r="D34" s="64" t="s">
+        <v>34</v>
+      </c>
+      <c r="E34" s="50" t="s">
+        <v>65</v>
+      </c>
+      <c r="F34" s="64" t="s">
+        <v>86</v>
+      </c>
+      <c r="G34" s="50" t="s">
+        <v>110</v>
+      </c>
+      <c r="H34" s="64" t="s">
+        <v>124</v>
+      </c>
+      <c r="I34" s="50" t="s">
+        <v>176</v>
+      </c>
+      <c r="J34" s="76" t="s">
+        <v>179</v>
+      </c>
+      <c r="K34" s="50" t="s">
+        <v>176</v>
+      </c>
+      <c r="L34" s="64">
+        <v>1</v>
+      </c>
+      <c r="M34" s="122">
+        <f t="shared" si="2"/>
         <v>5000</v>
       </c>
-      <c r="N33" s="41"/>
-      <c r="O33" s="88" t="s">
+      <c r="N34" s="64">
+        <v>5020</v>
+      </c>
+      <c r="O34" s="94" t="s">
         <v>152</v>
       </c>
-      <c r="P33" s="97"/>
-      <c r="Q33" s="110">
-        <f>P33*N33</f>
-        <v>0</v>
-      </c>
-      <c r="R33" s="41"/>
-      <c r="S33" s="111"/>
-    </row>
-    <row r="34" spans="1:19" s="109" customFormat="1" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A34" s="106"/>
-      <c r="B34" s="61">
-        <f t="shared" si="0"/>
-        <v>25</v>
-      </c>
-      <c r="C34" s="70" t="s">
-        <v>169</v>
-      </c>
-      <c r="D34" s="72" t="s">
-        <v>34</v>
-      </c>
-      <c r="E34" s="56" t="s">
-        <v>65</v>
-      </c>
-      <c r="F34" s="72" t="s">
-        <v>86</v>
-      </c>
-      <c r="G34" s="56" t="s">
-        <v>110</v>
-      </c>
-      <c r="H34" s="72" t="s">
-        <v>124</v>
-      </c>
-      <c r="I34" s="56" t="s">
-        <v>176</v>
-      </c>
-      <c r="J34" s="84" t="s">
-        <v>179</v>
-      </c>
-      <c r="K34" s="56" t="s">
-        <v>176</v>
-      </c>
-      <c r="L34" s="72">
-        <v>1</v>
-      </c>
-      <c r="M34" s="132">
-        <f t="shared" si="1"/>
-        <v>5000</v>
-      </c>
-      <c r="N34" s="72"/>
-      <c r="O34" s="102" t="s">
-        <v>152</v>
-      </c>
-      <c r="P34" s="98"/>
-      <c r="Q34" s="107">
-        <f>P34*N34</f>
-        <v>0</v>
-      </c>
-      <c r="R34" s="72"/>
-      <c r="S34" s="108"/>
-    </row>
-    <row r="35" spans="1:19" s="109" customFormat="1" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A35" s="106"/>
-      <c r="B35" s="61">
+      <c r="P34" s="90">
+        <v>0.29759999999999998</v>
+      </c>
+      <c r="Q34" s="99">
+        <f t="shared" si="3"/>
+        <v>1493.9519999999998</v>
+      </c>
+      <c r="R34" s="50"/>
+      <c r="S34" s="100"/>
+      <c r="X34"/>
+    </row>
+    <row r="35" spans="1:24" s="101" customFormat="1" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A35" s="98"/>
+      <c r="B35" s="55">
         <f>ROW(B35) - ROW($B$9)</f>
         <v>26</v>
       </c>
-      <c r="C35" s="59" t="s">
+      <c r="C35" s="53" t="s">
         <v>169</v>
       </c>
       <c r="D35" s="41" t="s">
@@ -7791,85 +8216,105 @@
       <c r="H35" s="41" t="s">
         <v>118</v>
       </c>
-      <c r="I35" s="40"/>
-      <c r="J35" s="41"/>
-      <c r="K35" s="40"/>
+      <c r="I35" s="40" t="s">
+        <v>176</v>
+      </c>
+      <c r="J35" s="41" t="s">
+        <v>176</v>
+      </c>
+      <c r="K35" s="40" t="s">
+        <v>176</v>
+      </c>
       <c r="L35" s="41">
         <v>1</v>
       </c>
       <c r="M35" s="40">
+        <f t="shared" si="2"/>
+        <v>5000</v>
+      </c>
+      <c r="N35" s="41">
+        <v>5020</v>
+      </c>
+      <c r="O35" s="80" t="s">
+        <v>212</v>
+      </c>
+      <c r="P35" s="89">
+        <v>14.82</v>
+      </c>
+      <c r="Q35" s="102">
+        <f t="shared" si="3"/>
+        <v>74396.399999999994</v>
+      </c>
+      <c r="R35" s="40"/>
+      <c r="S35" s="103"/>
+      <c r="X35"/>
+    </row>
+    <row r="36" spans="1:24" s="101" customFormat="1" ht="39" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A36" s="98"/>
+      <c r="B36" s="55">
         <f t="shared" si="1"/>
-        <v>5000</v>
-      </c>
-      <c r="N35" s="41"/>
-      <c r="O35" s="57"/>
-      <c r="P35" s="97"/>
-      <c r="Q35" s="110">
-        <f>P35*N35</f>
-        <v>0</v>
-      </c>
-      <c r="R35" s="41"/>
-      <c r="S35" s="111"/>
-    </row>
-    <row r="36" spans="1:19" s="109" customFormat="1" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A36" s="106"/>
-      <c r="B36" s="61">
-        <f t="shared" si="0"/>
         <v>27</v>
       </c>
-      <c r="C36" s="70" t="s">
+      <c r="C36" s="62" t="s">
         <v>169</v>
       </c>
-      <c r="D36" s="72" t="s">
+      <c r="D36" s="64" t="s">
         <v>36</v>
       </c>
-      <c r="E36" s="56" t="s">
+      <c r="E36" s="50" t="s">
         <v>67</v>
       </c>
-      <c r="F36" s="72" t="s">
+      <c r="F36" s="64" t="s">
         <v>186</v>
       </c>
-      <c r="G36" s="56" t="s">
+      <c r="G36" s="50" t="s">
         <v>88</v>
       </c>
-      <c r="H36" s="72" t="s">
+      <c r="H36" s="64" t="s">
         <v>118</v>
       </c>
-      <c r="I36" s="56" t="s">
-        <v>176</v>
-      </c>
-      <c r="J36" s="80" t="s">
+      <c r="I36" s="50" t="s">
+        <v>176</v>
+      </c>
+      <c r="J36" s="72" t="s">
         <v>199</v>
       </c>
-      <c r="K36" s="56" t="s">
-        <v>176</v>
-      </c>
-      <c r="L36" s="72">
+      <c r="K36" s="50" t="s">
+        <v>176</v>
+      </c>
+      <c r="L36" s="64">
         <v>2</v>
       </c>
-      <c r="M36" s="132">
-        <f t="shared" si="1"/>
+      <c r="M36" s="122">
+        <f t="shared" si="2"/>
         <v>10000</v>
       </c>
-      <c r="N36" s="72"/>
-      <c r="O36" s="102" t="s">
+      <c r="N36" s="64">
+        <v>10050</v>
+      </c>
+      <c r="O36" s="143" t="s">
         <v>152</v>
       </c>
-      <c r="P36" s="98"/>
-      <c r="Q36" s="107">
-        <f>P36*N36</f>
-        <v>0</v>
-      </c>
-      <c r="R36" s="72"/>
-      <c r="S36" s="108"/>
-    </row>
-    <row r="37" spans="1:19" s="109" customFormat="1" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A37" s="106"/>
-      <c r="B37" s="61">
+      <c r="P36" s="90">
+        <v>2.6855000000000002</v>
+      </c>
+      <c r="Q36" s="145">
+        <f t="shared" si="3"/>
+        <v>26989.275000000001</v>
+      </c>
+      <c r="R36" s="148" t="s">
+        <v>218</v>
+      </c>
+      <c r="S36" s="100"/>
+      <c r="X36"/>
+    </row>
+    <row r="37" spans="1:24" s="101" customFormat="1" ht="39" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A37" s="98"/>
+      <c r="B37" s="55">
         <f>ROW(B37) - ROW($B$9)</f>
         <v>28</v>
       </c>
-      <c r="C37" s="59" t="s">
+      <c r="C37" s="53" t="s">
         <v>169</v>
       </c>
       <c r="D37" s="41" t="s">
@@ -7890,7 +8335,7 @@
       <c r="I37" s="40" t="s">
         <v>176</v>
       </c>
-      <c r="J37" s="85" t="s">
+      <c r="J37" s="77" t="s">
         <v>180</v>
       </c>
       <c r="K37" s="40" t="s">
@@ -7900,145 +8345,173 @@
         <v>1</v>
       </c>
       <c r="M37" s="40">
+        <f t="shared" si="2"/>
+        <v>5000</v>
+      </c>
+      <c r="N37" s="41">
+        <v>5020</v>
+      </c>
+      <c r="O37" s="80" t="s">
+        <v>152</v>
+      </c>
+      <c r="P37" s="89">
+        <v>3.8199999999999998E-2</v>
+      </c>
+      <c r="Q37" s="102">
+        <f t="shared" si="3"/>
+        <v>191.76399999999998</v>
+      </c>
+      <c r="R37" s="149" t="s">
+        <v>218</v>
+      </c>
+      <c r="S37" s="103"/>
+      <c r="X37"/>
+    </row>
+    <row r="38" spans="1:24" s="101" customFormat="1" ht="48.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A38" s="98"/>
+      <c r="B38" s="55">
         <f t="shared" si="1"/>
+        <v>29</v>
+      </c>
+      <c r="C38" s="62" t="s">
+        <v>170</v>
+      </c>
+      <c r="D38" s="64" t="s">
+        <v>38</v>
+      </c>
+      <c r="E38" s="50" t="s">
+        <v>69</v>
+      </c>
+      <c r="F38" s="64" t="s">
+        <v>175</v>
+      </c>
+      <c r="G38" s="50" t="s">
+        <v>90</v>
+      </c>
+      <c r="H38" s="64" t="s">
+        <v>126</v>
+      </c>
+      <c r="I38" s="50" t="s">
+        <v>176</v>
+      </c>
+      <c r="J38" s="78" t="s">
+        <v>177</v>
+      </c>
+      <c r="K38" s="50" t="s">
+        <v>187</v>
+      </c>
+      <c r="L38" s="64">
+        <v>1</v>
+      </c>
+      <c r="M38" s="122">
+        <f t="shared" si="2"/>
         <v>5000</v>
       </c>
-      <c r="N37" s="41"/>
-      <c r="O37" s="88" t="s">
+      <c r="N38" s="64">
+        <v>5020</v>
+      </c>
+      <c r="O38" s="94" t="s">
         <v>152</v>
       </c>
-      <c r="P37" s="97"/>
-      <c r="Q37" s="110">
-        <f>P37*N37</f>
-        <v>0</v>
-      </c>
-      <c r="R37" s="41"/>
-      <c r="S37" s="111"/>
-    </row>
-    <row r="38" spans="1:19" s="109" customFormat="1" ht="48.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A38" s="106"/>
-      <c r="B38" s="61">
-        <f t="shared" si="0"/>
-        <v>29</v>
-      </c>
-      <c r="C38" s="70" t="s">
-        <v>170</v>
-      </c>
-      <c r="D38" s="72" t="s">
-        <v>38</v>
-      </c>
-      <c r="E38" s="56" t="s">
-        <v>69</v>
-      </c>
-      <c r="F38" s="72" t="s">
-        <v>175</v>
-      </c>
-      <c r="G38" s="56" t="s">
-        <v>90</v>
-      </c>
-      <c r="H38" s="72" t="s">
-        <v>126</v>
-      </c>
-      <c r="I38" s="56" t="s">
-        <v>176</v>
-      </c>
-      <c r="J38" s="86" t="s">
-        <v>177</v>
-      </c>
-      <c r="K38" s="56" t="s">
-        <v>187</v>
-      </c>
-      <c r="L38" s="72">
-        <v>1</v>
-      </c>
-      <c r="M38" s="132">
-        <f t="shared" si="1"/>
-        <v>5000</v>
-      </c>
-      <c r="N38" s="72"/>
-      <c r="O38" s="102" t="s">
-        <v>152</v>
-      </c>
-      <c r="P38" s="98"/>
-      <c r="Q38" s="107">
-        <f>P38*N38</f>
-        <v>0</v>
-      </c>
-      <c r="R38" s="72"/>
-      <c r="S38" s="108"/>
-    </row>
-    <row r="39" spans="1:19" s="109" customFormat="1" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A39" s="106"/>
-      <c r="B39" s="61">
+      <c r="P38" s="90">
+        <v>0.10050000000000001</v>
+      </c>
+      <c r="Q38" s="99">
+        <f t="shared" si="3"/>
+        <v>504.51000000000005</v>
+      </c>
+      <c r="R38" s="148" t="s">
+        <v>218</v>
+      </c>
+      <c r="S38" s="100"/>
+      <c r="X38"/>
+    </row>
+    <row r="39" spans="1:24" s="101" customFormat="1" ht="39" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A39" s="98"/>
+      <c r="B39" s="55">
         <f>ROW(B39) - ROW($B$9)</f>
         <v>30</v>
       </c>
-      <c r="C39" s="71"/>
-      <c r="D39" s="75" t="s">
+      <c r="C39" s="63" t="s">
+        <v>170</v>
+      </c>
+      <c r="D39" s="67" t="s">
         <v>39</v>
       </c>
-      <c r="E39" s="73" t="s">
+      <c r="E39" s="65" t="s">
         <v>70</v>
       </c>
-      <c r="F39" s="75" t="s">
+      <c r="F39" s="67" t="s">
         <v>175</v>
       </c>
-      <c r="G39" s="73" t="s">
+      <c r="G39" s="65" t="s">
         <v>91</v>
       </c>
-      <c r="H39" s="75" t="s">
+      <c r="H39" s="67" t="s">
         <v>127</v>
       </c>
-      <c r="I39" s="73" t="s">
-        <v>176</v>
-      </c>
-      <c r="J39" s="87" t="s">
+      <c r="I39" s="65" t="s">
+        <v>176</v>
+      </c>
+      <c r="J39" s="79" t="s">
         <v>178</v>
       </c>
-      <c r="K39" s="73" t="s">
+      <c r="K39" s="65" t="s">
         <v>188</v>
       </c>
-      <c r="L39" s="75">
+      <c r="L39" s="67">
         <v>2</v>
       </c>
-      <c r="M39" s="73">
-        <f t="shared" si="1"/>
+      <c r="M39" s="65">
+        <f t="shared" si="2"/>
         <v>10000</v>
       </c>
-      <c r="N39" s="75"/>
-      <c r="O39" s="88" t="s">
+      <c r="N39" s="67">
+        <v>5020</v>
+      </c>
+      <c r="O39" s="80" t="s">
         <v>152</v>
       </c>
-      <c r="P39" s="99"/>
-      <c r="Q39" s="113">
-        <f>P39*N39</f>
-        <v>0</v>
-      </c>
-      <c r="R39" s="75"/>
-      <c r="S39" s="114"/>
-    </row>
-    <row r="40" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="P39" s="91">
+        <v>4.0500000000000001E-2</v>
+      </c>
+      <c r="Q39" s="105">
+        <f t="shared" si="3"/>
+        <v>203.31</v>
+      </c>
+      <c r="R39" s="150" t="s">
+        <v>218</v>
+      </c>
+      <c r="S39" s="106"/>
+      <c r="X39"/>
+    </row>
+    <row r="40" spans="1:24" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A40" s="1"/>
-      <c r="B40" s="74"/>
-      <c r="C40" s="62"/>
-      <c r="D40" s="63"/>
-      <c r="E40" s="64"/>
-      <c r="F40" s="65"/>
-      <c r="G40" s="66"/>
-      <c r="H40" s="65"/>
-      <c r="I40" s="66"/>
-      <c r="J40" s="65"/>
-      <c r="K40" s="66"/>
-      <c r="L40" s="66"/>
-      <c r="M40" s="66"/>
-      <c r="N40" s="66"/>
-      <c r="O40" s="66"/>
-      <c r="P40" s="66"/>
-      <c r="Q40" s="66"/>
-      <c r="R40" s="67"/>
-      <c r="S40" s="68"/>
-    </row>
-    <row r="41" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B40" s="66"/>
+      <c r="C40" s="56"/>
+      <c r="D40" s="57"/>
+      <c r="E40" s="58"/>
+      <c r="F40" s="59"/>
+      <c r="G40" s="60"/>
+      <c r="H40" s="59"/>
+      <c r="I40" s="60"/>
+      <c r="J40" s="59"/>
+      <c r="K40" s="60"/>
+      <c r="L40" s="60"/>
+      <c r="M40" s="60"/>
+      <c r="N40" s="134" t="s">
+        <v>209</v>
+      </c>
+      <c r="O40" s="135"/>
+      <c r="P40" s="135"/>
+      <c r="Q40" s="124">
+        <f>SUM(Q10:Q39)</f>
+        <v>186903.826</v>
+      </c>
+      <c r="R40" s="130"/>
+      <c r="S40" s="131"/>
+    </row>
+    <row r="41" spans="1:24" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A41" s="1"/>
       <c r="B41" s="25"/>
       <c r="C41" s="37"/>
@@ -8052,20 +8525,27 @@
       <c r="K41" s="10"/>
       <c r="L41" s="10"/>
       <c r="M41" s="10"/>
-      <c r="N41" s="10"/>
-      <c r="O41" s="10"/>
-      <c r="P41" s="10"/>
-      <c r="Q41" s="10"/>
-      <c r="R41" s="53"/>
-      <c r="S41" s="54"/>
+      <c r="N41" s="134" t="s">
+        <v>210</v>
+      </c>
+      <c r="O41" s="135"/>
+      <c r="P41" s="135"/>
+      <c r="Q41" s="125">
+        <f>Q40/5000</f>
+        <v>37.380765199999999</v>
+      </c>
+      <c r="R41" s="132"/>
+      <c r="S41" s="133"/>
     </row>
   </sheetData>
-  <mergeCells count="3">
+  <mergeCells count="5">
     <mergeCell ref="K1:S1"/>
     <mergeCell ref="S3:S8"/>
     <mergeCell ref="R40:S41"/>
+    <mergeCell ref="N40:P40"/>
+    <mergeCell ref="N41:P41"/>
   </mergeCells>
-  <conditionalFormatting sqref="O13 O25 O31 O33 O35 O15 O17 O19">
+  <conditionalFormatting sqref="O13 O31 O33 O15 O17 O19 O35">
     <cfRule type="dataBar" priority="5">
       <dataBar>
         <cfvo type="min"/>
@@ -8160,12 +8640,11 @@
     <hyperlink ref="O24" r:id="rId22" xr:uid="{5ED73709-63B8-410D-81BB-E3384DFF6150}"/>
     <hyperlink ref="O26" r:id="rId23" xr:uid="{260528D6-F7D9-4C5B-9808-0D61E9031FAD}"/>
     <hyperlink ref="O30" r:id="rId24" xr:uid="{45EB2636-CD73-4B4B-AFC5-733A0A0E6D3D}"/>
-    <hyperlink ref="O32" r:id="rId25" xr:uid="{247E1A25-C5FB-471B-BEAA-AF3F4AEF2101}"/>
-    <hyperlink ref="O33" r:id="rId26" xr:uid="{8ACB1CF9-90A7-4871-BE83-A0BE5DD099AF}"/>
-    <hyperlink ref="O36" r:id="rId27" xr:uid="{B33148BA-8C8B-4B3F-8EE4-C64AB425EC1D}"/>
+    <hyperlink ref="O33" r:id="rId25" display="LCSC" xr:uid="{8ACB1CF9-90A7-4871-BE83-A0BE5DD099AF}"/>
+    <hyperlink ref="O36" r:id="rId26" xr:uid="{B33148BA-8C8B-4B3F-8EE4-C64AB425EC1D}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId28"/>
+  <drawing r:id="rId27"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
@@ -8180,7 +8659,7 @@
               <x14:axisColor rgb="FF000000"/>
             </x14:dataBar>
           </x14:cfRule>
-          <xm:sqref>O13 O25 O31 O33 O35 O15 O17 O19</xm:sqref>
+          <xm:sqref>O13 O31 O33 O15 O17 O19 O35</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
           <x14:cfRule type="dataBar" id="{7BDF827A-9CCF-4430-82C7-768A27027DE3}">

--- a/Deliverables/BOM/eSpark-BOM-v2.1_Wo_Battery Boards.xlsx
+++ b/Deliverables/BOM/eSpark-BOM-v2.1_Wo_Battery Boards.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="25726"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="25831"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\Melih-SoundSensor\Deliverables\BOM\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{686FFF28-20FD-4C10-BD42-91F322F9BCBD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DB496208-7E25-4AF8-9477-EF5B32735670}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-5730" yWindow="3105" windowWidth="11790" windowHeight="15360" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="20 Boards" sheetId="1" r:id="rId1"/>
@@ -1552,6 +1552,49 @@
     <xf numFmtId="166" fontId="15" fillId="3" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="28" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="27" fillId="4" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="19" fillId="4" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="23" fillId="4" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="2" borderId="17" xfId="1" quotePrefix="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="20" fillId="2" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="20" fillId="2" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="17" xfId="1" quotePrefix="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="21" fillId="4" borderId="17" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="4" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="4" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1583,49 +1626,6 @@
     <xf numFmtId="0" fontId="26" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="top"/>
       <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="27" fillId="4" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="19" fillId="4" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="23" fillId="4" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="2" borderId="17" xfId="1" quotePrefix="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="20" fillId="2" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="20" fillId="2" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="17" xfId="1" quotePrefix="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="21" fillId="4" borderId="17" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="4" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="4" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -2110,15 +2110,15 @@
       <c r="H1" s="2"/>
       <c r="I1" s="2"/>
       <c r="J1" s="2"/>
-      <c r="K1" s="126"/>
-      <c r="L1" s="126"/>
-      <c r="M1" s="126"/>
-      <c r="N1" s="126"/>
-      <c r="O1" s="126"/>
-      <c r="P1" s="126"/>
-      <c r="Q1" s="126"/>
-      <c r="R1" s="126"/>
-      <c r="S1" s="127"/>
+      <c r="K1" s="141"/>
+      <c r="L1" s="141"/>
+      <c r="M1" s="141"/>
+      <c r="N1" s="141"/>
+      <c r="O1" s="141"/>
+      <c r="P1" s="141"/>
+      <c r="Q1" s="141"/>
+      <c r="R1" s="141"/>
+      <c r="S1" s="142"/>
     </row>
     <row r="2" spans="1:19" ht="32.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1"/>
@@ -2168,7 +2168,7 @@
       <c r="P3" s="5"/>
       <c r="Q3" s="5"/>
       <c r="R3" s="5"/>
-      <c r="S3" s="128"/>
+      <c r="S3" s="143"/>
     </row>
     <row r="4" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A4" s="1"/>
@@ -2193,7 +2193,7 @@
       <c r="P4" s="6"/>
       <c r="Q4" s="6"/>
       <c r="R4" s="6"/>
-      <c r="S4" s="129"/>
+      <c r="S4" s="144"/>
     </row>
     <row r="5" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A5" s="1"/>
@@ -2218,7 +2218,7 @@
       <c r="P5" s="6"/>
       <c r="Q5" s="6"/>
       <c r="R5" s="6"/>
-      <c r="S5" s="129"/>
+      <c r="S5" s="144"/>
     </row>
     <row r="6" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A6" s="1"/>
@@ -2239,7 +2239,7 @@
       <c r="P6" s="6"/>
       <c r="Q6" s="6"/>
       <c r="R6" s="6"/>
-      <c r="S6" s="129"/>
+      <c r="S6" s="144"/>
     </row>
     <row r="7" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A7" s="1"/>
@@ -2260,7 +2260,7 @@
       <c r="P7" s="8"/>
       <c r="Q7" s="8"/>
       <c r="R7" s="8"/>
-      <c r="S7" s="129"/>
+      <c r="S7" s="144"/>
     </row>
     <row r="8" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" s="1"/>
@@ -2281,7 +2281,7 @@
       <c r="P8" s="8"/>
       <c r="Q8" s="8"/>
       <c r="R8" s="8"/>
-      <c r="S8" s="129"/>
+      <c r="S8" s="144"/>
     </row>
     <row r="9" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A9" s="1"/>
@@ -3186,54 +3186,54 @@
         <f>ROW(B25) - ROW($B$9)</f>
         <v>16</v>
       </c>
-      <c r="C25" s="139" t="s">
+      <c r="C25" s="129" t="s">
         <v>8</v>
       </c>
-      <c r="D25" s="140" t="s">
+      <c r="D25" s="130" t="s">
         <v>25</v>
       </c>
       <c r="E25" s="108" t="s">
         <v>56</v>
       </c>
-      <c r="F25" s="140" t="s">
+      <c r="F25" s="130" t="s">
         <v>175</v>
       </c>
       <c r="G25" s="108" t="s">
         <v>80</v>
       </c>
-      <c r="H25" s="140" t="s">
+      <c r="H25" s="130" t="s">
         <v>121</v>
       </c>
       <c r="I25" s="108" t="s">
         <v>176</v>
       </c>
-      <c r="J25" s="140" t="s">
+      <c r="J25" s="130" t="s">
         <v>176</v>
       </c>
       <c r="K25" s="108" t="s">
         <v>176</v>
       </c>
-      <c r="L25" s="140">
+      <c r="L25" s="130">
         <v>8</v>
       </c>
       <c r="M25" s="108">
         <f t="shared" si="2"/>
         <v>160</v>
       </c>
-      <c r="N25" s="140">
+      <c r="N25" s="130">
         <v>200</v>
       </c>
       <c r="O25" s="96" t="s">
         <v>211</v>
       </c>
-      <c r="P25" s="141">
+      <c r="P25" s="131">
         <v>2</v>
       </c>
-      <c r="Q25" s="142">
+      <c r="Q25" s="132">
         <f t="shared" si="0"/>
         <v>400</v>
       </c>
-      <c r="R25" s="136" t="s">
+      <c r="R25" s="126" t="s">
         <v>214</v>
       </c>
       <c r="S25" s="44"/>
@@ -3751,54 +3751,54 @@
         <f>ROW(B35) - ROW($B$9)</f>
         <v>26</v>
       </c>
-      <c r="C35" s="139" t="s">
+      <c r="C35" s="129" t="s">
         <v>169</v>
       </c>
-      <c r="D35" s="140" t="s">
+      <c r="D35" s="130" t="s">
         <v>35</v>
       </c>
       <c r="E35" s="108" t="s">
         <v>66</v>
       </c>
-      <c r="F35" s="140" t="s">
+      <c r="F35" s="130" t="s">
         <v>87</v>
       </c>
       <c r="G35" s="108" t="s">
         <v>111</v>
       </c>
-      <c r="H35" s="140" t="s">
+      <c r="H35" s="130" t="s">
         <v>118</v>
       </c>
       <c r="I35" s="108" t="s">
         <v>176</v>
       </c>
-      <c r="J35" s="140" t="s">
+      <c r="J35" s="130" t="s">
         <v>176</v>
       </c>
       <c r="K35" s="108" t="s">
         <v>176</v>
       </c>
-      <c r="L35" s="140">
+      <c r="L35" s="130">
         <v>1</v>
       </c>
       <c r="M35" s="108">
         <f t="shared" si="2"/>
         <v>20</v>
       </c>
-      <c r="N35" s="140">
+      <c r="N35" s="130">
         <v>22</v>
       </c>
       <c r="O35" s="80" t="s">
         <v>211</v>
       </c>
-      <c r="P35" s="141">
+      <c r="P35" s="131">
         <v>18.649999999999999</v>
       </c>
-      <c r="Q35" s="142">
+      <c r="Q35" s="132">
         <f t="shared" si="3"/>
         <v>410.29999999999995</v>
       </c>
-      <c r="R35" s="136" t="s">
+      <c r="R35" s="126" t="s">
         <v>214</v>
       </c>
       <c r="S35" s="44"/>
@@ -3846,13 +3846,13 @@
       <c r="N36" s="64">
         <v>44</v>
       </c>
-      <c r="O36" s="143" t="s">
+      <c r="O36" s="133" t="s">
         <v>152</v>
       </c>
       <c r="P36" s="90">
         <v>3.2374999999999998</v>
       </c>
-      <c r="Q36" s="144">
+      <c r="Q36" s="134">
         <f t="shared" si="3"/>
         <v>142.44999999999999</v>
       </c>
@@ -4041,17 +4041,17 @@
       <c r="K40" s="60"/>
       <c r="L40" s="60"/>
       <c r="M40" s="60"/>
-      <c r="N40" s="134" t="s">
+      <c r="N40" s="149" t="s">
         <v>209</v>
       </c>
-      <c r="O40" s="135"/>
-      <c r="P40" s="135"/>
+      <c r="O40" s="150"/>
+      <c r="P40" s="150"/>
       <c r="Q40" s="124">
         <f>SUM(Q10:Q39)</f>
         <v>1169.7855999999999</v>
       </c>
-      <c r="R40" s="130"/>
-      <c r="S40" s="131"/>
+      <c r="R40" s="145"/>
+      <c r="S40" s="146"/>
     </row>
     <row r="41" spans="1:19" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A41" s="1"/>
@@ -4067,17 +4067,17 @@
       <c r="K41" s="10"/>
       <c r="L41" s="10"/>
       <c r="M41" s="10"/>
-      <c r="N41" s="134" t="s">
+      <c r="N41" s="149" t="s">
         <v>210</v>
       </c>
-      <c r="O41" s="135"/>
-      <c r="P41" s="135"/>
+      <c r="O41" s="150"/>
+      <c r="P41" s="150"/>
       <c r="Q41" s="125">
         <f>Q40/20</f>
         <v>58.489279999999994</v>
       </c>
-      <c r="R41" s="132"/>
-      <c r="S41" s="133"/>
+      <c r="R41" s="147"/>
+      <c r="S41" s="148"/>
     </row>
   </sheetData>
   <mergeCells count="5">
@@ -4299,15 +4299,15 @@
       <c r="H1" s="2"/>
       <c r="I1" s="2"/>
       <c r="J1" s="2"/>
-      <c r="K1" s="126"/>
-      <c r="L1" s="126"/>
-      <c r="M1" s="126"/>
-      <c r="N1" s="126"/>
-      <c r="O1" s="126"/>
-      <c r="P1" s="126"/>
-      <c r="Q1" s="126"/>
-      <c r="R1" s="126"/>
-      <c r="S1" s="127"/>
+      <c r="K1" s="141"/>
+      <c r="L1" s="141"/>
+      <c r="M1" s="141"/>
+      <c r="N1" s="141"/>
+      <c r="O1" s="141"/>
+      <c r="P1" s="141"/>
+      <c r="Q1" s="141"/>
+      <c r="R1" s="141"/>
+      <c r="S1" s="142"/>
     </row>
     <row r="2" spans="1:19" ht="32.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1"/>
@@ -4357,7 +4357,7 @@
       <c r="P3" s="5"/>
       <c r="Q3" s="5"/>
       <c r="R3" s="5"/>
-      <c r="S3" s="128"/>
+      <c r="S3" s="143"/>
     </row>
     <row r="4" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A4" s="1"/>
@@ -4382,7 +4382,7 @@
       <c r="P4" s="6"/>
       <c r="Q4" s="6"/>
       <c r="R4" s="6"/>
-      <c r="S4" s="129"/>
+      <c r="S4" s="144"/>
     </row>
     <row r="5" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A5" s="1"/>
@@ -4407,7 +4407,7 @@
       <c r="P5" s="6"/>
       <c r="Q5" s="6"/>
       <c r="R5" s="6"/>
-      <c r="S5" s="129"/>
+      <c r="S5" s="144"/>
     </row>
     <row r="6" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A6" s="1"/>
@@ -4428,7 +4428,7 @@
       <c r="P6" s="6"/>
       <c r="Q6" s="6"/>
       <c r="R6" s="6"/>
-      <c r="S6" s="129"/>
+      <c r="S6" s="144"/>
     </row>
     <row r="7" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A7" s="1"/>
@@ -4449,7 +4449,7 @@
       <c r="P7" s="8"/>
       <c r="Q7" s="8"/>
       <c r="R7" s="8"/>
-      <c r="S7" s="129"/>
+      <c r="S7" s="144"/>
     </row>
     <row r="8" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" s="1"/>
@@ -4470,7 +4470,7 @@
       <c r="P8" s="8"/>
       <c r="Q8" s="8"/>
       <c r="R8" s="8"/>
-      <c r="S8" s="129"/>
+      <c r="S8" s="144"/>
     </row>
     <row r="9" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A9" s="1"/>
@@ -4974,7 +4974,7 @@
         <f t="shared" si="0"/>
         <v>94.99</v>
       </c>
-      <c r="R17" s="136" t="s">
+      <c r="R17" s="126" t="s">
         <v>218</v>
       </c>
       <c r="S17" s="44"/>
@@ -5144,7 +5144,7 @@
         <f t="shared" si="0"/>
         <v>740.6</v>
       </c>
-      <c r="R20" s="137" t="s">
+      <c r="R20" s="127" t="s">
         <v>218</v>
       </c>
       <c r="S20" s="92"/>
@@ -5821,7 +5821,7 @@
         <f t="shared" ref="Q32:Q39" si="3">P32*N32</f>
         <v>16.8</v>
       </c>
-      <c r="R32" s="137" t="s">
+      <c r="R32" s="127" t="s">
         <v>213</v>
       </c>
       <c r="S32" s="100"/>
@@ -5879,7 +5879,7 @@
         <f t="shared" si="3"/>
         <v>3182.4</v>
       </c>
-      <c r="R33" s="136" t="s">
+      <c r="R33" s="126" t="s">
         <v>213</v>
       </c>
       <c r="S33" s="103"/>
@@ -5993,7 +5993,7 @@
         <f t="shared" si="3"/>
         <v>15116.4</v>
       </c>
-      <c r="R35" s="136" t="s">
+      <c r="R35" s="126" t="s">
         <v>213</v>
       </c>
       <c r="S35" s="103"/>
@@ -6041,17 +6041,17 @@
       <c r="N36" s="64">
         <v>2020</v>
       </c>
-      <c r="O36" s="143" t="s">
+      <c r="O36" s="133" t="s">
         <v>152</v>
       </c>
       <c r="P36" s="90">
         <v>2.6855000000000002</v>
       </c>
-      <c r="Q36" s="145">
+      <c r="Q36" s="135">
         <f t="shared" si="3"/>
         <v>5424.71</v>
       </c>
-      <c r="R36" s="137" t="s">
+      <c r="R36" s="127" t="s">
         <v>215</v>
       </c>
       <c r="S36" s="100"/>
@@ -6109,7 +6109,7 @@
         <f t="shared" si="3"/>
         <v>42.738</v>
       </c>
-      <c r="R37" s="136" t="s">
+      <c r="R37" s="126" t="s">
         <v>216</v>
       </c>
       <c r="S37" s="103"/>
@@ -6223,7 +6223,7 @@
         <f t="shared" si="3"/>
         <v>83.025000000000006</v>
       </c>
-      <c r="R39" s="136" t="s">
+      <c r="R39" s="126" t="s">
         <v>217</v>
       </c>
       <c r="S39" s="106"/>
@@ -6242,17 +6242,17 @@
       <c r="K40" s="60"/>
       <c r="L40" s="60"/>
       <c r="M40" s="60"/>
-      <c r="N40" s="134" t="s">
+      <c r="N40" s="149" t="s">
         <v>209</v>
       </c>
-      <c r="O40" s="135"/>
-      <c r="P40" s="135"/>
+      <c r="O40" s="150"/>
+      <c r="P40" s="150"/>
       <c r="Q40" s="124">
         <f>SUM(Q10:Q39)</f>
         <v>38220.392</v>
       </c>
-      <c r="R40" s="130"/>
-      <c r="S40" s="131"/>
+      <c r="R40" s="145"/>
+      <c r="S40" s="146"/>
     </row>
     <row r="41" spans="1:19" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A41" s="1"/>
@@ -6268,20 +6268,20 @@
       <c r="K41" s="10"/>
       <c r="L41" s="10"/>
       <c r="M41" s="10"/>
-      <c r="N41" s="134" t="s">
+      <c r="N41" s="149" t="s">
         <v>210</v>
       </c>
-      <c r="O41" s="135"/>
-      <c r="P41" s="135"/>
+      <c r="O41" s="150"/>
+      <c r="P41" s="150"/>
       <c r="Q41" s="125">
         <f>Q40/1000</f>
         <v>38.220391999999997</v>
       </c>
-      <c r="R41" s="132"/>
-      <c r="S41" s="133"/>
+      <c r="R41" s="147"/>
+      <c r="S41" s="148"/>
     </row>
     <row r="43" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="P43" s="138"/>
+      <c r="P43" s="128"/>
     </row>
   </sheetData>
   <mergeCells count="5">
@@ -6528,15 +6528,15 @@
       <c r="H1" s="2"/>
       <c r="I1" s="2"/>
       <c r="J1" s="2"/>
-      <c r="K1" s="126"/>
-      <c r="L1" s="126"/>
-      <c r="M1" s="126"/>
-      <c r="N1" s="126"/>
-      <c r="O1" s="126"/>
-      <c r="P1" s="126"/>
-      <c r="Q1" s="126"/>
-      <c r="R1" s="126"/>
-      <c r="S1" s="127"/>
+      <c r="K1" s="141"/>
+      <c r="L1" s="141"/>
+      <c r="M1" s="141"/>
+      <c r="N1" s="141"/>
+      <c r="O1" s="141"/>
+      <c r="P1" s="141"/>
+      <c r="Q1" s="141"/>
+      <c r="R1" s="141"/>
+      <c r="S1" s="142"/>
     </row>
     <row r="2" spans="1:24" ht="32.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1"/>
@@ -6586,7 +6586,7 @@
       <c r="P3" s="5"/>
       <c r="Q3" s="5"/>
       <c r="R3" s="5"/>
-      <c r="S3" s="128"/>
+      <c r="S3" s="143"/>
     </row>
     <row r="4" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A4" s="1"/>
@@ -6611,7 +6611,7 @@
       <c r="P4" s="6"/>
       <c r="Q4" s="6"/>
       <c r="R4" s="6"/>
-      <c r="S4" s="129"/>
+      <c r="S4" s="144"/>
     </row>
     <row r="5" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A5" s="1"/>
@@ -6636,7 +6636,7 @@
       <c r="P5" s="6"/>
       <c r="Q5" s="6"/>
       <c r="R5" s="6"/>
-      <c r="S5" s="129"/>
+      <c r="S5" s="144"/>
     </row>
     <row r="6" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A6" s="1"/>
@@ -6657,7 +6657,7 @@
       <c r="P6" s="6"/>
       <c r="Q6" s="6"/>
       <c r="R6" s="6"/>
-      <c r="S6" s="129"/>
+      <c r="S6" s="144"/>
     </row>
     <row r="7" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A7" s="1"/>
@@ -6678,7 +6678,7 @@
       <c r="P7" s="8"/>
       <c r="Q7" s="8"/>
       <c r="R7" s="8"/>
-      <c r="S7" s="129"/>
+      <c r="S7" s="144"/>
     </row>
     <row r="8" spans="1:24" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" s="1"/>
@@ -6699,7 +6699,7 @@
       <c r="P8" s="8"/>
       <c r="Q8" s="8"/>
       <c r="R8" s="8"/>
-      <c r="S8" s="129"/>
+      <c r="S8" s="144"/>
     </row>
     <row r="9" spans="1:24" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A9" s="1"/>
@@ -6914,7 +6914,7 @@
       <c r="N12" s="64">
         <v>40200</v>
       </c>
-      <c r="O12" s="146" t="s">
+      <c r="O12" s="136" t="s">
         <v>152</v>
       </c>
       <c r="P12" s="90">
@@ -6924,7 +6924,7 @@
         <f t="shared" si="0"/>
         <v>60.300000000000004</v>
       </c>
-      <c r="R12" s="148" t="s">
+      <c r="R12" s="138" t="s">
         <v>218</v>
       </c>
       <c r="S12" s="100"/>
@@ -6972,7 +6972,7 @@
       <c r="N13" s="41">
         <v>10100</v>
       </c>
-      <c r="O13" s="147" t="s">
+      <c r="O13" s="137" t="s">
         <v>152</v>
       </c>
       <c r="P13" s="89">
@@ -6982,7 +6982,7 @@
         <f t="shared" si="0"/>
         <v>11778.619999999999</v>
       </c>
-      <c r="R13" s="149" t="s">
+      <c r="R13" s="139" t="s">
         <v>218</v>
       </c>
       <c r="S13" s="103"/>
@@ -7097,7 +7097,7 @@
         <f t="shared" si="0"/>
         <v>97.919999999999987</v>
       </c>
-      <c r="R15" s="149" t="s">
+      <c r="R15" s="139" t="s">
         <v>218</v>
       </c>
       <c r="S15" s="44"/>
@@ -7211,7 +7211,7 @@
         <f t="shared" si="0"/>
         <v>409.02000000000004</v>
       </c>
-      <c r="R17" s="149" t="s">
+      <c r="R17" s="139" t="s">
         <v>218</v>
       </c>
       <c r="S17" s="103"/>
@@ -7327,7 +7327,7 @@
         <f t="shared" si="0"/>
         <v>11.22</v>
       </c>
-      <c r="R19" s="149" t="s">
+      <c r="R19" s="139" t="s">
         <v>218</v>
       </c>
       <c r="S19" s="44"/>
@@ -7385,7 +7385,7 @@
         <f t="shared" si="0"/>
         <v>3689.2</v>
       </c>
-      <c r="R20" s="148" t="s">
+      <c r="R20" s="138" t="s">
         <v>218</v>
       </c>
       <c r="S20" s="100"/>
@@ -8292,17 +8292,17 @@
       <c r="N36" s="64">
         <v>10050</v>
       </c>
-      <c r="O36" s="143" t="s">
+      <c r="O36" s="133" t="s">
         <v>152</v>
       </c>
       <c r="P36" s="90">
         <v>2.6855000000000002</v>
       </c>
-      <c r="Q36" s="145">
+      <c r="Q36" s="135">
         <f t="shared" si="3"/>
         <v>26989.275000000001</v>
       </c>
-      <c r="R36" s="148" t="s">
+      <c r="R36" s="138" t="s">
         <v>218</v>
       </c>
       <c r="S36" s="100"/>
@@ -8361,7 +8361,7 @@
         <f t="shared" si="3"/>
         <v>191.76399999999998</v>
       </c>
-      <c r="R37" s="149" t="s">
+      <c r="R37" s="139" t="s">
         <v>218</v>
       </c>
       <c r="S37" s="103"/>
@@ -8420,7 +8420,7 @@
         <f t="shared" si="3"/>
         <v>504.51000000000005</v>
       </c>
-      <c r="R38" s="148" t="s">
+      <c r="R38" s="138" t="s">
         <v>218</v>
       </c>
       <c r="S38" s="100"/>
@@ -8479,7 +8479,7 @@
         <f t="shared" si="3"/>
         <v>203.31</v>
       </c>
-      <c r="R39" s="150" t="s">
+      <c r="R39" s="140" t="s">
         <v>218</v>
       </c>
       <c r="S39" s="106"/>
@@ -8499,17 +8499,17 @@
       <c r="K40" s="60"/>
       <c r="L40" s="60"/>
       <c r="M40" s="60"/>
-      <c r="N40" s="134" t="s">
+      <c r="N40" s="149" t="s">
         <v>209</v>
       </c>
-      <c r="O40" s="135"/>
-      <c r="P40" s="135"/>
+      <c r="O40" s="150"/>
+      <c r="P40" s="150"/>
       <c r="Q40" s="124">
         <f>SUM(Q10:Q39)</f>
         <v>186903.826</v>
       </c>
-      <c r="R40" s="130"/>
-      <c r="S40" s="131"/>
+      <c r="R40" s="145"/>
+      <c r="S40" s="146"/>
     </row>
     <row r="41" spans="1:24" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A41" s="1"/>
@@ -8525,17 +8525,17 @@
       <c r="K41" s="10"/>
       <c r="L41" s="10"/>
       <c r="M41" s="10"/>
-      <c r="N41" s="134" t="s">
+      <c r="N41" s="149" t="s">
         <v>210</v>
       </c>
-      <c r="O41" s="135"/>
-      <c r="P41" s="135"/>
+      <c r="O41" s="150"/>
+      <c r="P41" s="150"/>
       <c r="Q41" s="125">
         <f>Q40/5000</f>
         <v>37.380765199999999</v>
       </c>
-      <c r="R41" s="132"/>
-      <c r="S41" s="133"/>
+      <c r="R41" s="147"/>
+      <c r="S41" s="148"/>
     </row>
   </sheetData>
   <mergeCells count="5">
